--- a/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
+++ b/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
-    <sheet name="Kênh YouTube" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Kênh YouTube" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5122" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5118" uniqueCount="482">
   <si>
     <t>EMAIL</t>
   </si>
@@ -61,6 +61,70 @@
     <t>https://www.youtube.com/watch?v=qv5MG_UJsvQ</t>
   </si>
   <si>
+    <t xml:space="preserve">『修羅子のドロドロ人生朗読』では
+日常で起こる様々なスカッとする話や修羅場な体験談を
+投稿しております。
+是非チャンネル登録をお願いいたします！
+https://www.youtube.com/channel/UC--yJkKDiiSR-xsYeIFMvBg
+#修羅場 #スカッと #朗読
+◆再生リスト
+修羅子のドロドロ人生朗読
+https://www.youtube.com/playlist?list=PLZ_puWw8XkS7Tx5Qzly4IDk6Oug7Svana
+◆関連動画
+【修羅場な話】目を覚ますと精神病院の隔離病棟だった。俺「姉貴…これ今どういう状況…？」姉貴「あんた、何も憶えてないの？この5日間のこと…」姉貴は残酷な事実を話し始めました…【朗読】
+https://youtu.be/bsmxfFubyAo
+【修羅場な話】妻「失敗した…」ある日突然、警察から嫁が首を吊って亡くなったという電話が…後日、嫁の遺品を整理していると日記が見つかり見てみると俺は震え上がりました…【朗読】
+https://youtu.be/mz-FY-okItI
+【修羅場な話】俺「なぁ…ベッドに誰かいる？」…交通事故で半身不随になった愛する妻の毛布を剥ぐとそこには衝撃の光景が…【朗読】
+https://youtu.be/f-pn7L4INCI
+【修羅場な話】パソコンから嫁のハ〇撮り動画が出て来ました・・・間男「2年も付き合ってるって知ったら、卒倒するだろうなｗ」→キレた俺はこの動画をア〇ルトサイトに上げました…【朗読】
+https://youtu.be/bR8nkbO-ClI
+【修羅場な話】車の中に大量のDVDがあり中身を確認すると…嫁「黙っててゴメン。でも、言ったら絶対怒ってたでしょ？」そして離婚を決断しました【朗読】
+https://youtu.be/DKWm1RuMqoU
+【修羅場な話】間男「取引中止ってどういうことですか！？」俺「とぼけるならそれでこちらは構いませんよ」嫁「抱いて…」→俺は嫁に… 【朗読】
+https://youtu.be/qv5MG_UJsvQ
+【修羅場な話】ある日、夫が親友の娘を連れて帰ってきました…夫「亡くなった親友の娘だ。見捨てたら施設生活。だからうちで引き取る！頼む！」→しばらくして娘が語った真実に怒りを通り越しました…【朗読】
+https://youtu.be/w8IuyUGhMbU
+【修羅場な話】嫁が不倫をしていたが一度だけチャンスを与えるため夫婦水入らずの旅行に誘いました。嫁「分かった、会社に休めるか聞いてみる」すると旅行に行く3日前に嫁はこう言ってきたんです…【朗読】
+https://youtu.be/0mMZPZmigGU
+【修羅場な話】義兄夫婦が離婚することに。義嫁「引っ越すからもう会う機会もないと思うので、これ渡しておきます。」封筒の中身を確認すると…【朗読】
+https://youtu.be/cgb3zEvU6ak
+【修羅場な話】うちの両親は仮面夫婦です私「お父さん、離婚していいよ」父「お父さんはお母さんに復讐をしているんだよ」私「え？」【朗読】
+https://youtu.be/ZtAPTciroF8
+【修羅場な話】嫁が１０年来の親友と度々、肉体関係を交わしていました・・・親友「ただの遊びなんだからそんなにヤイヤイ言うなよｗｗ」→キレた俺はその親友の結婚式でサプライズを披露しました！【朗読】
+https://youtu.be/WdeE5K2VT2s
+【修羅場な話】嫁が間男を家に連れ込んでいた！離婚だけでは済ませたくない…友人と上司に協力してもらい復讐を誓った！ 【朗読】
+https://youtu.be/3CzomfPCHkc
+【修羅場】興信所に頼んで調査してもらうと妻の浮気の証拠がわんさか…汚嫁「あーあ、旦那まじつまんない。金もらって離婚したいな～」間男「離婚したら俺と結婚しようよｗ」→こいつらが後悔するくらいの復讐を
+https://youtu.be/2PVH-xpG3I8
+【修羅場】事あるごとに嫁いびりのトメがボケた。長男である夫は体裁を気にして引き取った。結果・・・ 【朗読】
+https://youtu.be/9ae5RR_YrG0
+【修羅場な話】絶縁状態の毒親母から「お前は家族に含まない。だけど家族で楽しむから寄付だけはしろ！」と呆れたことを言い放ち… 【朗読】
+https://youtu.be/OacaKd4uzVs
+◆BGM
+・YouTubeオーディオライブラリ
+https://studio.youtube.com/channel/UC--yJkKDiiSR-xsYeIFMvBg/music
+・甘茶の音楽工房
+https://amachamusic.chagasi.com/index.html
+◆用語説明
+・ウト　→　しゅうと（義理の父）
+・トメ　→　しゅうとめ、義母（義理の母）
+・コトメ子　→　コトメの子供
+・エネ　→　敵（エネ夫）
+・ウトメ　→　義理の親、義両親（ウトとトメのこと）
+・コウト　→　こじゅうと、小舅（義理の兄弟）
+・コトメ　→　こじゅうとめ、小姑、義姉、泥義姉（義理の姉妹）
+・DQN　→　軽率そうな粗暴そうな者。非常識なもの。インターネットスラング。（DQN返し）
+・マザコン　→　母親に対して青年が強い愛着・執着を持つ状態を指す。
+スカッと話、スカッとする話、スッキリ、撃退、感動話、感動する話、嘘のような本当の話、2ch、5ch、2ちゃんねる</t>
+  </si>
+  <si>
+    <t>修羅場, スカッとする話, 修羅場な話, 朗読, その後, 因果応報, スカッと, 復讐, 浮気, 不倫, 離婚, 後悔, 修羅場な話がすかっと大好きｗ, DQN返し, スッキリ, 汚嫁, 慰謝料, 感動話, 旦那, 撃退, 救急, 間男, DQN, スカッと話, 浮気男, いじわる, サレ妻, 修羅子のドロドロ人生朗読『修羅場な体験談』</t>
+  </si>
+  <si>
+    <t>Đã tạo video</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=hX45BtIdlIA</t>
   </si>
   <si>
@@ -1451,9 +1515,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=hbYXMP8bgZ4</t>
-  </si>
-  <si>
-    <t>Đã tạo video</t>
   </si>
 </sst>
 </file>
@@ -1462,11 +1523,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1495,9 +1556,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1779,7 +1843,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K466"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1842,23 +1906,20 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
-        <v>11</v>
-      </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1872,28 +1933,25 @@
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
-        <v>11</v>
-      </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1907,17 +1965,17 @@
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
@@ -1928,7 +1986,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>479</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1942,28 +2000,25 @@
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>21</v>
       </c>
-      <c r="J5" t="s">
-        <v>11</v>
-      </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1977,7 +2032,7 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -1991,14 +2046,11 @@
       <c r="H6" t="s">
         <v>11</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>21</v>
       </c>
-      <c r="J6" t="s">
-        <v>11</v>
-      </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2012,7 +2064,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -2033,7 +2085,7 @@
         <v>11</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2047,7 +2099,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -2068,7 +2120,7 @@
         <v>11</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2082,7 +2134,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -2103,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2117,7 +2169,7 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -2138,7 +2190,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2152,7 +2204,7 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -2173,7 +2225,7 @@
         <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2187,7 +2239,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -2208,7 +2260,7 @@
         <v>11</v>
       </c>
       <c r="K12" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2222,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -2243,7 +2295,7 @@
         <v>11</v>
       </c>
       <c r="K13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2257,7 +2309,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -2278,7 +2330,7 @@
         <v>11</v>
       </c>
       <c r="K14" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2292,7 +2344,7 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -2313,7 +2365,7 @@
         <v>11</v>
       </c>
       <c r="K15" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2327,7 +2379,7 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -2348,7 +2400,7 @@
         <v>11</v>
       </c>
       <c r="K16" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2362,7 +2414,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
@@ -2383,7 +2435,7 @@
         <v>11</v>
       </c>
       <c r="K17" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2397,7 +2449,7 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
@@ -2418,7 +2470,7 @@
         <v>11</v>
       </c>
       <c r="K18" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2432,7 +2484,7 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -2453,7 +2505,7 @@
         <v>11</v>
       </c>
       <c r="K19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2467,7 +2519,7 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -2488,7 +2540,7 @@
         <v>11</v>
       </c>
       <c r="K20" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2502,7 +2554,7 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
@@ -2523,7 +2575,7 @@
         <v>11</v>
       </c>
       <c r="K21" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2537,7 +2589,7 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -2558,7 +2610,7 @@
         <v>11</v>
       </c>
       <c r="K22" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2572,7 +2624,7 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
@@ -2593,7 +2645,7 @@
         <v>11</v>
       </c>
       <c r="K23" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -2607,7 +2659,7 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
@@ -2628,7 +2680,7 @@
         <v>11</v>
       </c>
       <c r="K24" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -2642,7 +2694,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
@@ -2663,7 +2715,7 @@
         <v>11</v>
       </c>
       <c r="K25" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -2677,7 +2729,7 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
@@ -2698,7 +2750,7 @@
         <v>11</v>
       </c>
       <c r="K26" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -2712,7 +2764,7 @@
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
@@ -2733,7 +2785,7 @@
         <v>11</v>
       </c>
       <c r="K27" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -2747,7 +2799,7 @@
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E28" t="s">
         <v>11</v>
@@ -2768,7 +2820,7 @@
         <v>11</v>
       </c>
       <c r="K28" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -2782,7 +2834,7 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -2803,7 +2855,7 @@
         <v>11</v>
       </c>
       <c r="K29" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -2817,7 +2869,7 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E30" t="s">
         <v>11</v>
@@ -2838,7 +2890,7 @@
         <v>11</v>
       </c>
       <c r="K30" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2852,7 +2904,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
@@ -2873,7 +2925,7 @@
         <v>11</v>
       </c>
       <c r="K31" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2887,7 +2939,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
@@ -2908,7 +2960,7 @@
         <v>11</v>
       </c>
       <c r="K32" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2922,7 +2974,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
@@ -2943,7 +2995,7 @@
         <v>11</v>
       </c>
       <c r="K33" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -2957,7 +3009,7 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
         <v>11</v>
@@ -2978,7 +3030,7 @@
         <v>11</v>
       </c>
       <c r="K34" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2992,7 +3044,7 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
@@ -3013,7 +3065,7 @@
         <v>11</v>
       </c>
       <c r="K35" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3027,7 +3079,7 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
         <v>11</v>
@@ -3048,7 +3100,7 @@
         <v>11</v>
       </c>
       <c r="K36" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3062,7 +3114,7 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E37" t="s">
         <v>11</v>
@@ -3083,7 +3135,7 @@
         <v>11</v>
       </c>
       <c r="K37" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3097,7 +3149,7 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E38" t="s">
         <v>11</v>
@@ -3118,7 +3170,7 @@
         <v>11</v>
       </c>
       <c r="K38" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3132,7 +3184,7 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
         <v>11</v>
@@ -3153,7 +3205,7 @@
         <v>11</v>
       </c>
       <c r="K39" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3167,7 +3219,7 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E40" t="s">
         <v>11</v>
@@ -3188,7 +3240,7 @@
         <v>11</v>
       </c>
       <c r="K40" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3202,7 +3254,7 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
@@ -3223,7 +3275,7 @@
         <v>11</v>
       </c>
       <c r="K41" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3237,7 +3289,7 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
         <v>11</v>
@@ -3258,7 +3310,7 @@
         <v>11</v>
       </c>
       <c r="K42" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3272,7 +3324,7 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E43" t="s">
         <v>11</v>
@@ -3293,7 +3345,7 @@
         <v>11</v>
       </c>
       <c r="K43" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3307,7 +3359,7 @@
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E44" t="s">
         <v>11</v>
@@ -3328,7 +3380,7 @@
         <v>11</v>
       </c>
       <c r="K44" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3342,7 +3394,7 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E45" t="s">
         <v>11</v>
@@ -3363,7 +3415,7 @@
         <v>11</v>
       </c>
       <c r="K45" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3377,7 +3429,7 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E46" t="s">
         <v>11</v>
@@ -3398,7 +3450,7 @@
         <v>11</v>
       </c>
       <c r="K46" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3412,7 +3464,7 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
@@ -3433,7 +3485,7 @@
         <v>11</v>
       </c>
       <c r="K47" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3447,7 +3499,7 @@
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E48" t="s">
         <v>11</v>
@@ -3468,7 +3520,7 @@
         <v>11</v>
       </c>
       <c r="K48" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3482,7 +3534,7 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E49" t="s">
         <v>11</v>
@@ -3503,7 +3555,7 @@
         <v>11</v>
       </c>
       <c r="K49" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -3517,7 +3569,7 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E50" t="s">
         <v>11</v>
@@ -3538,7 +3590,7 @@
         <v>11</v>
       </c>
       <c r="K50" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -3552,7 +3604,7 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E51" t="s">
         <v>11</v>
@@ -3573,7 +3625,7 @@
         <v>11</v>
       </c>
       <c r="K51" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -3587,7 +3639,7 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E52" t="s">
         <v>11</v>
@@ -3608,7 +3660,7 @@
         <v>11</v>
       </c>
       <c r="K52" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -3622,7 +3674,7 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
@@ -3643,7 +3695,7 @@
         <v>11</v>
       </c>
       <c r="K53" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -3657,7 +3709,7 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E54" t="s">
         <v>11</v>
@@ -3678,7 +3730,7 @@
         <v>11</v>
       </c>
       <c r="K54" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -3692,7 +3744,7 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E55" t="s">
         <v>11</v>
@@ -3713,7 +3765,7 @@
         <v>11</v>
       </c>
       <c r="K55" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -3727,7 +3779,7 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E56" t="s">
         <v>11</v>
@@ -3748,7 +3800,7 @@
         <v>11</v>
       </c>
       <c r="K56" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -3762,7 +3814,7 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E57" t="s">
         <v>11</v>
@@ -3783,7 +3835,7 @@
         <v>11</v>
       </c>
       <c r="K57" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -3797,7 +3849,7 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E58" t="s">
         <v>11</v>
@@ -3818,7 +3870,7 @@
         <v>11</v>
       </c>
       <c r="K58" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -3832,7 +3884,7 @@
         <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E59" t="s">
         <v>11</v>
@@ -3853,7 +3905,7 @@
         <v>11</v>
       </c>
       <c r="K59" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -3867,7 +3919,7 @@
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E60" t="s">
         <v>11</v>
@@ -3888,7 +3940,7 @@
         <v>11</v>
       </c>
       <c r="K60" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -3902,7 +3954,7 @@
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E61" t="s">
         <v>11</v>
@@ -3923,7 +3975,7 @@
         <v>11</v>
       </c>
       <c r="K61" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -3937,7 +3989,7 @@
         <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E62" t="s">
         <v>11</v>
@@ -3958,7 +4010,7 @@
         <v>11</v>
       </c>
       <c r="K62" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -3972,7 +4024,7 @@
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
@@ -3993,7 +4045,7 @@
         <v>11</v>
       </c>
       <c r="K63" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4007,7 +4059,7 @@
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E64" t="s">
         <v>11</v>
@@ -4028,7 +4080,7 @@
         <v>11</v>
       </c>
       <c r="K64" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4042,7 +4094,7 @@
         <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E65" t="s">
         <v>11</v>
@@ -4063,7 +4115,7 @@
         <v>11</v>
       </c>
       <c r="K65" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4077,7 +4129,7 @@
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E66" t="s">
         <v>11</v>
@@ -4098,7 +4150,7 @@
         <v>11</v>
       </c>
       <c r="K66" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4112,7 +4164,7 @@
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E67" t="s">
         <v>11</v>
@@ -4133,7 +4185,7 @@
         <v>11</v>
       </c>
       <c r="K67" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4147,7 +4199,7 @@
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E68" t="s">
         <v>11</v>
@@ -4168,7 +4220,7 @@
         <v>11</v>
       </c>
       <c r="K68" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4182,7 +4234,7 @@
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E69" t="s">
         <v>11</v>
@@ -4203,7 +4255,7 @@
         <v>11</v>
       </c>
       <c r="K69" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4217,7 +4269,7 @@
         <v>11</v>
       </c>
       <c r="D70" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
@@ -4238,7 +4290,7 @@
         <v>11</v>
       </c>
       <c r="K70" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4252,7 +4304,7 @@
         <v>11</v>
       </c>
       <c r="D71" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
@@ -4273,7 +4325,7 @@
         <v>11</v>
       </c>
       <c r="K71" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4287,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E72" t="s">
         <v>11</v>
@@ -4308,7 +4360,7 @@
         <v>11</v>
       </c>
       <c r="K72" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4322,7 +4374,7 @@
         <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
@@ -4343,7 +4395,7 @@
         <v>11</v>
       </c>
       <c r="K73" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4357,7 +4409,7 @@
         <v>11</v>
       </c>
       <c r="D74" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E74" t="s">
         <v>11</v>
@@ -4378,7 +4430,7 @@
         <v>11</v>
       </c>
       <c r="K74" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4392,7 +4444,7 @@
         <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E75" t="s">
         <v>11</v>
@@ -4413,7 +4465,7 @@
         <v>11</v>
       </c>
       <c r="K75" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4427,7 +4479,7 @@
         <v>11</v>
       </c>
       <c r="D76" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
@@ -4448,7 +4500,7 @@
         <v>11</v>
       </c>
       <c r="K76" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4462,7 +4514,7 @@
         <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E77" t="s">
         <v>11</v>
@@ -4483,7 +4535,7 @@
         <v>11</v>
       </c>
       <c r="K77" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4497,7 +4549,7 @@
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E78" t="s">
         <v>11</v>
@@ -4518,7 +4570,7 @@
         <v>11</v>
       </c>
       <c r="K78" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -4532,7 +4584,7 @@
         <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
@@ -4553,7 +4605,7 @@
         <v>11</v>
       </c>
       <c r="K79" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -4567,7 +4619,7 @@
         <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s">
         <v>11</v>
@@ -4588,7 +4640,7 @@
         <v>11</v>
       </c>
       <c r="K80" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -4602,7 +4654,7 @@
         <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E81" t="s">
         <v>11</v>
@@ -4623,7 +4675,7 @@
         <v>11</v>
       </c>
       <c r="K81" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -4637,7 +4689,7 @@
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E82" t="s">
         <v>11</v>
@@ -4658,7 +4710,7 @@
         <v>11</v>
       </c>
       <c r="K82" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -4672,7 +4724,7 @@
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E83" t="s">
         <v>11</v>
@@ -4693,7 +4745,7 @@
         <v>11</v>
       </c>
       <c r="K83" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -4707,7 +4759,7 @@
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E84" t="s">
         <v>11</v>
@@ -4728,7 +4780,7 @@
         <v>11</v>
       </c>
       <c r="K84" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -4742,7 +4794,7 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E85" t="s">
         <v>11</v>
@@ -4763,7 +4815,7 @@
         <v>11</v>
       </c>
       <c r="K85" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -4777,7 +4829,7 @@
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E86" t="s">
         <v>11</v>
@@ -4798,7 +4850,7 @@
         <v>11</v>
       </c>
       <c r="K86" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -4812,7 +4864,7 @@
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
@@ -4833,7 +4885,7 @@
         <v>11</v>
       </c>
       <c r="K87" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -4847,7 +4899,7 @@
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
@@ -4868,7 +4920,7 @@
         <v>11</v>
       </c>
       <c r="K88" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -4882,7 +4934,7 @@
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
@@ -4903,7 +4955,7 @@
         <v>11</v>
       </c>
       <c r="K89" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -4917,7 +4969,7 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
@@ -4938,7 +4990,7 @@
         <v>11</v>
       </c>
       <c r="K90" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -4952,7 +5004,7 @@
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
@@ -4973,7 +5025,7 @@
         <v>11</v>
       </c>
       <c r="K91" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -4987,7 +5039,7 @@
         <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E92" t="s">
         <v>11</v>
@@ -5008,7 +5060,7 @@
         <v>11</v>
       </c>
       <c r="K92" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5022,7 +5074,7 @@
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
@@ -5043,7 +5095,7 @@
         <v>11</v>
       </c>
       <c r="K93" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5057,7 +5109,7 @@
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E94" t="s">
         <v>11</v>
@@ -5078,7 +5130,7 @@
         <v>11</v>
       </c>
       <c r="K94" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5092,7 +5144,7 @@
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E95" t="s">
         <v>11</v>
@@ -5113,7 +5165,7 @@
         <v>11</v>
       </c>
       <c r="K95" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5127,7 +5179,7 @@
         <v>11</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E96" t="s">
         <v>11</v>
@@ -5148,7 +5200,7 @@
         <v>11</v>
       </c>
       <c r="K96" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5162,7 +5214,7 @@
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E97" t="s">
         <v>11</v>
@@ -5183,7 +5235,7 @@
         <v>11</v>
       </c>
       <c r="K97" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5197,7 +5249,7 @@
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E98" t="s">
         <v>11</v>
@@ -5218,7 +5270,7 @@
         <v>11</v>
       </c>
       <c r="K98" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5232,7 +5284,7 @@
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E99" t="s">
         <v>11</v>
@@ -5253,7 +5305,7 @@
         <v>11</v>
       </c>
       <c r="K99" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5267,7 +5319,7 @@
         <v>11</v>
       </c>
       <c r="D100" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E100" t="s">
         <v>11</v>
@@ -5288,7 +5340,7 @@
         <v>11</v>
       </c>
       <c r="K100" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5302,7 +5354,7 @@
         <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E101" t="s">
         <v>11</v>
@@ -5323,7 +5375,7 @@
         <v>11</v>
       </c>
       <c r="K101" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5337,7 +5389,7 @@
         <v>11</v>
       </c>
       <c r="D102" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E102" t="s">
         <v>11</v>
@@ -5358,7 +5410,7 @@
         <v>11</v>
       </c>
       <c r="K102" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5372,7 +5424,7 @@
         <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E103" t="s">
         <v>11</v>
@@ -5393,7 +5445,7 @@
         <v>11</v>
       </c>
       <c r="K103" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5407,7 +5459,7 @@
         <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E104" t="s">
         <v>11</v>
@@ -5428,7 +5480,7 @@
         <v>11</v>
       </c>
       <c r="K104" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5442,7 +5494,7 @@
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E105" t="s">
         <v>11</v>
@@ -5463,7 +5515,7 @@
         <v>11</v>
       </c>
       <c r="K105" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -5477,7 +5529,7 @@
         <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E106" t="s">
         <v>11</v>
@@ -5498,7 +5550,7 @@
         <v>11</v>
       </c>
       <c r="K106" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -5512,7 +5564,7 @@
         <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E107" t="s">
         <v>11</v>
@@ -5533,7 +5585,7 @@
         <v>11</v>
       </c>
       <c r="K107" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -5547,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
@@ -5568,7 +5620,7 @@
         <v>11</v>
       </c>
       <c r="K108" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -5582,7 +5634,7 @@
         <v>11</v>
       </c>
       <c r="D109" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E109" t="s">
         <v>11</v>
@@ -5603,7 +5655,7 @@
         <v>11</v>
       </c>
       <c r="K109" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -5617,7 +5669,7 @@
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E110" t="s">
         <v>11</v>
@@ -5638,7 +5690,7 @@
         <v>11</v>
       </c>
       <c r="K110" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -5652,7 +5704,7 @@
         <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E111" t="s">
         <v>11</v>
@@ -5673,7 +5725,7 @@
         <v>11</v>
       </c>
       <c r="K111" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -5687,7 +5739,7 @@
         <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E112" t="s">
         <v>11</v>
@@ -5708,7 +5760,7 @@
         <v>11</v>
       </c>
       <c r="K112" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -5722,7 +5774,7 @@
         <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
@@ -5743,7 +5795,7 @@
         <v>11</v>
       </c>
       <c r="K113" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -5757,7 +5809,7 @@
         <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E114" t="s">
         <v>11</v>
@@ -5778,7 +5830,7 @@
         <v>11</v>
       </c>
       <c r="K114" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -5792,7 +5844,7 @@
         <v>11</v>
       </c>
       <c r="D115" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
@@ -5813,7 +5865,7 @@
         <v>11</v>
       </c>
       <c r="K115" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -5827,7 +5879,7 @@
         <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E116" t="s">
         <v>11</v>
@@ -5848,7 +5900,7 @@
         <v>11</v>
       </c>
       <c r="K116" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -5862,7 +5914,7 @@
         <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
@@ -5883,7 +5935,7 @@
         <v>11</v>
       </c>
       <c r="K117" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -5897,7 +5949,7 @@
         <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E118" t="s">
         <v>11</v>
@@ -5918,7 +5970,7 @@
         <v>11</v>
       </c>
       <c r="K118" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -5932,7 +5984,7 @@
         <v>11</v>
       </c>
       <c r="D119" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E119" t="s">
         <v>11</v>
@@ -5953,7 +6005,7 @@
         <v>11</v>
       </c>
       <c r="K119" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -5967,7 +6019,7 @@
         <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E120" t="s">
         <v>11</v>
@@ -5988,7 +6040,7 @@
         <v>11</v>
       </c>
       <c r="K120" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6002,7 +6054,7 @@
         <v>11</v>
       </c>
       <c r="D121" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E121" t="s">
         <v>11</v>
@@ -6023,7 +6075,7 @@
         <v>11</v>
       </c>
       <c r="K121" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6037,7 +6089,7 @@
         <v>11</v>
       </c>
       <c r="D122" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E122" t="s">
         <v>11</v>
@@ -6058,7 +6110,7 @@
         <v>11</v>
       </c>
       <c r="K122" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6072,7 +6124,7 @@
         <v>11</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E123" t="s">
         <v>11</v>
@@ -6093,7 +6145,7 @@
         <v>11</v>
       </c>
       <c r="K123" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6107,7 +6159,7 @@
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E124" t="s">
         <v>11</v>
@@ -6128,7 +6180,7 @@
         <v>11</v>
       </c>
       <c r="K124" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6142,7 +6194,7 @@
         <v>11</v>
       </c>
       <c r="D125" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E125" t="s">
         <v>11</v>
@@ -6163,7 +6215,7 @@
         <v>11</v>
       </c>
       <c r="K125" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6177,7 +6229,7 @@
         <v>11</v>
       </c>
       <c r="D126" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E126" t="s">
         <v>11</v>
@@ -6198,7 +6250,7 @@
         <v>11</v>
       </c>
       <c r="K126" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6212,7 +6264,7 @@
         <v>11</v>
       </c>
       <c r="D127" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E127" t="s">
         <v>11</v>
@@ -6233,7 +6285,7 @@
         <v>11</v>
       </c>
       <c r="K127" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6247,7 +6299,7 @@
         <v>11</v>
       </c>
       <c r="D128" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E128" t="s">
         <v>11</v>
@@ -6268,7 +6320,7 @@
         <v>11</v>
       </c>
       <c r="K128" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6282,7 +6334,7 @@
         <v>11</v>
       </c>
       <c r="D129" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E129" t="s">
         <v>11</v>
@@ -6303,7 +6355,7 @@
         <v>11</v>
       </c>
       <c r="K129" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6317,7 +6369,7 @@
         <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E130" t="s">
         <v>11</v>
@@ -6338,7 +6390,7 @@
         <v>11</v>
       </c>
       <c r="K130" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6352,7 +6404,7 @@
         <v>11</v>
       </c>
       <c r="D131" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E131" t="s">
         <v>11</v>
@@ -6373,7 +6425,7 @@
         <v>11</v>
       </c>
       <c r="K131" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -6387,7 +6439,7 @@
         <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E132" t="s">
         <v>11</v>
@@ -6408,7 +6460,7 @@
         <v>11</v>
       </c>
       <c r="K132" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -6422,7 +6474,7 @@
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E133" t="s">
         <v>11</v>
@@ -6443,7 +6495,7 @@
         <v>11</v>
       </c>
       <c r="K133" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6457,7 +6509,7 @@
         <v>11</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E134" t="s">
         <v>11</v>
@@ -6478,7 +6530,7 @@
         <v>11</v>
       </c>
       <c r="K134" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6492,7 +6544,7 @@
         <v>11</v>
       </c>
       <c r="D135" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E135" t="s">
         <v>11</v>
@@ -6513,7 +6565,7 @@
         <v>11</v>
       </c>
       <c r="K135" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6527,7 +6579,7 @@
         <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E136" t="s">
         <v>11</v>
@@ -6548,7 +6600,7 @@
         <v>11</v>
       </c>
       <c r="K136" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -6562,7 +6614,7 @@
         <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E137" t="s">
         <v>11</v>
@@ -6583,7 +6635,7 @@
         <v>11</v>
       </c>
       <c r="K137" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -6597,7 +6649,7 @@
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E138" t="s">
         <v>11</v>
@@ -6618,7 +6670,7 @@
         <v>11</v>
       </c>
       <c r="K138" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -6632,7 +6684,7 @@
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E139" t="s">
         <v>11</v>
@@ -6653,7 +6705,7 @@
         <v>11</v>
       </c>
       <c r="K139" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -6667,7 +6719,7 @@
         <v>11</v>
       </c>
       <c r="D140" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E140" t="s">
         <v>11</v>
@@ -6688,7 +6740,7 @@
         <v>11</v>
       </c>
       <c r="K140" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -6702,7 +6754,7 @@
         <v>11</v>
       </c>
       <c r="D141" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E141" t="s">
         <v>11</v>
@@ -6723,7 +6775,7 @@
         <v>11</v>
       </c>
       <c r="K141" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -6737,7 +6789,7 @@
         <v>11</v>
       </c>
       <c r="D142" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E142" t="s">
         <v>11</v>
@@ -6758,7 +6810,7 @@
         <v>11</v>
       </c>
       <c r="K142" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -6772,7 +6824,7 @@
         <v>11</v>
       </c>
       <c r="D143" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E143" t="s">
         <v>11</v>
@@ -6793,7 +6845,7 @@
         <v>11</v>
       </c>
       <c r="K143" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -6807,7 +6859,7 @@
         <v>11</v>
       </c>
       <c r="D144" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E144" t="s">
         <v>11</v>
@@ -6828,7 +6880,7 @@
         <v>11</v>
       </c>
       <c r="K144" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -6842,7 +6894,7 @@
         <v>11</v>
       </c>
       <c r="D145" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E145" t="s">
         <v>11</v>
@@ -6863,7 +6915,7 @@
         <v>11</v>
       </c>
       <c r="K145" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -6877,7 +6929,7 @@
         <v>11</v>
       </c>
       <c r="D146" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E146" t="s">
         <v>11</v>
@@ -6898,7 +6950,7 @@
         <v>11</v>
       </c>
       <c r="K146" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -6912,7 +6964,7 @@
         <v>11</v>
       </c>
       <c r="D147" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E147" t="s">
         <v>11</v>
@@ -6933,7 +6985,7 @@
         <v>11</v>
       </c>
       <c r="K147" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -6947,7 +6999,7 @@
         <v>11</v>
       </c>
       <c r="D148" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E148" t="s">
         <v>11</v>
@@ -6968,7 +7020,7 @@
         <v>11</v>
       </c>
       <c r="K148" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -6982,7 +7034,7 @@
         <v>11</v>
       </c>
       <c r="D149" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E149" t="s">
         <v>11</v>
@@ -7003,7 +7055,7 @@
         <v>11</v>
       </c>
       <c r="K149" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7017,7 +7069,7 @@
         <v>11</v>
       </c>
       <c r="D150" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E150" t="s">
         <v>11</v>
@@ -7038,7 +7090,7 @@
         <v>11</v>
       </c>
       <c r="K150" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7052,7 +7104,7 @@
         <v>11</v>
       </c>
       <c r="D151" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E151" t="s">
         <v>11</v>
@@ -7073,7 +7125,7 @@
         <v>11</v>
       </c>
       <c r="K151" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7087,7 +7139,7 @@
         <v>11</v>
       </c>
       <c r="D152" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E152" t="s">
         <v>11</v>
@@ -7108,7 +7160,7 @@
         <v>11</v>
       </c>
       <c r="K152" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7122,7 +7174,7 @@
         <v>11</v>
       </c>
       <c r="D153" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E153" t="s">
         <v>11</v>
@@ -7143,7 +7195,7 @@
         <v>11</v>
       </c>
       <c r="K153" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7157,7 +7209,7 @@
         <v>11</v>
       </c>
       <c r="D154" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E154" t="s">
         <v>11</v>
@@ -7178,7 +7230,7 @@
         <v>11</v>
       </c>
       <c r="K154" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -7192,7 +7244,7 @@
         <v>11</v>
       </c>
       <c r="D155" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E155" t="s">
         <v>11</v>
@@ -7213,7 +7265,7 @@
         <v>11</v>
       </c>
       <c r="K155" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -7227,7 +7279,7 @@
         <v>11</v>
       </c>
       <c r="D156" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E156" t="s">
         <v>11</v>
@@ -7248,7 +7300,7 @@
         <v>11</v>
       </c>
       <c r="K156" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7262,7 +7314,7 @@
         <v>11</v>
       </c>
       <c r="D157" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E157" t="s">
         <v>11</v>
@@ -7283,7 +7335,7 @@
         <v>11</v>
       </c>
       <c r="K157" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7297,7 +7349,7 @@
         <v>11</v>
       </c>
       <c r="D158" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E158" t="s">
         <v>11</v>
@@ -7318,7 +7370,7 @@
         <v>11</v>
       </c>
       <c r="K158" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7332,7 +7384,7 @@
         <v>11</v>
       </c>
       <c r="D159" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E159" t="s">
         <v>11</v>
@@ -7353,7 +7405,7 @@
         <v>11</v>
       </c>
       <c r="K159" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7367,7 +7419,7 @@
         <v>11</v>
       </c>
       <c r="D160" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E160" t="s">
         <v>11</v>
@@ -7388,7 +7440,7 @@
         <v>11</v>
       </c>
       <c r="K160" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7402,7 +7454,7 @@
         <v>11</v>
       </c>
       <c r="D161" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E161" t="s">
         <v>11</v>
@@ -7423,7 +7475,7 @@
         <v>11</v>
       </c>
       <c r="K161" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -7437,7 +7489,7 @@
         <v>11</v>
       </c>
       <c r="D162" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E162" t="s">
         <v>11</v>
@@ -7458,7 +7510,7 @@
         <v>11</v>
       </c>
       <c r="K162" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -7472,7 +7524,7 @@
         <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E163" t="s">
         <v>11</v>
@@ -7493,7 +7545,7 @@
         <v>11</v>
       </c>
       <c r="K163" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7507,7 +7559,7 @@
         <v>11</v>
       </c>
       <c r="D164" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E164" t="s">
         <v>11</v>
@@ -7528,7 +7580,7 @@
         <v>11</v>
       </c>
       <c r="K164" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7542,7 +7594,7 @@
         <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E165" t="s">
         <v>11</v>
@@ -7563,7 +7615,7 @@
         <v>11</v>
       </c>
       <c r="K165" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -7577,7 +7629,7 @@
         <v>11</v>
       </c>
       <c r="D166" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E166" t="s">
         <v>11</v>
@@ -7598,7 +7650,7 @@
         <v>11</v>
       </c>
       <c r="K166" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -7612,7 +7664,7 @@
         <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E167" t="s">
         <v>11</v>
@@ -7633,7 +7685,7 @@
         <v>11</v>
       </c>
       <c r="K167" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -7647,7 +7699,7 @@
         <v>11</v>
       </c>
       <c r="D168" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E168" t="s">
         <v>11</v>
@@ -7668,7 +7720,7 @@
         <v>11</v>
       </c>
       <c r="K168" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -7682,7 +7734,7 @@
         <v>11</v>
       </c>
       <c r="D169" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E169" t="s">
         <v>11</v>
@@ -7703,7 +7755,7 @@
         <v>11</v>
       </c>
       <c r="K169" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -7717,7 +7769,7 @@
         <v>11</v>
       </c>
       <c r="D170" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E170" t="s">
         <v>11</v>
@@ -7738,7 +7790,7 @@
         <v>11</v>
       </c>
       <c r="K170" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -7752,7 +7804,7 @@
         <v>11</v>
       </c>
       <c r="D171" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E171" t="s">
         <v>11</v>
@@ -7773,7 +7825,7 @@
         <v>11</v>
       </c>
       <c r="K171" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -7787,7 +7839,7 @@
         <v>11</v>
       </c>
       <c r="D172" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E172" t="s">
         <v>11</v>
@@ -7808,7 +7860,7 @@
         <v>11</v>
       </c>
       <c r="K172" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -7822,7 +7874,7 @@
         <v>11</v>
       </c>
       <c r="D173" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E173" t="s">
         <v>11</v>
@@ -7843,7 +7895,7 @@
         <v>11</v>
       </c>
       <c r="K173" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -7857,7 +7909,7 @@
         <v>11</v>
       </c>
       <c r="D174" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E174" t="s">
         <v>11</v>
@@ -7878,7 +7930,7 @@
         <v>11</v>
       </c>
       <c r="K174" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -7892,7 +7944,7 @@
         <v>11</v>
       </c>
       <c r="D175" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E175" t="s">
         <v>11</v>
@@ -7913,7 +7965,7 @@
         <v>11</v>
       </c>
       <c r="K175" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -7927,7 +7979,7 @@
         <v>11</v>
       </c>
       <c r="D176" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E176" t="s">
         <v>11</v>
@@ -7948,7 +8000,7 @@
         <v>11</v>
       </c>
       <c r="K176" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -7962,7 +8014,7 @@
         <v>11</v>
       </c>
       <c r="D177" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E177" t="s">
         <v>11</v>
@@ -7983,7 +8035,7 @@
         <v>11</v>
       </c>
       <c r="K177" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -7997,7 +8049,7 @@
         <v>11</v>
       </c>
       <c r="D178" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E178" t="s">
         <v>11</v>
@@ -8018,7 +8070,7 @@
         <v>11</v>
       </c>
       <c r="K178" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8032,7 +8084,7 @@
         <v>11</v>
       </c>
       <c r="D179" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E179" t="s">
         <v>11</v>
@@ -8053,7 +8105,7 @@
         <v>11</v>
       </c>
       <c r="K179" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8067,7 +8119,7 @@
         <v>11</v>
       </c>
       <c r="D180" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E180" t="s">
         <v>11</v>
@@ -8088,7 +8140,7 @@
         <v>11</v>
       </c>
       <c r="K180" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8102,7 +8154,7 @@
         <v>11</v>
       </c>
       <c r="D181" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E181" t="s">
         <v>11</v>
@@ -8123,7 +8175,7 @@
         <v>11</v>
       </c>
       <c r="K181" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8137,7 +8189,7 @@
         <v>11</v>
       </c>
       <c r="D182" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E182" t="s">
         <v>11</v>
@@ -8158,7 +8210,7 @@
         <v>11</v>
       </c>
       <c r="K182" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8172,7 +8224,7 @@
         <v>11</v>
       </c>
       <c r="D183" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E183" t="s">
         <v>11</v>
@@ -8193,7 +8245,7 @@
         <v>11</v>
       </c>
       <c r="K183" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8207,7 +8259,7 @@
         <v>11</v>
       </c>
       <c r="D184" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E184" t="s">
         <v>11</v>
@@ -8228,7 +8280,7 @@
         <v>11</v>
       </c>
       <c r="K184" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8242,7 +8294,7 @@
         <v>11</v>
       </c>
       <c r="D185" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E185" t="s">
         <v>11</v>
@@ -8263,7 +8315,7 @@
         <v>11</v>
       </c>
       <c r="K185" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8277,7 +8329,7 @@
         <v>11</v>
       </c>
       <c r="D186" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E186" t="s">
         <v>11</v>
@@ -8298,7 +8350,7 @@
         <v>11</v>
       </c>
       <c r="K186" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8312,7 +8364,7 @@
         <v>11</v>
       </c>
       <c r="D187" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E187" t="s">
         <v>11</v>
@@ -8333,7 +8385,7 @@
         <v>11</v>
       </c>
       <c r="K187" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8347,7 +8399,7 @@
         <v>11</v>
       </c>
       <c r="D188" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E188" t="s">
         <v>11</v>
@@ -8368,7 +8420,7 @@
         <v>11</v>
       </c>
       <c r="K188" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -8382,7 +8434,7 @@
         <v>11</v>
       </c>
       <c r="D189" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E189" t="s">
         <v>11</v>
@@ -8403,7 +8455,7 @@
         <v>11</v>
       </c>
       <c r="K189" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8417,7 +8469,7 @@
         <v>11</v>
       </c>
       <c r="D190" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E190" t="s">
         <v>11</v>
@@ -8438,7 +8490,7 @@
         <v>11</v>
       </c>
       <c r="K190" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8452,7 +8504,7 @@
         <v>11</v>
       </c>
       <c r="D191" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E191" t="s">
         <v>11</v>
@@ -8473,7 +8525,7 @@
         <v>11</v>
       </c>
       <c r="K191" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8487,7 +8539,7 @@
         <v>11</v>
       </c>
       <c r="D192" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E192" t="s">
         <v>11</v>
@@ -8508,7 +8560,7 @@
         <v>11</v>
       </c>
       <c r="K192" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8522,7 +8574,7 @@
         <v>11</v>
       </c>
       <c r="D193" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E193" t="s">
         <v>11</v>
@@ -8543,7 +8595,7 @@
         <v>11</v>
       </c>
       <c r="K193" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8557,7 +8609,7 @@
         <v>11</v>
       </c>
       <c r="D194" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E194" t="s">
         <v>11</v>
@@ -8578,7 +8630,7 @@
         <v>11</v>
       </c>
       <c r="K194" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -8592,7 +8644,7 @@
         <v>11</v>
       </c>
       <c r="D195" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E195" t="s">
         <v>11</v>
@@ -8613,7 +8665,7 @@
         <v>11</v>
       </c>
       <c r="K195" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -8627,7 +8679,7 @@
         <v>11</v>
       </c>
       <c r="D196" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E196" t="s">
         <v>11</v>
@@ -8648,7 +8700,7 @@
         <v>11</v>
       </c>
       <c r="K196" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -8662,7 +8714,7 @@
         <v>11</v>
       </c>
       <c r="D197" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E197" t="s">
         <v>11</v>
@@ -8683,7 +8735,7 @@
         <v>11</v>
       </c>
       <c r="K197" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -8697,7 +8749,7 @@
         <v>11</v>
       </c>
       <c r="D198" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E198" t="s">
         <v>11</v>
@@ -8718,7 +8770,7 @@
         <v>11</v>
       </c>
       <c r="K198" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -8732,7 +8784,7 @@
         <v>11</v>
       </c>
       <c r="D199" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E199" t="s">
         <v>11</v>
@@ -8753,7 +8805,7 @@
         <v>11</v>
       </c>
       <c r="K199" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -8767,7 +8819,7 @@
         <v>11</v>
       </c>
       <c r="D200" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E200" t="s">
         <v>11</v>
@@ -8788,7 +8840,7 @@
         <v>11</v>
       </c>
       <c r="K200" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -8802,7 +8854,7 @@
         <v>11</v>
       </c>
       <c r="D201" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E201" t="s">
         <v>11</v>
@@ -8823,7 +8875,7 @@
         <v>11</v>
       </c>
       <c r="K201" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -8837,7 +8889,7 @@
         <v>11</v>
       </c>
       <c r="D202" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E202" t="s">
         <v>11</v>
@@ -8858,7 +8910,7 @@
         <v>11</v>
       </c>
       <c r="K202" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -8872,7 +8924,7 @@
         <v>11</v>
       </c>
       <c r="D203" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E203" t="s">
         <v>11</v>
@@ -8893,7 +8945,7 @@
         <v>11</v>
       </c>
       <c r="K203" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -8907,7 +8959,7 @@
         <v>11</v>
       </c>
       <c r="D204" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E204" t="s">
         <v>11</v>
@@ -8928,7 +8980,7 @@
         <v>11</v>
       </c>
       <c r="K204" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -8942,7 +8994,7 @@
         <v>11</v>
       </c>
       <c r="D205" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E205" t="s">
         <v>11</v>
@@ -8963,7 +9015,7 @@
         <v>11</v>
       </c>
       <c r="K205" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -8977,7 +9029,7 @@
         <v>11</v>
       </c>
       <c r="D206" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E206" t="s">
         <v>11</v>
@@ -8998,7 +9050,7 @@
         <v>11</v>
       </c>
       <c r="K206" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9012,7 +9064,7 @@
         <v>11</v>
       </c>
       <c r="D207" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E207" t="s">
         <v>11</v>
@@ -9033,7 +9085,7 @@
         <v>11</v>
       </c>
       <c r="K207" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9047,7 +9099,7 @@
         <v>11</v>
       </c>
       <c r="D208" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E208" t="s">
         <v>11</v>
@@ -9068,7 +9120,7 @@
         <v>11</v>
       </c>
       <c r="K208" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9082,7 +9134,7 @@
         <v>11</v>
       </c>
       <c r="D209" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E209" t="s">
         <v>11</v>
@@ -9103,7 +9155,7 @@
         <v>11</v>
       </c>
       <c r="K209" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9117,7 +9169,7 @@
         <v>11</v>
       </c>
       <c r="D210" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E210" t="s">
         <v>11</v>
@@ -9138,7 +9190,7 @@
         <v>11</v>
       </c>
       <c r="K210" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9152,7 +9204,7 @@
         <v>11</v>
       </c>
       <c r="D211" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E211" t="s">
         <v>11</v>
@@ -9173,7 +9225,7 @@
         <v>11</v>
       </c>
       <c r="K211" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9187,7 +9239,7 @@
         <v>11</v>
       </c>
       <c r="D212" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E212" t="s">
         <v>11</v>
@@ -9208,7 +9260,7 @@
         <v>11</v>
       </c>
       <c r="K212" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9222,7 +9274,7 @@
         <v>11</v>
       </c>
       <c r="D213" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E213" t="s">
         <v>11</v>
@@ -9243,7 +9295,7 @@
         <v>11</v>
       </c>
       <c r="K213" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9257,7 +9309,7 @@
         <v>11</v>
       </c>
       <c r="D214" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E214" t="s">
         <v>11</v>
@@ -9278,7 +9330,7 @@
         <v>11</v>
       </c>
       <c r="K214" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9292,7 +9344,7 @@
         <v>11</v>
       </c>
       <c r="D215" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E215" t="s">
         <v>11</v>
@@ -9313,7 +9365,7 @@
         <v>11</v>
       </c>
       <c r="K215" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9327,7 +9379,7 @@
         <v>11</v>
       </c>
       <c r="D216" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E216" t="s">
         <v>11</v>
@@ -9348,7 +9400,7 @@
         <v>11</v>
       </c>
       <c r="K216" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9362,7 +9414,7 @@
         <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E217" t="s">
         <v>11</v>
@@ -9383,7 +9435,7 @@
         <v>11</v>
       </c>
       <c r="K217" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9397,7 +9449,7 @@
         <v>11</v>
       </c>
       <c r="D218" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E218" t="s">
         <v>11</v>
@@ -9418,7 +9470,7 @@
         <v>11</v>
       </c>
       <c r="K218" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9432,7 +9484,7 @@
         <v>11</v>
       </c>
       <c r="D219" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E219" t="s">
         <v>11</v>
@@ -9453,7 +9505,7 @@
         <v>11</v>
       </c>
       <c r="K219" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -9467,7 +9519,7 @@
         <v>11</v>
       </c>
       <c r="D220" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E220" t="s">
         <v>11</v>
@@ -9488,7 +9540,7 @@
         <v>11</v>
       </c>
       <c r="K220" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -9502,7 +9554,7 @@
         <v>11</v>
       </c>
       <c r="D221" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E221" t="s">
         <v>11</v>
@@ -9523,7 +9575,7 @@
         <v>11</v>
       </c>
       <c r="K221" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -9537,7 +9589,7 @@
         <v>11</v>
       </c>
       <c r="D222" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E222" t="s">
         <v>11</v>
@@ -9558,7 +9610,7 @@
         <v>11</v>
       </c>
       <c r="K222" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -9572,7 +9624,7 @@
         <v>11</v>
       </c>
       <c r="D223" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E223" t="s">
         <v>11</v>
@@ -9593,7 +9645,7 @@
         <v>11</v>
       </c>
       <c r="K223" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -9607,7 +9659,7 @@
         <v>11</v>
       </c>
       <c r="D224" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E224" t="s">
         <v>11</v>
@@ -9628,7 +9680,7 @@
         <v>11</v>
       </c>
       <c r="K224" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -9642,7 +9694,7 @@
         <v>11</v>
       </c>
       <c r="D225" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E225" t="s">
         <v>11</v>
@@ -9663,7 +9715,7 @@
         <v>11</v>
       </c>
       <c r="K225" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -9677,7 +9729,7 @@
         <v>11</v>
       </c>
       <c r="D226" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E226" t="s">
         <v>11</v>
@@ -9698,7 +9750,7 @@
         <v>11</v>
       </c>
       <c r="K226" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -9712,7 +9764,7 @@
         <v>11</v>
       </c>
       <c r="D227" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E227" t="s">
         <v>11</v>
@@ -9733,7 +9785,7 @@
         <v>11</v>
       </c>
       <c r="K227" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -9747,7 +9799,7 @@
         <v>11</v>
       </c>
       <c r="D228" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E228" t="s">
         <v>11</v>
@@ -9768,7 +9820,7 @@
         <v>11</v>
       </c>
       <c r="K228" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -9782,7 +9834,7 @@
         <v>11</v>
       </c>
       <c r="D229" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E229" t="s">
         <v>11</v>
@@ -9803,7 +9855,7 @@
         <v>11</v>
       </c>
       <c r="K229" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
@@ -9817,7 +9869,7 @@
         <v>11</v>
       </c>
       <c r="D230" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E230" t="s">
         <v>11</v>
@@ -9838,7 +9890,7 @@
         <v>11</v>
       </c>
       <c r="K230" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
@@ -9852,7 +9904,7 @@
         <v>11</v>
       </c>
       <c r="D231" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E231" t="s">
         <v>11</v>
@@ -9873,7 +9925,7 @@
         <v>11</v>
       </c>
       <c r="K231" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -9887,7 +9939,7 @@
         <v>11</v>
       </c>
       <c r="D232" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E232" t="s">
         <v>11</v>
@@ -9908,7 +9960,7 @@
         <v>11</v>
       </c>
       <c r="K232" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -9922,7 +9974,7 @@
         <v>11</v>
       </c>
       <c r="D233" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E233" t="s">
         <v>11</v>
@@ -9943,7 +9995,7 @@
         <v>11</v>
       </c>
       <c r="K233" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -9957,7 +10009,7 @@
         <v>11</v>
       </c>
       <c r="D234" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E234" t="s">
         <v>11</v>
@@ -9978,7 +10030,7 @@
         <v>11</v>
       </c>
       <c r="K234" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -9992,7 +10044,7 @@
         <v>11</v>
       </c>
       <c r="D235" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E235" t="s">
         <v>11</v>
@@ -10013,7 +10065,7 @@
         <v>11</v>
       </c>
       <c r="K235" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -10027,7 +10079,7 @@
         <v>11</v>
       </c>
       <c r="D236" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E236" t="s">
         <v>11</v>
@@ -10048,7 +10100,7 @@
         <v>11</v>
       </c>
       <c r="K236" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -10062,7 +10114,7 @@
         <v>11</v>
       </c>
       <c r="D237" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E237" t="s">
         <v>11</v>
@@ -10083,7 +10135,7 @@
         <v>11</v>
       </c>
       <c r="K237" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10097,7 +10149,7 @@
         <v>11</v>
       </c>
       <c r="D238" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E238" t="s">
         <v>11</v>
@@ -10118,7 +10170,7 @@
         <v>11</v>
       </c>
       <c r="K238" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -10132,7 +10184,7 @@
         <v>11</v>
       </c>
       <c r="D239" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E239" t="s">
         <v>11</v>
@@ -10153,7 +10205,7 @@
         <v>11</v>
       </c>
       <c r="K239" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
@@ -10167,7 +10219,7 @@
         <v>11</v>
       </c>
       <c r="D240" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -10188,7 +10240,7 @@
         <v>11</v>
       </c>
       <c r="K240" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -10202,7 +10254,7 @@
         <v>11</v>
       </c>
       <c r="D241" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E241" t="s">
         <v>11</v>
@@ -10223,7 +10275,7 @@
         <v>11</v>
       </c>
       <c r="K241" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10237,7 +10289,7 @@
         <v>11</v>
       </c>
       <c r="D242" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E242" t="s">
         <v>11</v>
@@ -10258,7 +10310,7 @@
         <v>11</v>
       </c>
       <c r="K242" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10272,7 +10324,7 @@
         <v>11</v>
       </c>
       <c r="D243" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E243" t="s">
         <v>11</v>
@@ -10293,7 +10345,7 @@
         <v>11</v>
       </c>
       <c r="K243" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10307,7 +10359,7 @@
         <v>11</v>
       </c>
       <c r="D244" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E244" t="s">
         <v>11</v>
@@ -10328,7 +10380,7 @@
         <v>11</v>
       </c>
       <c r="K244" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10342,7 +10394,7 @@
         <v>11</v>
       </c>
       <c r="D245" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E245" t="s">
         <v>11</v>
@@ -10363,7 +10415,7 @@
         <v>11</v>
       </c>
       <c r="K245" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10377,7 +10429,7 @@
         <v>11</v>
       </c>
       <c r="D246" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E246" t="s">
         <v>11</v>
@@ -10398,7 +10450,7 @@
         <v>11</v>
       </c>
       <c r="K246" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10412,7 +10464,7 @@
         <v>11</v>
       </c>
       <c r="D247" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E247" t="s">
         <v>11</v>
@@ -10433,7 +10485,7 @@
         <v>11</v>
       </c>
       <c r="K247" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10447,7 +10499,7 @@
         <v>11</v>
       </c>
       <c r="D248" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E248" t="s">
         <v>11</v>
@@ -10468,7 +10520,7 @@
         <v>11</v>
       </c>
       <c r="K248" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10482,7 +10534,7 @@
         <v>11</v>
       </c>
       <c r="D249" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E249" t="s">
         <v>11</v>
@@ -10503,7 +10555,7 @@
         <v>11</v>
       </c>
       <c r="K249" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10517,7 +10569,7 @@
         <v>11</v>
       </c>
       <c r="D250" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E250" t="s">
         <v>11</v>
@@ -10538,7 +10590,7 @@
         <v>11</v>
       </c>
       <c r="K250" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10552,7 +10604,7 @@
         <v>11</v>
       </c>
       <c r="D251" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E251" t="s">
         <v>11</v>
@@ -10573,7 +10625,7 @@
         <v>11</v>
       </c>
       <c r="K251" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10587,7 +10639,7 @@
         <v>11</v>
       </c>
       <c r="D252" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E252" t="s">
         <v>11</v>
@@ -10608,7 +10660,7 @@
         <v>11</v>
       </c>
       <c r="K252" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10622,7 +10674,7 @@
         <v>11</v>
       </c>
       <c r="D253" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E253" t="s">
         <v>11</v>
@@ -10643,7 +10695,7 @@
         <v>11</v>
       </c>
       <c r="K253" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10657,7 +10709,7 @@
         <v>11</v>
       </c>
       <c r="D254" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E254" t="s">
         <v>11</v>
@@ -10678,7 +10730,7 @@
         <v>11</v>
       </c>
       <c r="K254" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10692,7 +10744,7 @@
         <v>11</v>
       </c>
       <c r="D255" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E255" t="s">
         <v>11</v>
@@ -10713,7 +10765,7 @@
         <v>11</v>
       </c>
       <c r="K255" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -10727,7 +10779,7 @@
         <v>11</v>
       </c>
       <c r="D256" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E256" t="s">
         <v>11</v>
@@ -10748,7 +10800,7 @@
         <v>11</v>
       </c>
       <c r="K256" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -10762,7 +10814,7 @@
         <v>11</v>
       </c>
       <c r="D257" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E257" t="s">
         <v>11</v>
@@ -10783,7 +10835,7 @@
         <v>11</v>
       </c>
       <c r="K257" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -10797,7 +10849,7 @@
         <v>11</v>
       </c>
       <c r="D258" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E258" t="s">
         <v>11</v>
@@ -10818,7 +10870,7 @@
         <v>11</v>
       </c>
       <c r="K258" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -10832,7 +10884,7 @@
         <v>11</v>
       </c>
       <c r="D259" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E259" t="s">
         <v>11</v>
@@ -10853,7 +10905,7 @@
         <v>11</v>
       </c>
       <c r="K259" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -10867,7 +10919,7 @@
         <v>11</v>
       </c>
       <c r="D260" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E260" t="s">
         <v>11</v>
@@ -10888,7 +10940,7 @@
         <v>11</v>
       </c>
       <c r="K260" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -10902,7 +10954,7 @@
         <v>11</v>
       </c>
       <c r="D261" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E261" t="s">
         <v>11</v>
@@ -10923,7 +10975,7 @@
         <v>11</v>
       </c>
       <c r="K261" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -10937,7 +10989,7 @@
         <v>11</v>
       </c>
       <c r="D262" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E262" t="s">
         <v>11</v>
@@ -10958,7 +11010,7 @@
         <v>11</v>
       </c>
       <c r="K262" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -10972,7 +11024,7 @@
         <v>11</v>
       </c>
       <c r="D263" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E263" t="s">
         <v>11</v>
@@ -10993,7 +11045,7 @@
         <v>11</v>
       </c>
       <c r="K263" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -11007,7 +11059,7 @@
         <v>11</v>
       </c>
       <c r="D264" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E264" t="s">
         <v>11</v>
@@ -11028,7 +11080,7 @@
         <v>11</v>
       </c>
       <c r="K264" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -11042,7 +11094,7 @@
         <v>11</v>
       </c>
       <c r="D265" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
@@ -11063,7 +11115,7 @@
         <v>11</v>
       </c>
       <c r="K265" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -11077,7 +11129,7 @@
         <v>11</v>
       </c>
       <c r="D266" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E266" t="s">
         <v>11</v>
@@ -11098,7 +11150,7 @@
         <v>11</v>
       </c>
       <c r="K266" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -11112,7 +11164,7 @@
         <v>11</v>
       </c>
       <c r="D267" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E267" t="s">
         <v>11</v>
@@ -11133,7 +11185,7 @@
         <v>11</v>
       </c>
       <c r="K267" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
@@ -11147,7 +11199,7 @@
         <v>11</v>
       </c>
       <c r="D268" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E268" t="s">
         <v>11</v>
@@ -11168,7 +11220,7 @@
         <v>11</v>
       </c>
       <c r="K268" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -11182,7 +11234,7 @@
         <v>11</v>
       </c>
       <c r="D269" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E269" t="s">
         <v>11</v>
@@ -11203,7 +11255,7 @@
         <v>11</v>
       </c>
       <c r="K269" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -11217,7 +11269,7 @@
         <v>11</v>
       </c>
       <c r="D270" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E270" t="s">
         <v>11</v>
@@ -11238,7 +11290,7 @@
         <v>11</v>
       </c>
       <c r="K270" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -11252,7 +11304,7 @@
         <v>11</v>
       </c>
       <c r="D271" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E271" t="s">
         <v>11</v>
@@ -11273,7 +11325,7 @@
         <v>11</v>
       </c>
       <c r="K271" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
@@ -11287,7 +11339,7 @@
         <v>11</v>
       </c>
       <c r="D272" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E272" t="s">
         <v>11</v>
@@ -11308,7 +11360,7 @@
         <v>11</v>
       </c>
       <c r="K272" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
@@ -11322,7 +11374,7 @@
         <v>11</v>
       </c>
       <c r="D273" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E273" t="s">
         <v>11</v>
@@ -11343,7 +11395,7 @@
         <v>11</v>
       </c>
       <c r="K273" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
@@ -11357,7 +11409,7 @@
         <v>11</v>
       </c>
       <c r="D274" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E274" t="s">
         <v>11</v>
@@ -11378,7 +11430,7 @@
         <v>11</v>
       </c>
       <c r="K274" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
@@ -11392,7 +11444,7 @@
         <v>11</v>
       </c>
       <c r="D275" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E275" t="s">
         <v>11</v>
@@ -11413,7 +11465,7 @@
         <v>11</v>
       </c>
       <c r="K275" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -11427,7 +11479,7 @@
         <v>11</v>
       </c>
       <c r="D276" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E276" t="s">
         <v>11</v>
@@ -11448,7 +11500,7 @@
         <v>11</v>
       </c>
       <c r="K276" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -11462,7 +11514,7 @@
         <v>11</v>
       </c>
       <c r="D277" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E277" t="s">
         <v>11</v>
@@ -11483,7 +11535,7 @@
         <v>11</v>
       </c>
       <c r="K277" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -11497,7 +11549,7 @@
         <v>11</v>
       </c>
       <c r="D278" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E278" t="s">
         <v>11</v>
@@ -11518,7 +11570,7 @@
         <v>11</v>
       </c>
       <c r="K278" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -11532,7 +11584,7 @@
         <v>11</v>
       </c>
       <c r="D279" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E279" t="s">
         <v>11</v>
@@ -11553,7 +11605,7 @@
         <v>11</v>
       </c>
       <c r="K279" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11567,7 +11619,7 @@
         <v>11</v>
       </c>
       <c r="D280" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
@@ -11588,7 +11640,7 @@
         <v>11</v>
       </c>
       <c r="K280" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11602,7 +11654,7 @@
         <v>11</v>
       </c>
       <c r="D281" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E281" t="s">
         <v>11</v>
@@ -11623,7 +11675,7 @@
         <v>11</v>
       </c>
       <c r="K281" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11637,7 +11689,7 @@
         <v>11</v>
       </c>
       <c r="D282" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E282" t="s">
         <v>11</v>
@@ -11658,7 +11710,7 @@
         <v>11</v>
       </c>
       <c r="K282" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11672,7 +11724,7 @@
         <v>11</v>
       </c>
       <c r="D283" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E283" t="s">
         <v>11</v>
@@ -11693,7 +11745,7 @@
         <v>11</v>
       </c>
       <c r="K283" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11707,7 +11759,7 @@
         <v>11</v>
       </c>
       <c r="D284" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E284" t="s">
         <v>11</v>
@@ -11728,7 +11780,7 @@
         <v>11</v>
       </c>
       <c r="K284" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11742,7 +11794,7 @@
         <v>11</v>
       </c>
       <c r="D285" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E285" t="s">
         <v>11</v>
@@ -11763,7 +11815,7 @@
         <v>11</v>
       </c>
       <c r="K285" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -11777,7 +11829,7 @@
         <v>11</v>
       </c>
       <c r="D286" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E286" t="s">
         <v>11</v>
@@ -11798,7 +11850,7 @@
         <v>11</v>
       </c>
       <c r="K286" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -11812,7 +11864,7 @@
         <v>11</v>
       </c>
       <c r="D287" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E287" t="s">
         <v>11</v>
@@ -11833,7 +11885,7 @@
         <v>11</v>
       </c>
       <c r="K287" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -11847,7 +11899,7 @@
         <v>11</v>
       </c>
       <c r="D288" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E288" t="s">
         <v>11</v>
@@ -11868,7 +11920,7 @@
         <v>11</v>
       </c>
       <c r="K288" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -11882,7 +11934,7 @@
         <v>11</v>
       </c>
       <c r="D289" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E289" t="s">
         <v>11</v>
@@ -11903,7 +11955,7 @@
         <v>11</v>
       </c>
       <c r="K289" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -11917,7 +11969,7 @@
         <v>11</v>
       </c>
       <c r="D290" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E290" t="s">
         <v>11</v>
@@ -11938,7 +11990,7 @@
         <v>11</v>
       </c>
       <c r="K290" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -11952,7 +12004,7 @@
         <v>11</v>
       </c>
       <c r="D291" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E291" t="s">
         <v>11</v>
@@ -11973,7 +12025,7 @@
         <v>11</v>
       </c>
       <c r="K291" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -11987,7 +12039,7 @@
         <v>11</v>
       </c>
       <c r="D292" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E292" t="s">
         <v>11</v>
@@ -12008,7 +12060,7 @@
         <v>11</v>
       </c>
       <c r="K292" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12022,7 +12074,7 @@
         <v>11</v>
       </c>
       <c r="D293" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E293" t="s">
         <v>11</v>
@@ -12043,7 +12095,7 @@
         <v>11</v>
       </c>
       <c r="K293" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12057,7 +12109,7 @@
         <v>11</v>
       </c>
       <c r="D294" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E294" t="s">
         <v>11</v>
@@ -12078,7 +12130,7 @@
         <v>11</v>
       </c>
       <c r="K294" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12092,7 +12144,7 @@
         <v>11</v>
       </c>
       <c r="D295" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E295" t="s">
         <v>11</v>
@@ -12113,7 +12165,7 @@
         <v>11</v>
       </c>
       <c r="K295" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12127,7 +12179,7 @@
         <v>11</v>
       </c>
       <c r="D296" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E296" t="s">
         <v>11</v>
@@ -12148,7 +12200,7 @@
         <v>11</v>
       </c>
       <c r="K296" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12162,7 +12214,7 @@
         <v>11</v>
       </c>
       <c r="D297" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E297" t="s">
         <v>11</v>
@@ -12183,7 +12235,7 @@
         <v>11</v>
       </c>
       <c r="K297" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12197,7 +12249,7 @@
         <v>11</v>
       </c>
       <c r="D298" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E298" t="s">
         <v>11</v>
@@ -12218,7 +12270,7 @@
         <v>11</v>
       </c>
       <c r="K298" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12232,7 +12284,7 @@
         <v>11</v>
       </c>
       <c r="D299" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E299" t="s">
         <v>11</v>
@@ -12253,7 +12305,7 @@
         <v>11</v>
       </c>
       <c r="K299" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12267,7 +12319,7 @@
         <v>11</v>
       </c>
       <c r="D300" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E300" t="s">
         <v>11</v>
@@ -12288,7 +12340,7 @@
         <v>11</v>
       </c>
       <c r="K300" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12302,7 +12354,7 @@
         <v>11</v>
       </c>
       <c r="D301" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E301" t="s">
         <v>11</v>
@@ -12323,7 +12375,7 @@
         <v>11</v>
       </c>
       <c r="K301" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12337,7 +12389,7 @@
         <v>11</v>
       </c>
       <c r="D302" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E302" t="s">
         <v>11</v>
@@ -12358,7 +12410,7 @@
         <v>11</v>
       </c>
       <c r="K302" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -12372,7 +12424,7 @@
         <v>11</v>
       </c>
       <c r="D303" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E303" t="s">
         <v>11</v>
@@ -12393,7 +12445,7 @@
         <v>11</v>
       </c>
       <c r="K303" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -12407,7 +12459,7 @@
         <v>11</v>
       </c>
       <c r="D304" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E304" t="s">
         <v>11</v>
@@ -12428,7 +12480,7 @@
         <v>11</v>
       </c>
       <c r="K304" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -12442,7 +12494,7 @@
         <v>11</v>
       </c>
       <c r="D305" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E305" t="s">
         <v>11</v>
@@ -12463,7 +12515,7 @@
         <v>11</v>
       </c>
       <c r="K305" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12477,7 +12529,7 @@
         <v>11</v>
       </c>
       <c r="D306" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E306" t="s">
         <v>11</v>
@@ -12498,7 +12550,7 @@
         <v>11</v>
       </c>
       <c r="K306" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12512,7 +12564,7 @@
         <v>11</v>
       </c>
       <c r="D307" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E307" t="s">
         <v>11</v>
@@ -12533,7 +12585,7 @@
         <v>11</v>
       </c>
       <c r="K307" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
@@ -12547,7 +12599,7 @@
         <v>11</v>
       </c>
       <c r="D308" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E308" t="s">
         <v>11</v>
@@ -12568,7 +12620,7 @@
         <v>11</v>
       </c>
       <c r="K308" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
@@ -12582,7 +12634,7 @@
         <v>11</v>
       </c>
       <c r="D309" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E309" t="s">
         <v>11</v>
@@ -12603,7 +12655,7 @@
         <v>11</v>
       </c>
       <c r="K309" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
@@ -12617,7 +12669,7 @@
         <v>11</v>
       </c>
       <c r="D310" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E310" t="s">
         <v>11</v>
@@ -12638,7 +12690,7 @@
         <v>11</v>
       </c>
       <c r="K310" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
@@ -12652,7 +12704,7 @@
         <v>11</v>
       </c>
       <c r="D311" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E311" t="s">
         <v>11</v>
@@ -12673,7 +12725,7 @@
         <v>11</v>
       </c>
       <c r="K311" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
@@ -12687,7 +12739,7 @@
         <v>11</v>
       </c>
       <c r="D312" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E312" t="s">
         <v>11</v>
@@ -12708,7 +12760,7 @@
         <v>11</v>
       </c>
       <c r="K312" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
@@ -12722,7 +12774,7 @@
         <v>11</v>
       </c>
       <c r="D313" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E313" t="s">
         <v>11</v>
@@ -12743,7 +12795,7 @@
         <v>11</v>
       </c>
       <c r="K313" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
@@ -12757,7 +12809,7 @@
         <v>11</v>
       </c>
       <c r="D314" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E314" t="s">
         <v>11</v>
@@ -12778,7 +12830,7 @@
         <v>11</v>
       </c>
       <c r="K314" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
@@ -12792,7 +12844,7 @@
         <v>11</v>
       </c>
       <c r="D315" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E315" t="s">
         <v>11</v>
@@ -12813,7 +12865,7 @@
         <v>11</v>
       </c>
       <c r="K315" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
@@ -12827,7 +12879,7 @@
         <v>11</v>
       </c>
       <c r="D316" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E316" t="s">
         <v>11</v>
@@ -12848,7 +12900,7 @@
         <v>11</v>
       </c>
       <c r="K316" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
@@ -12862,7 +12914,7 @@
         <v>11</v>
       </c>
       <c r="D317" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E317" t="s">
         <v>11</v>
@@ -12883,7 +12935,7 @@
         <v>11</v>
       </c>
       <c r="K317" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
@@ -12897,7 +12949,7 @@
         <v>11</v>
       </c>
       <c r="D318" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E318" t="s">
         <v>11</v>
@@ -12918,7 +12970,7 @@
         <v>11</v>
       </c>
       <c r="K318" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
@@ -12932,7 +12984,7 @@
         <v>11</v>
       </c>
       <c r="D319" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E319" t="s">
         <v>11</v>
@@ -12953,7 +13005,7 @@
         <v>11</v>
       </c>
       <c r="K319" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
@@ -12967,7 +13019,7 @@
         <v>11</v>
       </c>
       <c r="D320" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E320" t="s">
         <v>11</v>
@@ -12988,7 +13040,7 @@
         <v>11</v>
       </c>
       <c r="K320" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
@@ -13002,7 +13054,7 @@
         <v>11</v>
       </c>
       <c r="D321" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E321" t="s">
         <v>11</v>
@@ -13023,7 +13075,7 @@
         <v>11</v>
       </c>
       <c r="K321" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
@@ -13037,7 +13089,7 @@
         <v>11</v>
       </c>
       <c r="D322" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E322" t="s">
         <v>11</v>
@@ -13058,7 +13110,7 @@
         <v>11</v>
       </c>
       <c r="K322" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
@@ -13072,7 +13124,7 @@
         <v>11</v>
       </c>
       <c r="D323" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E323" t="s">
         <v>11</v>
@@ -13093,7 +13145,7 @@
         <v>11</v>
       </c>
       <c r="K323" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
@@ -13107,7 +13159,7 @@
         <v>11</v>
       </c>
       <c r="D324" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E324" t="s">
         <v>11</v>
@@ -13128,7 +13180,7 @@
         <v>11</v>
       </c>
       <c r="K324" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
@@ -13142,7 +13194,7 @@
         <v>11</v>
       </c>
       <c r="D325" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E325" t="s">
         <v>11</v>
@@ -13163,7 +13215,7 @@
         <v>11</v>
       </c>
       <c r="K325" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
@@ -13177,7 +13229,7 @@
         <v>11</v>
       </c>
       <c r="D326" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E326" t="s">
         <v>11</v>
@@ -13198,7 +13250,7 @@
         <v>11</v>
       </c>
       <c r="K326" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
@@ -13212,7 +13264,7 @@
         <v>11</v>
       </c>
       <c r="D327" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E327" t="s">
         <v>11</v>
@@ -13233,7 +13285,7 @@
         <v>11</v>
       </c>
       <c r="K327" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -13247,7 +13299,7 @@
         <v>11</v>
       </c>
       <c r="D328" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E328" t="s">
         <v>11</v>
@@ -13268,7 +13320,7 @@
         <v>11</v>
       </c>
       <c r="K328" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
@@ -13282,7 +13334,7 @@
         <v>11</v>
       </c>
       <c r="D329" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E329" t="s">
         <v>11</v>
@@ -13303,7 +13355,7 @@
         <v>11</v>
       </c>
       <c r="K329" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
@@ -13317,7 +13369,7 @@
         <v>11</v>
       </c>
       <c r="D330" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E330" t="s">
         <v>11</v>
@@ -13338,7 +13390,7 @@
         <v>11</v>
       </c>
       <c r="K330" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
@@ -13352,7 +13404,7 @@
         <v>11</v>
       </c>
       <c r="D331" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E331" t="s">
         <v>11</v>
@@ -13373,7 +13425,7 @@
         <v>11</v>
       </c>
       <c r="K331" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
@@ -13387,7 +13439,7 @@
         <v>11</v>
       </c>
       <c r="D332" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E332" t="s">
         <v>11</v>
@@ -13408,7 +13460,7 @@
         <v>11</v>
       </c>
       <c r="K332" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
@@ -13422,7 +13474,7 @@
         <v>11</v>
       </c>
       <c r="D333" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E333" t="s">
         <v>11</v>
@@ -13443,7 +13495,7 @@
         <v>11</v>
       </c>
       <c r="K333" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
@@ -13457,7 +13509,7 @@
         <v>11</v>
       </c>
       <c r="D334" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E334" t="s">
         <v>11</v>
@@ -13478,7 +13530,7 @@
         <v>11</v>
       </c>
       <c r="K334" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
@@ -13492,7 +13544,7 @@
         <v>11</v>
       </c>
       <c r="D335" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E335" t="s">
         <v>11</v>
@@ -13513,7 +13565,7 @@
         <v>11</v>
       </c>
       <c r="K335" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
@@ -13527,7 +13579,7 @@
         <v>11</v>
       </c>
       <c r="D336" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E336" t="s">
         <v>11</v>
@@ -13548,7 +13600,7 @@
         <v>11</v>
       </c>
       <c r="K336" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
@@ -13562,7 +13614,7 @@
         <v>11</v>
       </c>
       <c r="D337" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E337" t="s">
         <v>11</v>
@@ -13583,7 +13635,7 @@
         <v>11</v>
       </c>
       <c r="K337" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
@@ -13597,7 +13649,7 @@
         <v>11</v>
       </c>
       <c r="D338" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E338" t="s">
         <v>11</v>
@@ -13618,7 +13670,7 @@
         <v>11</v>
       </c>
       <c r="K338" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
@@ -13632,7 +13684,7 @@
         <v>11</v>
       </c>
       <c r="D339" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E339" t="s">
         <v>11</v>
@@ -13653,7 +13705,7 @@
         <v>11</v>
       </c>
       <c r="K339" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
@@ -13667,7 +13719,7 @@
         <v>11</v>
       </c>
       <c r="D340" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E340" t="s">
         <v>11</v>
@@ -13688,7 +13740,7 @@
         <v>11</v>
       </c>
       <c r="K340" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
@@ -13702,7 +13754,7 @@
         <v>11</v>
       </c>
       <c r="D341" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E341" t="s">
         <v>11</v>
@@ -13723,7 +13775,7 @@
         <v>11</v>
       </c>
       <c r="K341" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
@@ -13737,7 +13789,7 @@
         <v>11</v>
       </c>
       <c r="D342" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E342" t="s">
         <v>11</v>
@@ -13758,7 +13810,7 @@
         <v>11</v>
       </c>
       <c r="K342" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
@@ -13772,7 +13824,7 @@
         <v>11</v>
       </c>
       <c r="D343" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E343" t="s">
         <v>11</v>
@@ -13793,7 +13845,7 @@
         <v>11</v>
       </c>
       <c r="K343" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
@@ -13807,7 +13859,7 @@
         <v>11</v>
       </c>
       <c r="D344" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E344" t="s">
         <v>11</v>
@@ -13828,7 +13880,7 @@
         <v>11</v>
       </c>
       <c r="K344" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
@@ -13842,7 +13894,7 @@
         <v>11</v>
       </c>
       <c r="D345" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E345" t="s">
         <v>11</v>
@@ -13863,7 +13915,7 @@
         <v>11</v>
       </c>
       <c r="K345" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -13877,7 +13929,7 @@
         <v>11</v>
       </c>
       <c r="D346" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E346" t="s">
         <v>11</v>
@@ -13898,7 +13950,7 @@
         <v>11</v>
       </c>
       <c r="K346" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
@@ -13912,7 +13964,7 @@
         <v>11</v>
       </c>
       <c r="D347" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E347" t="s">
         <v>11</v>
@@ -13933,7 +13985,7 @@
         <v>11</v>
       </c>
       <c r="K347" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
@@ -13947,7 +13999,7 @@
         <v>11</v>
       </c>
       <c r="D348" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E348" t="s">
         <v>11</v>
@@ -13968,7 +14020,7 @@
         <v>11</v>
       </c>
       <c r="K348" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
@@ -13982,7 +14034,7 @@
         <v>11</v>
       </c>
       <c r="D349" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E349" t="s">
         <v>11</v>
@@ -14003,7 +14055,7 @@
         <v>11</v>
       </c>
       <c r="K349" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
@@ -14017,7 +14069,7 @@
         <v>11</v>
       </c>
       <c r="D350" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E350" t="s">
         <v>11</v>
@@ -14038,7 +14090,7 @@
         <v>11</v>
       </c>
       <c r="K350" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
@@ -14052,7 +14104,7 @@
         <v>11</v>
       </c>
       <c r="D351" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E351" t="s">
         <v>11</v>
@@ -14073,7 +14125,7 @@
         <v>11</v>
       </c>
       <c r="K351" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
@@ -14087,7 +14139,7 @@
         <v>11</v>
       </c>
       <c r="D352" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E352" t="s">
         <v>11</v>
@@ -14108,7 +14160,7 @@
         <v>11</v>
       </c>
       <c r="K352" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
@@ -14122,7 +14174,7 @@
         <v>11</v>
       </c>
       <c r="D353" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E353" t="s">
         <v>11</v>
@@ -14143,7 +14195,7 @@
         <v>11</v>
       </c>
       <c r="K353" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
@@ -14157,7 +14209,7 @@
         <v>11</v>
       </c>
       <c r="D354" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E354" t="s">
         <v>11</v>
@@ -14178,7 +14230,7 @@
         <v>11</v>
       </c>
       <c r="K354" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -14192,7 +14244,7 @@
         <v>11</v>
       </c>
       <c r="D355" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E355" t="s">
         <v>11</v>
@@ -14213,7 +14265,7 @@
         <v>11</v>
       </c>
       <c r="K355" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
@@ -14227,7 +14279,7 @@
         <v>11</v>
       </c>
       <c r="D356" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E356" t="s">
         <v>11</v>
@@ -14248,7 +14300,7 @@
         <v>11</v>
       </c>
       <c r="K356" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
@@ -14262,7 +14314,7 @@
         <v>11</v>
       </c>
       <c r="D357" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E357" t="s">
         <v>11</v>
@@ -14283,7 +14335,7 @@
         <v>11</v>
       </c>
       <c r="K357" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
@@ -14297,7 +14349,7 @@
         <v>11</v>
       </c>
       <c r="D358" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E358" t="s">
         <v>11</v>
@@ -14318,7 +14370,7 @@
         <v>11</v>
       </c>
       <c r="K358" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.25">
@@ -14332,7 +14384,7 @@
         <v>11</v>
       </c>
       <c r="D359" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E359" t="s">
         <v>11</v>
@@ -14353,7 +14405,7 @@
         <v>11</v>
       </c>
       <c r="K359" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
@@ -14367,7 +14419,7 @@
         <v>11</v>
       </c>
       <c r="D360" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E360" t="s">
         <v>11</v>
@@ -14388,7 +14440,7 @@
         <v>11</v>
       </c>
       <c r="K360" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
@@ -14402,7 +14454,7 @@
         <v>11</v>
       </c>
       <c r="D361" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E361" t="s">
         <v>11</v>
@@ -14423,7 +14475,7 @@
         <v>11</v>
       </c>
       <c r="K361" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
@@ -14437,7 +14489,7 @@
         <v>11</v>
       </c>
       <c r="D362" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E362" t="s">
         <v>11</v>
@@ -14458,7 +14510,7 @@
         <v>11</v>
       </c>
       <c r="K362" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
@@ -14472,7 +14524,7 @@
         <v>11</v>
       </c>
       <c r="D363" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E363" t="s">
         <v>11</v>
@@ -14493,7 +14545,7 @@
         <v>11</v>
       </c>
       <c r="K363" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.25">
@@ -14507,7 +14559,7 @@
         <v>11</v>
       </c>
       <c r="D364" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E364" t="s">
         <v>11</v>
@@ -14528,7 +14580,7 @@
         <v>11</v>
       </c>
       <c r="K364" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
@@ -14542,7 +14594,7 @@
         <v>11</v>
       </c>
       <c r="D365" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E365" t="s">
         <v>11</v>
@@ -14563,7 +14615,7 @@
         <v>11</v>
       </c>
       <c r="K365" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
@@ -14577,7 +14629,7 @@
         <v>11</v>
       </c>
       <c r="D366" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E366" t="s">
         <v>11</v>
@@ -14598,7 +14650,7 @@
         <v>11</v>
       </c>
       <c r="K366" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
@@ -14612,7 +14664,7 @@
         <v>11</v>
       </c>
       <c r="D367" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E367" t="s">
         <v>11</v>
@@ -14633,7 +14685,7 @@
         <v>11</v>
       </c>
       <c r="K367" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
@@ -14647,7 +14699,7 @@
         <v>11</v>
       </c>
       <c r="D368" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E368" t="s">
         <v>11</v>
@@ -14668,7 +14720,7 @@
         <v>11</v>
       </c>
       <c r="K368" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
@@ -14682,7 +14734,7 @@
         <v>11</v>
       </c>
       <c r="D369" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E369" t="s">
         <v>11</v>
@@ -14703,7 +14755,7 @@
         <v>11</v>
       </c>
       <c r="K369" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.25">
@@ -14717,7 +14769,7 @@
         <v>11</v>
       </c>
       <c r="D370" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E370" t="s">
         <v>11</v>
@@ -14738,7 +14790,7 @@
         <v>11</v>
       </c>
       <c r="K370" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.25">
@@ -14752,7 +14804,7 @@
         <v>11</v>
       </c>
       <c r="D371" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E371" t="s">
         <v>11</v>
@@ -14773,7 +14825,7 @@
         <v>11</v>
       </c>
       <c r="K371" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
@@ -14787,7 +14839,7 @@
         <v>11</v>
       </c>
       <c r="D372" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E372" t="s">
         <v>11</v>
@@ -14808,7 +14860,7 @@
         <v>11</v>
       </c>
       <c r="K372" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
@@ -14822,7 +14874,7 @@
         <v>11</v>
       </c>
       <c r="D373" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E373" t="s">
         <v>11</v>
@@ -14843,7 +14895,7 @@
         <v>11</v>
       </c>
       <c r="K373" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
@@ -14857,7 +14909,7 @@
         <v>11</v>
       </c>
       <c r="D374" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E374" t="s">
         <v>11</v>
@@ -14878,7 +14930,7 @@
         <v>11</v>
       </c>
       <c r="K374" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
@@ -14892,7 +14944,7 @@
         <v>11</v>
       </c>
       <c r="D375" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E375" t="s">
         <v>11</v>
@@ -14913,7 +14965,7 @@
         <v>11</v>
       </c>
       <c r="K375" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
@@ -14927,7 +14979,7 @@
         <v>11</v>
       </c>
       <c r="D376" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E376" t="s">
         <v>11</v>
@@ -14948,7 +15000,7 @@
         <v>11</v>
       </c>
       <c r="K376" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
@@ -14962,7 +15014,7 @@
         <v>11</v>
       </c>
       <c r="D377" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E377" t="s">
         <v>11</v>
@@ -14983,7 +15035,7 @@
         <v>11</v>
       </c>
       <c r="K377" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
@@ -14997,7 +15049,7 @@
         <v>11</v>
       </c>
       <c r="D378" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E378" t="s">
         <v>11</v>
@@ -15018,7 +15070,7 @@
         <v>11</v>
       </c>
       <c r="K378" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
@@ -15032,7 +15084,7 @@
         <v>11</v>
       </c>
       <c r="D379" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E379" t="s">
         <v>11</v>
@@ -15053,7 +15105,7 @@
         <v>11</v>
       </c>
       <c r="K379" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.25">
@@ -15067,7 +15119,7 @@
         <v>11</v>
       </c>
       <c r="D380" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E380" t="s">
         <v>11</v>
@@ -15088,7 +15140,7 @@
         <v>11</v>
       </c>
       <c r="K380" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.25">
@@ -15102,7 +15154,7 @@
         <v>11</v>
       </c>
       <c r="D381" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E381" t="s">
         <v>11</v>
@@ -15123,7 +15175,7 @@
         <v>11</v>
       </c>
       <c r="K381" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.25">
@@ -15137,7 +15189,7 @@
         <v>11</v>
       </c>
       <c r="D382" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E382" t="s">
         <v>11</v>
@@ -15158,7 +15210,7 @@
         <v>11</v>
       </c>
       <c r="K382" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.25">
@@ -15172,7 +15224,7 @@
         <v>11</v>
       </c>
       <c r="D383" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E383" t="s">
         <v>11</v>
@@ -15193,7 +15245,7 @@
         <v>11</v>
       </c>
       <c r="K383" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
@@ -15207,7 +15259,7 @@
         <v>11</v>
       </c>
       <c r="D384" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E384" t="s">
         <v>11</v>
@@ -15228,7 +15280,7 @@
         <v>11</v>
       </c>
       <c r="K384" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.25">
@@ -15242,7 +15294,7 @@
         <v>11</v>
       </c>
       <c r="D385" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E385" t="s">
         <v>11</v>
@@ -15263,7 +15315,7 @@
         <v>11</v>
       </c>
       <c r="K385" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.25">
@@ -15277,7 +15329,7 @@
         <v>11</v>
       </c>
       <c r="D386" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E386" t="s">
         <v>11</v>
@@ -15298,7 +15350,7 @@
         <v>11</v>
       </c>
       <c r="K386" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.25">
@@ -15312,7 +15364,7 @@
         <v>11</v>
       </c>
       <c r="D387" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E387" t="s">
         <v>11</v>
@@ -15333,7 +15385,7 @@
         <v>11</v>
       </c>
       <c r="K387" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.25">
@@ -15347,7 +15399,7 @@
         <v>11</v>
       </c>
       <c r="D388" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E388" t="s">
         <v>11</v>
@@ -15368,7 +15420,7 @@
         <v>11</v>
       </c>
       <c r="K388" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.25">
@@ -15382,7 +15434,7 @@
         <v>11</v>
       </c>
       <c r="D389" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E389" t="s">
         <v>11</v>
@@ -15403,7 +15455,7 @@
         <v>11</v>
       </c>
       <c r="K389" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.25">
@@ -15417,7 +15469,7 @@
         <v>11</v>
       </c>
       <c r="D390" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E390" t="s">
         <v>11</v>
@@ -15438,7 +15490,7 @@
         <v>11</v>
       </c>
       <c r="K390" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.25">
@@ -15452,7 +15504,7 @@
         <v>11</v>
       </c>
       <c r="D391" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E391" t="s">
         <v>11</v>
@@ -15473,7 +15525,7 @@
         <v>11</v>
       </c>
       <c r="K391" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
@@ -15487,7 +15539,7 @@
         <v>11</v>
       </c>
       <c r="D392" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E392" t="s">
         <v>11</v>
@@ -15508,7 +15560,7 @@
         <v>11</v>
       </c>
       <c r="K392" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.25">
@@ -15522,7 +15574,7 @@
         <v>11</v>
       </c>
       <c r="D393" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E393" t="s">
         <v>11</v>
@@ -15543,7 +15595,7 @@
         <v>11</v>
       </c>
       <c r="K393" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
@@ -15557,7 +15609,7 @@
         <v>11</v>
       </c>
       <c r="D394" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E394" t="s">
         <v>11</v>
@@ -15578,7 +15630,7 @@
         <v>11</v>
       </c>
       <c r="K394" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
@@ -15592,7 +15644,7 @@
         <v>11</v>
       </c>
       <c r="D395" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E395" t="s">
         <v>11</v>
@@ -15613,7 +15665,7 @@
         <v>11</v>
       </c>
       <c r="K395" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.25">
@@ -15627,7 +15679,7 @@
         <v>11</v>
       </c>
       <c r="D396" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E396" t="s">
         <v>11</v>
@@ -15648,7 +15700,7 @@
         <v>11</v>
       </c>
       <c r="K396" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.25">
@@ -15662,7 +15714,7 @@
         <v>11</v>
       </c>
       <c r="D397" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E397" t="s">
         <v>11</v>
@@ -15683,7 +15735,7 @@
         <v>11</v>
       </c>
       <c r="K397" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
@@ -15697,7 +15749,7 @@
         <v>11</v>
       </c>
       <c r="D398" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E398" t="s">
         <v>11</v>
@@ -15718,7 +15770,7 @@
         <v>11</v>
       </c>
       <c r="K398" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
@@ -15732,7 +15784,7 @@
         <v>11</v>
       </c>
       <c r="D399" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E399" t="s">
         <v>11</v>
@@ -15753,7 +15805,7 @@
         <v>11</v>
       </c>
       <c r="K399" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.25">
@@ -15767,7 +15819,7 @@
         <v>11</v>
       </c>
       <c r="D400" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E400" t="s">
         <v>11</v>
@@ -15788,7 +15840,7 @@
         <v>11</v>
       </c>
       <c r="K400" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.25">
@@ -15802,7 +15854,7 @@
         <v>11</v>
       </c>
       <c r="D401" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E401" t="s">
         <v>11</v>
@@ -15823,7 +15875,7 @@
         <v>11</v>
       </c>
       <c r="K401" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.25">
@@ -15837,7 +15889,7 @@
         <v>11</v>
       </c>
       <c r="D402" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E402" t="s">
         <v>11</v>
@@ -15858,7 +15910,7 @@
         <v>11</v>
       </c>
       <c r="K402" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.25">
@@ -15872,7 +15924,7 @@
         <v>11</v>
       </c>
       <c r="D403" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E403" t="s">
         <v>11</v>
@@ -15893,7 +15945,7 @@
         <v>11</v>
       </c>
       <c r="K403" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.25">
@@ -15907,7 +15959,7 @@
         <v>11</v>
       </c>
       <c r="D404" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E404" t="s">
         <v>11</v>
@@ -15928,7 +15980,7 @@
         <v>11</v>
       </c>
       <c r="K404" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.25">
@@ -15942,7 +15994,7 @@
         <v>11</v>
       </c>
       <c r="D405" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E405" t="s">
         <v>11</v>
@@ -15963,7 +16015,7 @@
         <v>11</v>
       </c>
       <c r="K405" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
@@ -15977,7 +16029,7 @@
         <v>11</v>
       </c>
       <c r="D406" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E406" t="s">
         <v>11</v>
@@ -15998,7 +16050,7 @@
         <v>11</v>
       </c>
       <c r="K406" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.25">
@@ -16012,7 +16064,7 @@
         <v>11</v>
       </c>
       <c r="D407" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E407" t="s">
         <v>11</v>
@@ -16033,7 +16085,7 @@
         <v>11</v>
       </c>
       <c r="K407" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
@@ -16047,7 +16099,7 @@
         <v>11</v>
       </c>
       <c r="D408" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E408" t="s">
         <v>11</v>
@@ -16068,7 +16120,7 @@
         <v>11</v>
       </c>
       <c r="K408" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.25">
@@ -16082,7 +16134,7 @@
         <v>11</v>
       </c>
       <c r="D409" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E409" t="s">
         <v>11</v>
@@ -16103,7 +16155,7 @@
         <v>11</v>
       </c>
       <c r="K409" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.25">
@@ -16117,7 +16169,7 @@
         <v>11</v>
       </c>
       <c r="D410" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E410" t="s">
         <v>11</v>
@@ -16138,7 +16190,7 @@
         <v>11</v>
       </c>
       <c r="K410" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.25">
@@ -16152,7 +16204,7 @@
         <v>11</v>
       </c>
       <c r="D411" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E411" t="s">
         <v>11</v>
@@ -16173,7 +16225,7 @@
         <v>11</v>
       </c>
       <c r="K411" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.25">
@@ -16187,7 +16239,7 @@
         <v>11</v>
       </c>
       <c r="D412" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E412" t="s">
         <v>11</v>
@@ -16208,7 +16260,7 @@
         <v>11</v>
       </c>
       <c r="K412" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.25">
@@ -16222,7 +16274,7 @@
         <v>11</v>
       </c>
       <c r="D413" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E413" t="s">
         <v>11</v>
@@ -16243,7 +16295,7 @@
         <v>11</v>
       </c>
       <c r="K413" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.25">
@@ -16257,7 +16309,7 @@
         <v>11</v>
       </c>
       <c r="D414" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E414" t="s">
         <v>11</v>
@@ -16278,7 +16330,7 @@
         <v>11</v>
       </c>
       <c r="K414" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.25">
@@ -16292,7 +16344,7 @@
         <v>11</v>
       </c>
       <c r="D415" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E415" t="s">
         <v>11</v>
@@ -16313,7 +16365,7 @@
         <v>11</v>
       </c>
       <c r="K415" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.25">
@@ -16327,7 +16379,7 @@
         <v>11</v>
       </c>
       <c r="D416" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E416" t="s">
         <v>11</v>
@@ -16348,7 +16400,7 @@
         <v>11</v>
       </c>
       <c r="K416" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.25">
@@ -16362,7 +16414,7 @@
         <v>11</v>
       </c>
       <c r="D417" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E417" t="s">
         <v>11</v>
@@ -16383,7 +16435,7 @@
         <v>11</v>
       </c>
       <c r="K417" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.25">
@@ -16397,7 +16449,7 @@
         <v>11</v>
       </c>
       <c r="D418" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E418" t="s">
         <v>11</v>
@@ -16418,7 +16470,7 @@
         <v>11</v>
       </c>
       <c r="K418" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.25">
@@ -16432,7 +16484,7 @@
         <v>11</v>
       </c>
       <c r="D419" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E419" t="s">
         <v>11</v>
@@ -16453,7 +16505,7 @@
         <v>11</v>
       </c>
       <c r="K419" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.25">
@@ -16467,7 +16519,7 @@
         <v>11</v>
       </c>
       <c r="D420" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E420" t="s">
         <v>11</v>
@@ -16488,7 +16540,7 @@
         <v>11</v>
       </c>
       <c r="K420" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.25">
@@ -16502,7 +16554,7 @@
         <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E421" t="s">
         <v>11</v>
@@ -16523,7 +16575,7 @@
         <v>11</v>
       </c>
       <c r="K421" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.25">
@@ -16537,7 +16589,7 @@
         <v>11</v>
       </c>
       <c r="D422" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E422" t="s">
         <v>11</v>
@@ -16558,7 +16610,7 @@
         <v>11</v>
       </c>
       <c r="K422" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.25">
@@ -16572,7 +16624,7 @@
         <v>11</v>
       </c>
       <c r="D423" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E423" t="s">
         <v>11</v>
@@ -16593,7 +16645,7 @@
         <v>11</v>
       </c>
       <c r="K423" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.25">
@@ -16607,7 +16659,7 @@
         <v>11</v>
       </c>
       <c r="D424" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E424" t="s">
         <v>11</v>
@@ -16628,7 +16680,7 @@
         <v>11</v>
       </c>
       <c r="K424" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.25">
@@ -16642,7 +16694,7 @@
         <v>11</v>
       </c>
       <c r="D425" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E425" t="s">
         <v>11</v>
@@ -16663,7 +16715,7 @@
         <v>11</v>
       </c>
       <c r="K425" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.25">
@@ -16677,7 +16729,7 @@
         <v>11</v>
       </c>
       <c r="D426" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E426" t="s">
         <v>11</v>
@@ -16698,7 +16750,7 @@
         <v>11</v>
       </c>
       <c r="K426" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.25">
@@ -16712,7 +16764,7 @@
         <v>11</v>
       </c>
       <c r="D427" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E427" t="s">
         <v>11</v>
@@ -16733,7 +16785,7 @@
         <v>11</v>
       </c>
       <c r="K427" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.25">
@@ -16747,7 +16799,7 @@
         <v>11</v>
       </c>
       <c r="D428" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E428" t="s">
         <v>11</v>
@@ -16768,7 +16820,7 @@
         <v>11</v>
       </c>
       <c r="K428" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.25">
@@ -16782,7 +16834,7 @@
         <v>11</v>
       </c>
       <c r="D429" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E429" t="s">
         <v>11</v>
@@ -16803,7 +16855,7 @@
         <v>11</v>
       </c>
       <c r="K429" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.25">
@@ -16817,7 +16869,7 @@
         <v>11</v>
       </c>
       <c r="D430" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E430" t="s">
         <v>11</v>
@@ -16838,7 +16890,7 @@
         <v>11</v>
       </c>
       <c r="K430" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.25">
@@ -16852,7 +16904,7 @@
         <v>11</v>
       </c>
       <c r="D431" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E431" t="s">
         <v>11</v>
@@ -16873,7 +16925,7 @@
         <v>11</v>
       </c>
       <c r="K431" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.25">
@@ -16887,7 +16939,7 @@
         <v>11</v>
       </c>
       <c r="D432" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E432" t="s">
         <v>11</v>
@@ -16908,7 +16960,7 @@
         <v>11</v>
       </c>
       <c r="K432" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.25">
@@ -16922,7 +16974,7 @@
         <v>11</v>
       </c>
       <c r="D433" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E433" t="s">
         <v>11</v>
@@ -16943,7 +16995,7 @@
         <v>11</v>
       </c>
       <c r="K433" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.25">
@@ -16957,7 +17009,7 @@
         <v>11</v>
       </c>
       <c r="D434" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E434" t="s">
         <v>11</v>
@@ -16978,7 +17030,7 @@
         <v>11</v>
       </c>
       <c r="K434" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.25">
@@ -16992,7 +17044,7 @@
         <v>11</v>
       </c>
       <c r="D435" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E435" t="s">
         <v>11</v>
@@ -17013,7 +17065,7 @@
         <v>11</v>
       </c>
       <c r="K435" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.25">
@@ -17027,7 +17079,7 @@
         <v>11</v>
       </c>
       <c r="D436" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E436" t="s">
         <v>11</v>
@@ -17048,7 +17100,7 @@
         <v>11</v>
       </c>
       <c r="K436" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.25">
@@ -17062,7 +17114,7 @@
         <v>11</v>
       </c>
       <c r="D437" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E437" t="s">
         <v>11</v>
@@ -17083,7 +17135,7 @@
         <v>11</v>
       </c>
       <c r="K437" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.25">
@@ -17097,7 +17149,7 @@
         <v>11</v>
       </c>
       <c r="D438" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E438" t="s">
         <v>11</v>
@@ -17118,7 +17170,7 @@
         <v>11</v>
       </c>
       <c r="K438" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.25">
@@ -17132,7 +17184,7 @@
         <v>11</v>
       </c>
       <c r="D439" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E439" t="s">
         <v>11</v>
@@ -17153,7 +17205,7 @@
         <v>11</v>
       </c>
       <c r="K439" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.25">
@@ -17167,7 +17219,7 @@
         <v>11</v>
       </c>
       <c r="D440" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E440" t="s">
         <v>11</v>
@@ -17188,7 +17240,7 @@
         <v>11</v>
       </c>
       <c r="K440" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.25">
@@ -17202,7 +17254,7 @@
         <v>11</v>
       </c>
       <c r="D441" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E441" t="s">
         <v>11</v>
@@ -17223,7 +17275,7 @@
         <v>11</v>
       </c>
       <c r="K441" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.25">
@@ -17237,7 +17289,7 @@
         <v>11</v>
       </c>
       <c r="D442" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E442" t="s">
         <v>11</v>
@@ -17258,7 +17310,7 @@
         <v>11</v>
       </c>
       <c r="K442" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.25">
@@ -17272,7 +17324,7 @@
         <v>11</v>
       </c>
       <c r="D443" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E443" t="s">
         <v>11</v>
@@ -17293,7 +17345,7 @@
         <v>11</v>
       </c>
       <c r="K443" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.25">
@@ -17307,7 +17359,7 @@
         <v>11</v>
       </c>
       <c r="D444" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E444" t="s">
         <v>11</v>
@@ -17328,7 +17380,7 @@
         <v>11</v>
       </c>
       <c r="K444" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.25">
@@ -17342,7 +17394,7 @@
         <v>11</v>
       </c>
       <c r="D445" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E445" t="s">
         <v>11</v>
@@ -17363,7 +17415,7 @@
         <v>11</v>
       </c>
       <c r="K445" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.25">
@@ -17377,7 +17429,7 @@
         <v>11</v>
       </c>
       <c r="D446" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E446" t="s">
         <v>11</v>
@@ -17398,7 +17450,7 @@
         <v>11</v>
       </c>
       <c r="K446" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.25">
@@ -17412,7 +17464,7 @@
         <v>11</v>
       </c>
       <c r="D447" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E447" t="s">
         <v>11</v>
@@ -17433,7 +17485,7 @@
         <v>11</v>
       </c>
       <c r="K447" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.25">
@@ -17447,7 +17499,7 @@
         <v>11</v>
       </c>
       <c r="D448" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E448" t="s">
         <v>11</v>
@@ -17468,7 +17520,7 @@
         <v>11</v>
       </c>
       <c r="K448" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.25">
@@ -17482,7 +17534,7 @@
         <v>11</v>
       </c>
       <c r="D449" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E449" t="s">
         <v>11</v>
@@ -17503,7 +17555,7 @@
         <v>11</v>
       </c>
       <c r="K449" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.25">
@@ -17517,7 +17569,7 @@
         <v>11</v>
       </c>
       <c r="D450" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E450" t="s">
         <v>11</v>
@@ -17538,7 +17590,7 @@
         <v>11</v>
       </c>
       <c r="K450" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.25">
@@ -17552,7 +17604,7 @@
         <v>11</v>
       </c>
       <c r="D451" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E451" t="s">
         <v>11</v>
@@ -17573,7 +17625,7 @@
         <v>11</v>
       </c>
       <c r="K451" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.25">
@@ -17587,7 +17639,7 @@
         <v>11</v>
       </c>
       <c r="D452" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E452" t="s">
         <v>11</v>
@@ -17608,7 +17660,7 @@
         <v>11</v>
       </c>
       <c r="K452" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.25">
@@ -17622,7 +17674,7 @@
         <v>11</v>
       </c>
       <c r="D453" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E453" t="s">
         <v>11</v>
@@ -17643,7 +17695,7 @@
         <v>11</v>
       </c>
       <c r="K453" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.25">
@@ -17657,7 +17709,7 @@
         <v>11</v>
       </c>
       <c r="D454" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E454" t="s">
         <v>11</v>
@@ -17678,7 +17730,7 @@
         <v>11</v>
       </c>
       <c r="K454" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.25">
@@ -17692,7 +17744,7 @@
         <v>11</v>
       </c>
       <c r="D455" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E455" t="s">
         <v>11</v>
@@ -17713,7 +17765,7 @@
         <v>11</v>
       </c>
       <c r="K455" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.25">
@@ -17727,7 +17779,7 @@
         <v>11</v>
       </c>
       <c r="D456" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E456" t="s">
         <v>11</v>
@@ -17748,7 +17800,7 @@
         <v>11</v>
       </c>
       <c r="K456" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.25">
@@ -17762,7 +17814,7 @@
         <v>11</v>
       </c>
       <c r="D457" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E457" t="s">
         <v>11</v>
@@ -17783,7 +17835,7 @@
         <v>11</v>
       </c>
       <c r="K457" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.25">
@@ -17797,7 +17849,7 @@
         <v>11</v>
       </c>
       <c r="D458" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E458" t="s">
         <v>11</v>
@@ -17818,7 +17870,7 @@
         <v>11</v>
       </c>
       <c r="K458" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.25">
@@ -17832,7 +17884,7 @@
         <v>11</v>
       </c>
       <c r="D459" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E459" t="s">
         <v>11</v>
@@ -17853,7 +17905,7 @@
         <v>11</v>
       </c>
       <c r="K459" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.25">
@@ -17867,7 +17919,7 @@
         <v>11</v>
       </c>
       <c r="D460" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E460" t="s">
         <v>11</v>
@@ -17888,7 +17940,7 @@
         <v>11</v>
       </c>
       <c r="K460" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.25">
@@ -17902,7 +17954,7 @@
         <v>11</v>
       </c>
       <c r="D461" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E461" t="s">
         <v>11</v>
@@ -17923,7 +17975,7 @@
         <v>11</v>
       </c>
       <c r="K461" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.25">
@@ -17937,7 +17989,7 @@
         <v>11</v>
       </c>
       <c r="D462" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E462" t="s">
         <v>11</v>
@@ -17958,7 +18010,7 @@
         <v>11</v>
       </c>
       <c r="K462" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.25">
@@ -17972,7 +18024,7 @@
         <v>11</v>
       </c>
       <c r="D463" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E463" t="s">
         <v>11</v>
@@ -17993,7 +18045,7 @@
         <v>11</v>
       </c>
       <c r="K463" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.25">
@@ -18007,7 +18059,7 @@
         <v>11</v>
       </c>
       <c r="D464" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E464" t="s">
         <v>11</v>
@@ -18028,7 +18080,7 @@
         <v>11</v>
       </c>
       <c r="K464" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
@@ -18042,7 +18094,7 @@
         <v>11</v>
       </c>
       <c r="D465" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E465" t="s">
         <v>11</v>
@@ -18063,7 +18115,7 @@
         <v>11</v>
       </c>
       <c r="K465" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.25">
@@ -18077,7 +18129,7 @@
         <v>11</v>
       </c>
       <c r="D466" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E466" t="s">
         <v>11</v>
@@ -18098,7 +18150,7 @@
         <v>11</v>
       </c>
       <c r="K466" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -18117,6 +18169,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
+++ b/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Kênh YouTube" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5112" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5111" uniqueCount="484">
   <si>
     <t>EMAIL</t>
   </si>
@@ -143,6 +143,9 @@
     <t>https://www.youtube.com/watch?v=5SkR8ViDXpg</t>
   </si>
   <si>
+    <t>【修羅場な話】嫁が不倫した。間嫁「大事な話がある。お宅の嫁と私の夫が不倫してる」俺「えっ！？」急いでファミレスに向かうと... 間嫁「制裁の条件は...慰謝料は山分けしましょう」俺「おｋ」→結果【朗読</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=0mMZPZmigGU</t>
   </si>
   <si>
@@ -1524,7 +1527,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1534,8 +1537,15 @@
     </font>
     <font>
       <u/>
+      <charset val="134"/>
       <color theme="10"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="134"/>
+      <color theme="1"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1570,10 +1580,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1634,7 +1644,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1669,7 +1679,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1843,19 +1853,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K466"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2066,13 +2070,13 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>11</v>
@@ -2080,8 +2084,8 @@
       <c r="J7" t="s">
         <v>11</v>
       </c>
-      <c r="K7" t="s">
-        <v>11</v>
+      <c r="K7">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2095,7 +2099,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -2130,7 +2134,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -2165,7 +2169,7 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -2200,7 +2204,7 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -2235,7 +2239,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2270,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -2305,7 +2309,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2340,7 +2344,7 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -2375,7 +2379,7 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -2410,7 +2414,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -2445,7 +2449,7 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -2480,7 +2484,7 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -2515,7 +2519,7 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -2550,7 +2554,7 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -2585,7 +2589,7 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -2620,7 +2624,7 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -2655,7 +2659,7 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -2690,7 +2694,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -2725,7 +2729,7 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -2760,7 +2764,7 @@
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -2795,7 +2799,7 @@
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -2830,7 +2834,7 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -2865,7 +2869,7 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -2900,7 +2904,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -2935,7 +2939,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -2970,7 +2974,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3005,7 +3009,7 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3040,7 +3044,7 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3075,7 +3079,7 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -3110,7 +3114,7 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3145,7 +3149,7 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -3180,7 +3184,7 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -3215,7 +3219,7 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -3250,7 +3254,7 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -3285,7 +3289,7 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -3320,7 +3324,7 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -3355,7 +3359,7 @@
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -3390,7 +3394,7 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -3425,7 +3429,7 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -3460,7 +3464,7 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -3495,7 +3499,7 @@
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -3530,7 +3534,7 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -3565,7 +3569,7 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -3600,7 +3604,7 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -3635,7 +3639,7 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -3670,7 +3674,7 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -3705,7 +3709,7 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -3740,7 +3744,7 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -3775,7 +3779,7 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -3810,7 +3814,7 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -3845,7 +3849,7 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -3880,7 +3884,7 @@
         <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -3915,7 +3919,7 @@
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -3950,7 +3954,7 @@
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -3985,7 +3989,7 @@
         <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -4020,7 +4024,7 @@
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -4055,7 +4059,7 @@
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -4090,7 +4094,7 @@
         <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -4125,7 +4129,7 @@
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -4160,7 +4164,7 @@
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -4195,7 +4199,7 @@
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -4230,7 +4234,7 @@
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -4265,7 +4269,7 @@
         <v>11</v>
       </c>
       <c r="D70" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -4300,7 +4304,7 @@
         <v>11</v>
       </c>
       <c r="D71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -4335,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -4370,7 +4374,7 @@
         <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -4405,7 +4409,7 @@
         <v>11</v>
       </c>
       <c r="D74" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -4440,7 +4444,7 @@
         <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -4475,7 +4479,7 @@
         <v>11</v>
       </c>
       <c r="D76" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -4510,7 +4514,7 @@
         <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -4545,7 +4549,7 @@
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -4580,7 +4584,7 @@
         <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -4615,7 +4619,7 @@
         <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -4650,7 +4654,7 @@
         <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E81" t="s">
         <v>15</v>
@@ -4685,7 +4689,7 @@
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
@@ -4720,7 +4724,7 @@
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E83" t="s">
         <v>15</v>
@@ -4755,7 +4759,7 @@
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -4790,7 +4794,7 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -4825,7 +4829,7 @@
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
@@ -4860,7 +4864,7 @@
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -4895,7 +4899,7 @@
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -4930,7 +4934,7 @@
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -4965,7 +4969,7 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -5000,7 +5004,7 @@
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -5035,7 +5039,7 @@
         <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -5070,7 +5074,7 @@
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -5105,7 +5109,7 @@
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -5140,7 +5144,7 @@
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -5175,7 +5179,7 @@
         <v>11</v>
       </c>
       <c r="D96" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E96" t="s">
         <v>15</v>
@@ -5210,7 +5214,7 @@
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E97" t="s">
         <v>15</v>
@@ -5245,7 +5249,7 @@
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E98" t="s">
         <v>15</v>
@@ -5280,7 +5284,7 @@
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E99" t="s">
         <v>15</v>
@@ -5315,7 +5319,7 @@
         <v>11</v>
       </c>
       <c r="D100" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E100" t="s">
         <v>15</v>
@@ -5350,7 +5354,7 @@
         <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E101" t="s">
         <v>15</v>
@@ -5385,7 +5389,7 @@
         <v>11</v>
       </c>
       <c r="D102" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E102" t="s">
         <v>15</v>
@@ -5420,7 +5424,7 @@
         <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E103" t="s">
         <v>15</v>
@@ -5455,7 +5459,7 @@
         <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E104" t="s">
         <v>15</v>
@@ -5490,7 +5494,7 @@
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E105" t="s">
         <v>15</v>
@@ -5525,7 +5529,7 @@
         <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E106" t="s">
         <v>15</v>
@@ -5560,7 +5564,7 @@
         <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E107" t="s">
         <v>15</v>
@@ -5595,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E108" t="s">
         <v>15</v>
@@ -5630,7 +5634,7 @@
         <v>11</v>
       </c>
       <c r="D109" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E109" t="s">
         <v>15</v>
@@ -5665,7 +5669,7 @@
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E110" t="s">
         <v>15</v>
@@ -5700,7 +5704,7 @@
         <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E111" t="s">
         <v>15</v>
@@ -5735,7 +5739,7 @@
         <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E112" t="s">
         <v>15</v>
@@ -5770,7 +5774,7 @@
         <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E113" t="s">
         <v>15</v>
@@ -5805,7 +5809,7 @@
         <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E114" t="s">
         <v>15</v>
@@ -5840,7 +5844,7 @@
         <v>11</v>
       </c>
       <c r="D115" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E115" t="s">
         <v>15</v>
@@ -5875,7 +5879,7 @@
         <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E116" t="s">
         <v>15</v>
@@ -5910,7 +5914,7 @@
         <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E117" t="s">
         <v>15</v>
@@ -5945,7 +5949,7 @@
         <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E118" t="s">
         <v>15</v>
@@ -5980,7 +5984,7 @@
         <v>11</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E119" t="s">
         <v>15</v>
@@ -6015,7 +6019,7 @@
         <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E120" t="s">
         <v>15</v>
@@ -6050,7 +6054,7 @@
         <v>11</v>
       </c>
       <c r="D121" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E121" t="s">
         <v>15</v>
@@ -6085,7 +6089,7 @@
         <v>11</v>
       </c>
       <c r="D122" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E122" t="s">
         <v>15</v>
@@ -6120,7 +6124,7 @@
         <v>11</v>
       </c>
       <c r="D123" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E123" t="s">
         <v>15</v>
@@ -6155,7 +6159,7 @@
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E124" t="s">
         <v>15</v>
@@ -6190,7 +6194,7 @@
         <v>11</v>
       </c>
       <c r="D125" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E125" t="s">
         <v>15</v>
@@ -6225,7 +6229,7 @@
         <v>11</v>
       </c>
       <c r="D126" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
@@ -6260,7 +6264,7 @@
         <v>11</v>
       </c>
       <c r="D127" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E127" t="s">
         <v>15</v>
@@ -6295,7 +6299,7 @@
         <v>11</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E128" t="s">
         <v>15</v>
@@ -6330,7 +6334,7 @@
         <v>11</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s">
         <v>15</v>
@@ -6365,7 +6369,7 @@
         <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E130" t="s">
         <v>15</v>
@@ -6400,7 +6404,7 @@
         <v>11</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E131" t="s">
         <v>15</v>
@@ -6435,7 +6439,7 @@
         <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E132" t="s">
         <v>15</v>
@@ -6470,7 +6474,7 @@
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E133" t="s">
         <v>15</v>
@@ -6505,7 +6509,7 @@
         <v>11</v>
       </c>
       <c r="D134" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E134" t="s">
         <v>15</v>
@@ -6540,7 +6544,7 @@
         <v>11</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E135" t="s">
         <v>15</v>
@@ -6575,7 +6579,7 @@
         <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E136" t="s">
         <v>15</v>
@@ -6610,7 +6614,7 @@
         <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E137" t="s">
         <v>15</v>
@@ -6645,7 +6649,7 @@
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E138" t="s">
         <v>15</v>
@@ -6680,7 +6684,7 @@
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E139" t="s">
         <v>15</v>
@@ -6715,7 +6719,7 @@
         <v>11</v>
       </c>
       <c r="D140" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E140" t="s">
         <v>15</v>
@@ -6750,7 +6754,7 @@
         <v>11</v>
       </c>
       <c r="D141" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E141" t="s">
         <v>15</v>
@@ -6785,7 +6789,7 @@
         <v>11</v>
       </c>
       <c r="D142" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E142" t="s">
         <v>15</v>
@@ -6820,7 +6824,7 @@
         <v>11</v>
       </c>
       <c r="D143" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E143" t="s">
         <v>15</v>
@@ -6855,7 +6859,7 @@
         <v>11</v>
       </c>
       <c r="D144" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E144" t="s">
         <v>15</v>
@@ -6890,7 +6894,7 @@
         <v>11</v>
       </c>
       <c r="D145" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E145" t="s">
         <v>15</v>
@@ -6925,7 +6929,7 @@
         <v>11</v>
       </c>
       <c r="D146" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E146" t="s">
         <v>15</v>
@@ -6960,7 +6964,7 @@
         <v>11</v>
       </c>
       <c r="D147" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E147" t="s">
         <v>15</v>
@@ -6995,7 +6999,7 @@
         <v>11</v>
       </c>
       <c r="D148" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E148" t="s">
         <v>15</v>
@@ -7030,7 +7034,7 @@
         <v>11</v>
       </c>
       <c r="D149" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E149" t="s">
         <v>15</v>
@@ -7065,7 +7069,7 @@
         <v>11</v>
       </c>
       <c r="D150" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E150" t="s">
         <v>15</v>
@@ -7100,7 +7104,7 @@
         <v>11</v>
       </c>
       <c r="D151" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E151" t="s">
         <v>15</v>
@@ -7135,7 +7139,7 @@
         <v>11</v>
       </c>
       <c r="D152" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E152" t="s">
         <v>15</v>
@@ -7170,7 +7174,7 @@
         <v>11</v>
       </c>
       <c r="D153" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E153" t="s">
         <v>15</v>
@@ -7205,7 +7209,7 @@
         <v>11</v>
       </c>
       <c r="D154" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E154" t="s">
         <v>15</v>
@@ -7240,7 +7244,7 @@
         <v>11</v>
       </c>
       <c r="D155" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E155" t="s">
         <v>15</v>
@@ -7275,7 +7279,7 @@
         <v>11</v>
       </c>
       <c r="D156" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E156" t="s">
         <v>15</v>
@@ -7310,7 +7314,7 @@
         <v>11</v>
       </c>
       <c r="D157" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E157" t="s">
         <v>15</v>
@@ -7345,7 +7349,7 @@
         <v>11</v>
       </c>
       <c r="D158" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E158" t="s">
         <v>15</v>
@@ -7380,7 +7384,7 @@
         <v>11</v>
       </c>
       <c r="D159" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E159" t="s">
         <v>15</v>
@@ -7415,7 +7419,7 @@
         <v>11</v>
       </c>
       <c r="D160" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E160" t="s">
         <v>15</v>
@@ -7450,7 +7454,7 @@
         <v>11</v>
       </c>
       <c r="D161" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E161" t="s">
         <v>15</v>
@@ -7485,7 +7489,7 @@
         <v>11</v>
       </c>
       <c r="D162" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E162" t="s">
         <v>15</v>
@@ -7520,7 +7524,7 @@
         <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E163" t="s">
         <v>15</v>
@@ -7555,7 +7559,7 @@
         <v>11</v>
       </c>
       <c r="D164" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E164" t="s">
         <v>15</v>
@@ -7590,7 +7594,7 @@
         <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E165" t="s">
         <v>15</v>
@@ -7625,7 +7629,7 @@
         <v>11</v>
       </c>
       <c r="D166" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E166" t="s">
         <v>15</v>
@@ -7660,7 +7664,7 @@
         <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E167" t="s">
         <v>15</v>
@@ -7695,7 +7699,7 @@
         <v>11</v>
       </c>
       <c r="D168" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E168" t="s">
         <v>15</v>
@@ -7730,7 +7734,7 @@
         <v>11</v>
       </c>
       <c r="D169" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E169" t="s">
         <v>15</v>
@@ -7765,7 +7769,7 @@
         <v>11</v>
       </c>
       <c r="D170" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E170" t="s">
         <v>15</v>
@@ -7800,7 +7804,7 @@
         <v>11</v>
       </c>
       <c r="D171" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E171" t="s">
         <v>15</v>
@@ -7835,7 +7839,7 @@
         <v>11</v>
       </c>
       <c r="D172" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E172" t="s">
         <v>15</v>
@@ -7870,7 +7874,7 @@
         <v>11</v>
       </c>
       <c r="D173" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E173" t="s">
         <v>15</v>
@@ -7905,7 +7909,7 @@
         <v>11</v>
       </c>
       <c r="D174" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E174" t="s">
         <v>15</v>
@@ -7940,7 +7944,7 @@
         <v>11</v>
       </c>
       <c r="D175" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E175" t="s">
         <v>15</v>
@@ -7975,7 +7979,7 @@
         <v>11</v>
       </c>
       <c r="D176" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E176" t="s">
         <v>15</v>
@@ -8010,7 +8014,7 @@
         <v>11</v>
       </c>
       <c r="D177" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E177" t="s">
         <v>15</v>
@@ -8045,7 +8049,7 @@
         <v>11</v>
       </c>
       <c r="D178" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E178" t="s">
         <v>15</v>
@@ -8080,7 +8084,7 @@
         <v>11</v>
       </c>
       <c r="D179" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E179" t="s">
         <v>15</v>
@@ -8115,7 +8119,7 @@
         <v>11</v>
       </c>
       <c r="D180" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E180" t="s">
         <v>15</v>
@@ -8150,7 +8154,7 @@
         <v>11</v>
       </c>
       <c r="D181" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E181" t="s">
         <v>15</v>
@@ -8185,7 +8189,7 @@
         <v>11</v>
       </c>
       <c r="D182" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E182" t="s">
         <v>15</v>
@@ -8220,7 +8224,7 @@
         <v>11</v>
       </c>
       <c r="D183" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E183" t="s">
         <v>15</v>
@@ -8255,7 +8259,7 @@
         <v>11</v>
       </c>
       <c r="D184" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E184" t="s">
         <v>15</v>
@@ -8290,7 +8294,7 @@
         <v>11</v>
       </c>
       <c r="D185" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E185" t="s">
         <v>15</v>
@@ -8325,7 +8329,7 @@
         <v>11</v>
       </c>
       <c r="D186" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E186" t="s">
         <v>15</v>
@@ -8360,7 +8364,7 @@
         <v>11</v>
       </c>
       <c r="D187" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E187" t="s">
         <v>15</v>
@@ -8395,7 +8399,7 @@
         <v>11</v>
       </c>
       <c r="D188" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E188" t="s">
         <v>15</v>
@@ -8430,7 +8434,7 @@
         <v>11</v>
       </c>
       <c r="D189" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E189" t="s">
         <v>15</v>
@@ -8465,7 +8469,7 @@
         <v>11</v>
       </c>
       <c r="D190" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E190" t="s">
         <v>15</v>
@@ -8500,7 +8504,7 @@
         <v>11</v>
       </c>
       <c r="D191" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E191" t="s">
         <v>15</v>
@@ -8535,7 +8539,7 @@
         <v>11</v>
       </c>
       <c r="D192" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E192" t="s">
         <v>15</v>
@@ -8570,7 +8574,7 @@
         <v>11</v>
       </c>
       <c r="D193" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E193" t="s">
         <v>15</v>
@@ -8605,7 +8609,7 @@
         <v>11</v>
       </c>
       <c r="D194" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E194" t="s">
         <v>15</v>
@@ -8640,7 +8644,7 @@
         <v>11</v>
       </c>
       <c r="D195" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E195" t="s">
         <v>15</v>
@@ -8675,7 +8679,7 @@
         <v>11</v>
       </c>
       <c r="D196" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E196" t="s">
         <v>15</v>
@@ -8710,7 +8714,7 @@
         <v>11</v>
       </c>
       <c r="D197" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E197" t="s">
         <v>15</v>
@@ -8745,7 +8749,7 @@
         <v>11</v>
       </c>
       <c r="D198" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E198" t="s">
         <v>15</v>
@@ -8780,7 +8784,7 @@
         <v>11</v>
       </c>
       <c r="D199" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E199" t="s">
         <v>15</v>
@@ -8815,7 +8819,7 @@
         <v>11</v>
       </c>
       <c r="D200" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E200" t="s">
         <v>15</v>
@@ -8850,7 +8854,7 @@
         <v>11</v>
       </c>
       <c r="D201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E201" t="s">
         <v>15</v>
@@ -8885,7 +8889,7 @@
         <v>11</v>
       </c>
       <c r="D202" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E202" t="s">
         <v>15</v>
@@ -8920,7 +8924,7 @@
         <v>11</v>
       </c>
       <c r="D203" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E203" t="s">
         <v>15</v>
@@ -8955,7 +8959,7 @@
         <v>11</v>
       </c>
       <c r="D204" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E204" t="s">
         <v>15</v>
@@ -8990,7 +8994,7 @@
         <v>11</v>
       </c>
       <c r="D205" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E205" t="s">
         <v>15</v>
@@ -9025,7 +9029,7 @@
         <v>11</v>
       </c>
       <c r="D206" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E206" t="s">
         <v>15</v>
@@ -9060,7 +9064,7 @@
         <v>11</v>
       </c>
       <c r="D207" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E207" t="s">
         <v>15</v>
@@ -9095,7 +9099,7 @@
         <v>11</v>
       </c>
       <c r="D208" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E208" t="s">
         <v>15</v>
@@ -9130,7 +9134,7 @@
         <v>11</v>
       </c>
       <c r="D209" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E209" t="s">
         <v>15</v>
@@ -9165,7 +9169,7 @@
         <v>11</v>
       </c>
       <c r="D210" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E210" t="s">
         <v>15</v>
@@ -9200,7 +9204,7 @@
         <v>11</v>
       </c>
       <c r="D211" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E211" t="s">
         <v>15</v>
@@ -9235,7 +9239,7 @@
         <v>11</v>
       </c>
       <c r="D212" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E212" t="s">
         <v>15</v>
@@ -9270,7 +9274,7 @@
         <v>11</v>
       </c>
       <c r="D213" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E213" t="s">
         <v>15</v>
@@ -9305,7 +9309,7 @@
         <v>11</v>
       </c>
       <c r="D214" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E214" t="s">
         <v>15</v>
@@ -9340,7 +9344,7 @@
         <v>11</v>
       </c>
       <c r="D215" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E215" t="s">
         <v>15</v>
@@ -9375,7 +9379,7 @@
         <v>11</v>
       </c>
       <c r="D216" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E216" t="s">
         <v>15</v>
@@ -9410,7 +9414,7 @@
         <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E217" t="s">
         <v>15</v>
@@ -9445,7 +9449,7 @@
         <v>11</v>
       </c>
       <c r="D218" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E218" t="s">
         <v>15</v>
@@ -9480,7 +9484,7 @@
         <v>11</v>
       </c>
       <c r="D219" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E219" t="s">
         <v>15</v>
@@ -9515,7 +9519,7 @@
         <v>11</v>
       </c>
       <c r="D220" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E220" t="s">
         <v>15</v>
@@ -9550,7 +9554,7 @@
         <v>11</v>
       </c>
       <c r="D221" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E221" t="s">
         <v>15</v>
@@ -9585,7 +9589,7 @@
         <v>11</v>
       </c>
       <c r="D222" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E222" t="s">
         <v>15</v>
@@ -9620,7 +9624,7 @@
         <v>11</v>
       </c>
       <c r="D223" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E223" t="s">
         <v>15</v>
@@ -9655,7 +9659,7 @@
         <v>11</v>
       </c>
       <c r="D224" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E224" t="s">
         <v>15</v>
@@ -9690,7 +9694,7 @@
         <v>11</v>
       </c>
       <c r="D225" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E225" t="s">
         <v>15</v>
@@ -9725,7 +9729,7 @@
         <v>11</v>
       </c>
       <c r="D226" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E226" t="s">
         <v>15</v>
@@ -9760,7 +9764,7 @@
         <v>11</v>
       </c>
       <c r="D227" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E227" t="s">
         <v>15</v>
@@ -9795,7 +9799,7 @@
         <v>11</v>
       </c>
       <c r="D228" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E228" t="s">
         <v>15</v>
@@ -9830,7 +9834,7 @@
         <v>11</v>
       </c>
       <c r="D229" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E229" t="s">
         <v>15</v>
@@ -9865,7 +9869,7 @@
         <v>11</v>
       </c>
       <c r="D230" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E230" t="s">
         <v>15</v>
@@ -9900,7 +9904,7 @@
         <v>11</v>
       </c>
       <c r="D231" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E231" t="s">
         <v>15</v>
@@ -9935,7 +9939,7 @@
         <v>11</v>
       </c>
       <c r="D232" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E232" t="s">
         <v>15</v>
@@ -9970,7 +9974,7 @@
         <v>11</v>
       </c>
       <c r="D233" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E233" t="s">
         <v>15</v>
@@ -10005,7 +10009,7 @@
         <v>11</v>
       </c>
       <c r="D234" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E234" t="s">
         <v>15</v>
@@ -10040,7 +10044,7 @@
         <v>11</v>
       </c>
       <c r="D235" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E235" t="s">
         <v>15</v>
@@ -10075,7 +10079,7 @@
         <v>11</v>
       </c>
       <c r="D236" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E236" t="s">
         <v>15</v>
@@ -10110,7 +10114,7 @@
         <v>11</v>
       </c>
       <c r="D237" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E237" t="s">
         <v>15</v>
@@ -10145,7 +10149,7 @@
         <v>11</v>
       </c>
       <c r="D238" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E238" t="s">
         <v>15</v>
@@ -10180,7 +10184,7 @@
         <v>11</v>
       </c>
       <c r="D239" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E239" t="s">
         <v>15</v>
@@ -10215,7 +10219,7 @@
         <v>11</v>
       </c>
       <c r="D240" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E240" t="s">
         <v>15</v>
@@ -10250,7 +10254,7 @@
         <v>11</v>
       </c>
       <c r="D241" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E241" t="s">
         <v>15</v>
@@ -10285,7 +10289,7 @@
         <v>11</v>
       </c>
       <c r="D242" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E242" t="s">
         <v>15</v>
@@ -10320,7 +10324,7 @@
         <v>11</v>
       </c>
       <c r="D243" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E243" t="s">
         <v>15</v>
@@ -10355,7 +10359,7 @@
         <v>11</v>
       </c>
       <c r="D244" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E244" t="s">
         <v>15</v>
@@ -10390,7 +10394,7 @@
         <v>11</v>
       </c>
       <c r="D245" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E245" t="s">
         <v>15</v>
@@ -10425,7 +10429,7 @@
         <v>11</v>
       </c>
       <c r="D246" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E246" t="s">
         <v>15</v>
@@ -10460,7 +10464,7 @@
         <v>11</v>
       </c>
       <c r="D247" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E247" t="s">
         <v>15</v>
@@ -10495,7 +10499,7 @@
         <v>11</v>
       </c>
       <c r="D248" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E248" t="s">
         <v>15</v>
@@ -10530,7 +10534,7 @@
         <v>11</v>
       </c>
       <c r="D249" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E249" t="s">
         <v>15</v>
@@ -10565,7 +10569,7 @@
         <v>11</v>
       </c>
       <c r="D250" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E250" t="s">
         <v>15</v>
@@ -10600,7 +10604,7 @@
         <v>11</v>
       </c>
       <c r="D251" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E251" t="s">
         <v>15</v>
@@ -10635,7 +10639,7 @@
         <v>11</v>
       </c>
       <c r="D252" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E252" t="s">
         <v>15</v>
@@ -10670,7 +10674,7 @@
         <v>11</v>
       </c>
       <c r="D253" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E253" t="s">
         <v>15</v>
@@ -10705,7 +10709,7 @@
         <v>11</v>
       </c>
       <c r="D254" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E254" t="s">
         <v>15</v>
@@ -10740,7 +10744,7 @@
         <v>11</v>
       </c>
       <c r="D255" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E255" t="s">
         <v>15</v>
@@ -10775,7 +10779,7 @@
         <v>11</v>
       </c>
       <c r="D256" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E256" t="s">
         <v>15</v>
@@ -10810,7 +10814,7 @@
         <v>11</v>
       </c>
       <c r="D257" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E257" t="s">
         <v>15</v>
@@ -10845,7 +10849,7 @@
         <v>11</v>
       </c>
       <c r="D258" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E258" t="s">
         <v>15</v>
@@ -10880,7 +10884,7 @@
         <v>11</v>
       </c>
       <c r="D259" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E259" t="s">
         <v>15</v>
@@ -10915,7 +10919,7 @@
         <v>11</v>
       </c>
       <c r="D260" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E260" t="s">
         <v>15</v>
@@ -10950,7 +10954,7 @@
         <v>11</v>
       </c>
       <c r="D261" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E261" t="s">
         <v>15</v>
@@ -10985,7 +10989,7 @@
         <v>11</v>
       </c>
       <c r="D262" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E262" t="s">
         <v>15</v>
@@ -11020,7 +11024,7 @@
         <v>11</v>
       </c>
       <c r="D263" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E263" t="s">
         <v>15</v>
@@ -11055,7 +11059,7 @@
         <v>11</v>
       </c>
       <c r="D264" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E264" t="s">
         <v>15</v>
@@ -11090,7 +11094,7 @@
         <v>11</v>
       </c>
       <c r="D265" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E265" t="s">
         <v>15</v>
@@ -11125,7 +11129,7 @@
         <v>11</v>
       </c>
       <c r="D266" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E266" t="s">
         <v>15</v>
@@ -11160,7 +11164,7 @@
         <v>11</v>
       </c>
       <c r="D267" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E267" t="s">
         <v>15</v>
@@ -11195,7 +11199,7 @@
         <v>11</v>
       </c>
       <c r="D268" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E268" t="s">
         <v>15</v>
@@ -11230,7 +11234,7 @@
         <v>11</v>
       </c>
       <c r="D269" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E269" t="s">
         <v>15</v>
@@ -11265,7 +11269,7 @@
         <v>11</v>
       </c>
       <c r="D270" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E270" t="s">
         <v>15</v>
@@ -11300,7 +11304,7 @@
         <v>11</v>
       </c>
       <c r="D271" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E271" t="s">
         <v>15</v>
@@ -11335,7 +11339,7 @@
         <v>11</v>
       </c>
       <c r="D272" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E272" t="s">
         <v>15</v>
@@ -11370,7 +11374,7 @@
         <v>11</v>
       </c>
       <c r="D273" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E273" t="s">
         <v>15</v>
@@ -11405,7 +11409,7 @@
         <v>11</v>
       </c>
       <c r="D274" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E274" t="s">
         <v>15</v>
@@ -11440,7 +11444,7 @@
         <v>11</v>
       </c>
       <c r="D275" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E275" t="s">
         <v>15</v>
@@ -11475,7 +11479,7 @@
         <v>11</v>
       </c>
       <c r="D276" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E276" t="s">
         <v>15</v>
@@ -11510,7 +11514,7 @@
         <v>11</v>
       </c>
       <c r="D277" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E277" t="s">
         <v>15</v>
@@ -11545,7 +11549,7 @@
         <v>11</v>
       </c>
       <c r="D278" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E278" t="s">
         <v>15</v>
@@ -11580,7 +11584,7 @@
         <v>11</v>
       </c>
       <c r="D279" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E279" t="s">
         <v>15</v>
@@ -11615,7 +11619,7 @@
         <v>11</v>
       </c>
       <c r="D280" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E280" t="s">
         <v>15</v>
@@ -11650,7 +11654,7 @@
         <v>11</v>
       </c>
       <c r="D281" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E281" t="s">
         <v>15</v>
@@ -11685,7 +11689,7 @@
         <v>11</v>
       </c>
       <c r="D282" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E282" t="s">
         <v>15</v>
@@ -11720,7 +11724,7 @@
         <v>11</v>
       </c>
       <c r="D283" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E283" t="s">
         <v>15</v>
@@ -11755,7 +11759,7 @@
         <v>11</v>
       </c>
       <c r="D284" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E284" t="s">
         <v>15</v>
@@ -11790,7 +11794,7 @@
         <v>11</v>
       </c>
       <c r="D285" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E285" t="s">
         <v>15</v>
@@ -11825,7 +11829,7 @@
         <v>11</v>
       </c>
       <c r="D286" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E286" t="s">
         <v>15</v>
@@ -11860,7 +11864,7 @@
         <v>11</v>
       </c>
       <c r="D287" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E287" t="s">
         <v>15</v>
@@ -11895,7 +11899,7 @@
         <v>11</v>
       </c>
       <c r="D288" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E288" t="s">
         <v>15</v>
@@ -11930,7 +11934,7 @@
         <v>11</v>
       </c>
       <c r="D289" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E289" t="s">
         <v>15</v>
@@ -11965,7 +11969,7 @@
         <v>11</v>
       </c>
       <c r="D290" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E290" t="s">
         <v>15</v>
@@ -12000,7 +12004,7 @@
         <v>11</v>
       </c>
       <c r="D291" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E291" t="s">
         <v>15</v>
@@ -12035,7 +12039,7 @@
         <v>11</v>
       </c>
       <c r="D292" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E292" t="s">
         <v>15</v>
@@ -12070,7 +12074,7 @@
         <v>11</v>
       </c>
       <c r="D293" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E293" t="s">
         <v>15</v>
@@ -12105,7 +12109,7 @@
         <v>11</v>
       </c>
       <c r="D294" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E294" t="s">
         <v>15</v>
@@ -12140,7 +12144,7 @@
         <v>11</v>
       </c>
       <c r="D295" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E295" t="s">
         <v>15</v>
@@ -12175,7 +12179,7 @@
         <v>11</v>
       </c>
       <c r="D296" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E296" t="s">
         <v>15</v>
@@ -12210,7 +12214,7 @@
         <v>11</v>
       </c>
       <c r="D297" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E297" t="s">
         <v>15</v>
@@ -12245,7 +12249,7 @@
         <v>11</v>
       </c>
       <c r="D298" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E298" t="s">
         <v>15</v>
@@ -12280,7 +12284,7 @@
         <v>11</v>
       </c>
       <c r="D299" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E299" t="s">
         <v>15</v>
@@ -12315,7 +12319,7 @@
         <v>11</v>
       </c>
       <c r="D300" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E300" t="s">
         <v>15</v>
@@ -12350,7 +12354,7 @@
         <v>11</v>
       </c>
       <c r="D301" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E301" t="s">
         <v>15</v>
@@ -12385,7 +12389,7 @@
         <v>11</v>
       </c>
       <c r="D302" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E302" t="s">
         <v>15</v>
@@ -12420,7 +12424,7 @@
         <v>11</v>
       </c>
       <c r="D303" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E303" t="s">
         <v>15</v>
@@ -12455,7 +12459,7 @@
         <v>11</v>
       </c>
       <c r="D304" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E304" t="s">
         <v>15</v>
@@ -12490,7 +12494,7 @@
         <v>11</v>
       </c>
       <c r="D305" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E305" t="s">
         <v>15</v>
@@ -12525,7 +12529,7 @@
         <v>11</v>
       </c>
       <c r="D306" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E306" t="s">
         <v>15</v>
@@ -12560,7 +12564,7 @@
         <v>11</v>
       </c>
       <c r="D307" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E307" t="s">
         <v>15</v>
@@ -12595,7 +12599,7 @@
         <v>11</v>
       </c>
       <c r="D308" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E308" t="s">
         <v>15</v>
@@ -12630,7 +12634,7 @@
         <v>11</v>
       </c>
       <c r="D309" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E309" t="s">
         <v>15</v>
@@ -12665,7 +12669,7 @@
         <v>11</v>
       </c>
       <c r="D310" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E310" t="s">
         <v>15</v>
@@ -12700,7 +12704,7 @@
         <v>11</v>
       </c>
       <c r="D311" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E311" t="s">
         <v>15</v>
@@ -12735,7 +12739,7 @@
         <v>11</v>
       </c>
       <c r="D312" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E312" t="s">
         <v>15</v>
@@ -12770,7 +12774,7 @@
         <v>11</v>
       </c>
       <c r="D313" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E313" t="s">
         <v>15</v>
@@ -12805,7 +12809,7 @@
         <v>11</v>
       </c>
       <c r="D314" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E314" t="s">
         <v>15</v>
@@ -12840,7 +12844,7 @@
         <v>11</v>
       </c>
       <c r="D315" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E315" t="s">
         <v>15</v>
@@ -12875,7 +12879,7 @@
         <v>11</v>
       </c>
       <c r="D316" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E316" t="s">
         <v>15</v>
@@ -12910,7 +12914,7 @@
         <v>11</v>
       </c>
       <c r="D317" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E317" t="s">
         <v>15</v>
@@ -12945,7 +12949,7 @@
         <v>11</v>
       </c>
       <c r="D318" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E318" t="s">
         <v>15</v>
@@ -12980,7 +12984,7 @@
         <v>11</v>
       </c>
       <c r="D319" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E319" t="s">
         <v>15</v>
@@ -13015,7 +13019,7 @@
         <v>11</v>
       </c>
       <c r="D320" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E320" t="s">
         <v>15</v>
@@ -13050,7 +13054,7 @@
         <v>11</v>
       </c>
       <c r="D321" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E321" t="s">
         <v>15</v>
@@ -13085,7 +13089,7 @@
         <v>11</v>
       </c>
       <c r="D322" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E322" t="s">
         <v>15</v>
@@ -13120,7 +13124,7 @@
         <v>11</v>
       </c>
       <c r="D323" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E323" t="s">
         <v>15</v>
@@ -13155,7 +13159,7 @@
         <v>11</v>
       </c>
       <c r="D324" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E324" t="s">
         <v>15</v>
@@ -13190,7 +13194,7 @@
         <v>11</v>
       </c>
       <c r="D325" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E325" t="s">
         <v>15</v>
@@ -13225,7 +13229,7 @@
         <v>11</v>
       </c>
       <c r="D326" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E326" t="s">
         <v>15</v>
@@ -13260,7 +13264,7 @@
         <v>11</v>
       </c>
       <c r="D327" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E327" t="s">
         <v>15</v>
@@ -13295,7 +13299,7 @@
         <v>11</v>
       </c>
       <c r="D328" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E328" t="s">
         <v>15</v>
@@ -13330,7 +13334,7 @@
         <v>11</v>
       </c>
       <c r="D329" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E329" t="s">
         <v>15</v>
@@ -13365,7 +13369,7 @@
         <v>11</v>
       </c>
       <c r="D330" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E330" t="s">
         <v>15</v>
@@ -13400,7 +13404,7 @@
         <v>11</v>
       </c>
       <c r="D331" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E331" t="s">
         <v>15</v>
@@ -13435,7 +13439,7 @@
         <v>11</v>
       </c>
       <c r="D332" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E332" t="s">
         <v>15</v>
@@ -13470,7 +13474,7 @@
         <v>11</v>
       </c>
       <c r="D333" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E333" t="s">
         <v>15</v>
@@ -13505,7 +13509,7 @@
         <v>11</v>
       </c>
       <c r="D334" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E334" t="s">
         <v>15</v>
@@ -13540,7 +13544,7 @@
         <v>11</v>
       </c>
       <c r="D335" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E335" t="s">
         <v>15</v>
@@ -13575,7 +13579,7 @@
         <v>11</v>
       </c>
       <c r="D336" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E336" t="s">
         <v>15</v>
@@ -13610,7 +13614,7 @@
         <v>11</v>
       </c>
       <c r="D337" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E337" t="s">
         <v>15</v>
@@ -13645,7 +13649,7 @@
         <v>11</v>
       </c>
       <c r="D338" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E338" t="s">
         <v>15</v>
@@ -13680,7 +13684,7 @@
         <v>11</v>
       </c>
       <c r="D339" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E339" t="s">
         <v>15</v>
@@ -13715,7 +13719,7 @@
         <v>11</v>
       </c>
       <c r="D340" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E340" t="s">
         <v>15</v>
@@ -13750,7 +13754,7 @@
         <v>11</v>
       </c>
       <c r="D341" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E341" t="s">
         <v>15</v>
@@ -13785,7 +13789,7 @@
         <v>11</v>
       </c>
       <c r="D342" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E342" t="s">
         <v>15</v>
@@ -13820,7 +13824,7 @@
         <v>11</v>
       </c>
       <c r="D343" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E343" t="s">
         <v>15</v>
@@ -13855,7 +13859,7 @@
         <v>11</v>
       </c>
       <c r="D344" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E344" t="s">
         <v>15</v>
@@ -13890,7 +13894,7 @@
         <v>11</v>
       </c>
       <c r="D345" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E345" t="s">
         <v>15</v>
@@ -13925,7 +13929,7 @@
         <v>11</v>
       </c>
       <c r="D346" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E346" t="s">
         <v>15</v>
@@ -13960,7 +13964,7 @@
         <v>11</v>
       </c>
       <c r="D347" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E347" t="s">
         <v>15</v>
@@ -13995,7 +13999,7 @@
         <v>11</v>
       </c>
       <c r="D348" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E348" t="s">
         <v>15</v>
@@ -14030,7 +14034,7 @@
         <v>11</v>
       </c>
       <c r="D349" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E349" t="s">
         <v>15</v>
@@ -14065,7 +14069,7 @@
         <v>11</v>
       </c>
       <c r="D350" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E350" t="s">
         <v>15</v>
@@ -14100,7 +14104,7 @@
         <v>11</v>
       </c>
       <c r="D351" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E351" t="s">
         <v>15</v>
@@ -14135,7 +14139,7 @@
         <v>11</v>
       </c>
       <c r="D352" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E352" t="s">
         <v>15</v>
@@ -14170,7 +14174,7 @@
         <v>11</v>
       </c>
       <c r="D353" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E353" t="s">
         <v>15</v>
@@ -14205,7 +14209,7 @@
         <v>11</v>
       </c>
       <c r="D354" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E354" t="s">
         <v>15</v>
@@ -14240,7 +14244,7 @@
         <v>11</v>
       </c>
       <c r="D355" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E355" t="s">
         <v>15</v>
@@ -14275,7 +14279,7 @@
         <v>11</v>
       </c>
       <c r="D356" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E356" t="s">
         <v>15</v>
@@ -14310,7 +14314,7 @@
         <v>11</v>
       </c>
       <c r="D357" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E357" t="s">
         <v>15</v>
@@ -14345,7 +14349,7 @@
         <v>11</v>
       </c>
       <c r="D358" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E358" t="s">
         <v>15</v>
@@ -14380,7 +14384,7 @@
         <v>11</v>
       </c>
       <c r="D359" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E359" t="s">
         <v>15</v>
@@ -14415,7 +14419,7 @@
         <v>11</v>
       </c>
       <c r="D360" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E360" t="s">
         <v>15</v>
@@ -14450,7 +14454,7 @@
         <v>11</v>
       </c>
       <c r="D361" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E361" t="s">
         <v>15</v>
@@ -14485,7 +14489,7 @@
         <v>11</v>
       </c>
       <c r="D362" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E362" t="s">
         <v>15</v>
@@ -14520,7 +14524,7 @@
         <v>11</v>
       </c>
       <c r="D363" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E363" t="s">
         <v>15</v>
@@ -14555,7 +14559,7 @@
         <v>11</v>
       </c>
       <c r="D364" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E364" t="s">
         <v>15</v>
@@ -14590,7 +14594,7 @@
         <v>11</v>
       </c>
       <c r="D365" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E365" t="s">
         <v>15</v>
@@ -14625,7 +14629,7 @@
         <v>11</v>
       </c>
       <c r="D366" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E366" t="s">
         <v>15</v>
@@ -14660,7 +14664,7 @@
         <v>11</v>
       </c>
       <c r="D367" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E367" t="s">
         <v>15</v>
@@ -14695,7 +14699,7 @@
         <v>11</v>
       </c>
       <c r="D368" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E368" t="s">
         <v>15</v>
@@ -14730,7 +14734,7 @@
         <v>11</v>
       </c>
       <c r="D369" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E369" t="s">
         <v>15</v>
@@ -14765,7 +14769,7 @@
         <v>11</v>
       </c>
       <c r="D370" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E370" t="s">
         <v>15</v>
@@ -14800,7 +14804,7 @@
         <v>11</v>
       </c>
       <c r="D371" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E371" t="s">
         <v>15</v>
@@ -14835,7 +14839,7 @@
         <v>11</v>
       </c>
       <c r="D372" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E372" t="s">
         <v>15</v>
@@ -14870,7 +14874,7 @@
         <v>11</v>
       </c>
       <c r="D373" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E373" t="s">
         <v>15</v>
@@ -14905,7 +14909,7 @@
         <v>11</v>
       </c>
       <c r="D374" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E374" t="s">
         <v>15</v>
@@ -14940,7 +14944,7 @@
         <v>11</v>
       </c>
       <c r="D375" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E375" t="s">
         <v>15</v>
@@ -14975,7 +14979,7 @@
         <v>11</v>
       </c>
       <c r="D376" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E376" t="s">
         <v>15</v>
@@ -15010,7 +15014,7 @@
         <v>11</v>
       </c>
       <c r="D377" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E377" t="s">
         <v>15</v>
@@ -15045,7 +15049,7 @@
         <v>11</v>
       </c>
       <c r="D378" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E378" t="s">
         <v>15</v>
@@ -15080,7 +15084,7 @@
         <v>11</v>
       </c>
       <c r="D379" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E379" t="s">
         <v>15</v>
@@ -15115,7 +15119,7 @@
         <v>11</v>
       </c>
       <c r="D380" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E380" t="s">
         <v>15</v>
@@ -15150,7 +15154,7 @@
         <v>11</v>
       </c>
       <c r="D381" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E381" t="s">
         <v>15</v>
@@ -15185,7 +15189,7 @@
         <v>11</v>
       </c>
       <c r="D382" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E382" t="s">
         <v>15</v>
@@ -15220,7 +15224,7 @@
         <v>11</v>
       </c>
       <c r="D383" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E383" t="s">
         <v>15</v>
@@ -15255,7 +15259,7 @@
         <v>11</v>
       </c>
       <c r="D384" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E384" t="s">
         <v>15</v>
@@ -15290,7 +15294,7 @@
         <v>11</v>
       </c>
       <c r="D385" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E385" t="s">
         <v>15</v>
@@ -15325,7 +15329,7 @@
         <v>11</v>
       </c>
       <c r="D386" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E386" t="s">
         <v>15</v>
@@ -15360,7 +15364,7 @@
         <v>11</v>
       </c>
       <c r="D387" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E387" t="s">
         <v>15</v>
@@ -15395,7 +15399,7 @@
         <v>11</v>
       </c>
       <c r="D388" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E388" t="s">
         <v>15</v>
@@ -15430,7 +15434,7 @@
         <v>11</v>
       </c>
       <c r="D389" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E389" t="s">
         <v>15</v>
@@ -15465,7 +15469,7 @@
         <v>11</v>
       </c>
       <c r="D390" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E390" t="s">
         <v>15</v>
@@ -15500,7 +15504,7 @@
         <v>11</v>
       </c>
       <c r="D391" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E391" t="s">
         <v>15</v>
@@ -15535,7 +15539,7 @@
         <v>11</v>
       </c>
       <c r="D392" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E392" t="s">
         <v>15</v>
@@ -15570,7 +15574,7 @@
         <v>11</v>
       </c>
       <c r="D393" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E393" t="s">
         <v>15</v>
@@ -15605,7 +15609,7 @@
         <v>11</v>
       </c>
       <c r="D394" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E394" t="s">
         <v>15</v>
@@ -15640,7 +15644,7 @@
         <v>11</v>
       </c>
       <c r="D395" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E395" t="s">
         <v>15</v>
@@ -15675,7 +15679,7 @@
         <v>11</v>
       </c>
       <c r="D396" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E396" t="s">
         <v>15</v>
@@ -15710,7 +15714,7 @@
         <v>11</v>
       </c>
       <c r="D397" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E397" t="s">
         <v>15</v>
@@ -15745,7 +15749,7 @@
         <v>11</v>
       </c>
       <c r="D398" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E398" t="s">
         <v>15</v>
@@ -15780,7 +15784,7 @@
         <v>11</v>
       </c>
       <c r="D399" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E399" t="s">
         <v>15</v>
@@ -15815,7 +15819,7 @@
         <v>11</v>
       </c>
       <c r="D400" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E400" t="s">
         <v>15</v>
@@ -15850,7 +15854,7 @@
         <v>11</v>
       </c>
       <c r="D401" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E401" t="s">
         <v>15</v>
@@ -15885,7 +15889,7 @@
         <v>11</v>
       </c>
       <c r="D402" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E402" t="s">
         <v>15</v>
@@ -15920,7 +15924,7 @@
         <v>11</v>
       </c>
       <c r="D403" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E403" t="s">
         <v>15</v>
@@ -15955,7 +15959,7 @@
         <v>11</v>
       </c>
       <c r="D404" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E404" t="s">
         <v>15</v>
@@ -15990,7 +15994,7 @@
         <v>11</v>
       </c>
       <c r="D405" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E405" t="s">
         <v>15</v>
@@ -16025,7 +16029,7 @@
         <v>11</v>
       </c>
       <c r="D406" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E406" t="s">
         <v>15</v>
@@ -16060,7 +16064,7 @@
         <v>11</v>
       </c>
       <c r="D407" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E407" t="s">
         <v>15</v>
@@ -16095,7 +16099,7 @@
         <v>11</v>
       </c>
       <c r="D408" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E408" t="s">
         <v>15</v>
@@ -16130,7 +16134,7 @@
         <v>11</v>
       </c>
       <c r="D409" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E409" t="s">
         <v>15</v>
@@ -16165,7 +16169,7 @@
         <v>11</v>
       </c>
       <c r="D410" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E410" t="s">
         <v>15</v>
@@ -16200,7 +16204,7 @@
         <v>11</v>
       </c>
       <c r="D411" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E411" t="s">
         <v>15</v>
@@ -16235,7 +16239,7 @@
         <v>11</v>
       </c>
       <c r="D412" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E412" t="s">
         <v>15</v>
@@ -16270,7 +16274,7 @@
         <v>11</v>
       </c>
       <c r="D413" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E413" t="s">
         <v>15</v>
@@ -16305,7 +16309,7 @@
         <v>11</v>
       </c>
       <c r="D414" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E414" t="s">
         <v>15</v>
@@ -16340,7 +16344,7 @@
         <v>11</v>
       </c>
       <c r="D415" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E415" t="s">
         <v>15</v>
@@ -16375,7 +16379,7 @@
         <v>11</v>
       </c>
       <c r="D416" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E416" t="s">
         <v>15</v>
@@ -16410,7 +16414,7 @@
         <v>11</v>
       </c>
       <c r="D417" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E417" t="s">
         <v>15</v>
@@ -16445,7 +16449,7 @@
         <v>11</v>
       </c>
       <c r="D418" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E418" t="s">
         <v>15</v>
@@ -16480,7 +16484,7 @@
         <v>11</v>
       </c>
       <c r="D419" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E419" t="s">
         <v>15</v>
@@ -16515,7 +16519,7 @@
         <v>11</v>
       </c>
       <c r="D420" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E420" t="s">
         <v>15</v>
@@ -16550,7 +16554,7 @@
         <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E421" t="s">
         <v>15</v>
@@ -16585,7 +16589,7 @@
         <v>11</v>
       </c>
       <c r="D422" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E422" t="s">
         <v>15</v>
@@ -16620,7 +16624,7 @@
         <v>11</v>
       </c>
       <c r="D423" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E423" t="s">
         <v>15</v>
@@ -16655,7 +16659,7 @@
         <v>11</v>
       </c>
       <c r="D424" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E424" t="s">
         <v>15</v>
@@ -16690,7 +16694,7 @@
         <v>11</v>
       </c>
       <c r="D425" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E425" t="s">
         <v>15</v>
@@ -16725,7 +16729,7 @@
         <v>11</v>
       </c>
       <c r="D426" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E426" t="s">
         <v>15</v>
@@ -16760,7 +16764,7 @@
         <v>11</v>
       </c>
       <c r="D427" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E427" t="s">
         <v>15</v>
@@ -16795,7 +16799,7 @@
         <v>11</v>
       </c>
       <c r="D428" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E428" t="s">
         <v>15</v>
@@ -16830,7 +16834,7 @@
         <v>11</v>
       </c>
       <c r="D429" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E429" t="s">
         <v>15</v>
@@ -16865,7 +16869,7 @@
         <v>11</v>
       </c>
       <c r="D430" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E430" t="s">
         <v>15</v>
@@ -16900,7 +16904,7 @@
         <v>11</v>
       </c>
       <c r="D431" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E431" t="s">
         <v>15</v>
@@ -16935,7 +16939,7 @@
         <v>11</v>
       </c>
       <c r="D432" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E432" t="s">
         <v>15</v>
@@ -16970,7 +16974,7 @@
         <v>11</v>
       </c>
       <c r="D433" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E433" t="s">
         <v>15</v>
@@ -17005,7 +17009,7 @@
         <v>11</v>
       </c>
       <c r="D434" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E434" t="s">
         <v>15</v>
@@ -17040,7 +17044,7 @@
         <v>11</v>
       </c>
       <c r="D435" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E435" t="s">
         <v>15</v>
@@ -17075,7 +17079,7 @@
         <v>11</v>
       </c>
       <c r="D436" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E436" t="s">
         <v>15</v>
@@ -17110,7 +17114,7 @@
         <v>11</v>
       </c>
       <c r="D437" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E437" t="s">
         <v>15</v>
@@ -17145,7 +17149,7 @@
         <v>11</v>
       </c>
       <c r="D438" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E438" t="s">
         <v>15</v>
@@ -17180,7 +17184,7 @@
         <v>11</v>
       </c>
       <c r="D439" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E439" t="s">
         <v>15</v>
@@ -17215,7 +17219,7 @@
         <v>11</v>
       </c>
       <c r="D440" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E440" t="s">
         <v>15</v>
@@ -17250,7 +17254,7 @@
         <v>11</v>
       </c>
       <c r="D441" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E441" t="s">
         <v>15</v>
@@ -17285,7 +17289,7 @@
         <v>11</v>
       </c>
       <c r="D442" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E442" t="s">
         <v>15</v>
@@ -17320,7 +17324,7 @@
         <v>11</v>
       </c>
       <c r="D443" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E443" t="s">
         <v>15</v>
@@ -17355,7 +17359,7 @@
         <v>11</v>
       </c>
       <c r="D444" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E444" t="s">
         <v>15</v>
@@ -17390,7 +17394,7 @@
         <v>11</v>
       </c>
       <c r="D445" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E445" t="s">
         <v>15</v>
@@ -17425,7 +17429,7 @@
         <v>11</v>
       </c>
       <c r="D446" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E446" t="s">
         <v>15</v>
@@ -17460,7 +17464,7 @@
         <v>11</v>
       </c>
       <c r="D447" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E447" t="s">
         <v>15</v>
@@ -17495,7 +17499,7 @@
         <v>11</v>
       </c>
       <c r="D448" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E448" t="s">
         <v>15</v>
@@ -17530,7 +17534,7 @@
         <v>11</v>
       </c>
       <c r="D449" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E449" t="s">
         <v>15</v>
@@ -17565,7 +17569,7 @@
         <v>11</v>
       </c>
       <c r="D450" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E450" t="s">
         <v>15</v>
@@ -17600,7 +17604,7 @@
         <v>11</v>
       </c>
       <c r="D451" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E451" t="s">
         <v>15</v>
@@ -17635,7 +17639,7 @@
         <v>11</v>
       </c>
       <c r="D452" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E452" t="s">
         <v>15</v>
@@ -17670,7 +17674,7 @@
         <v>11</v>
       </c>
       <c r="D453" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E453" t="s">
         <v>15</v>
@@ -17705,7 +17709,7 @@
         <v>11</v>
       </c>
       <c r="D454" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E454" t="s">
         <v>15</v>
@@ -17740,7 +17744,7 @@
         <v>11</v>
       </c>
       <c r="D455" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E455" t="s">
         <v>15</v>
@@ -17775,7 +17779,7 @@
         <v>11</v>
       </c>
       <c r="D456" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E456" t="s">
         <v>15</v>
@@ -17810,7 +17814,7 @@
         <v>11</v>
       </c>
       <c r="D457" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E457" t="s">
         <v>15</v>
@@ -17845,7 +17849,7 @@
         <v>11</v>
       </c>
       <c r="D458" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E458" t="s">
         <v>15</v>
@@ -17880,7 +17884,7 @@
         <v>11</v>
       </c>
       <c r="D459" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E459" t="s">
         <v>15</v>
@@ -17915,7 +17919,7 @@
         <v>11</v>
       </c>
       <c r="D460" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E460" t="s">
         <v>15</v>
@@ -17950,7 +17954,7 @@
         <v>11</v>
       </c>
       <c r="D461" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E461" t="s">
         <v>15</v>
@@ -17985,7 +17989,7 @@
         <v>11</v>
       </c>
       <c r="D462" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E462" t="s">
         <v>15</v>
@@ -18020,7 +18024,7 @@
         <v>11</v>
       </c>
       <c r="D463" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E463" t="s">
         <v>15</v>
@@ -18055,7 +18059,7 @@
         <v>11</v>
       </c>
       <c r="D464" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E464" t="s">
         <v>15</v>
@@ -18090,7 +18094,7 @@
         <v>11</v>
       </c>
       <c r="D465" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E465" t="s">
         <v>15</v>
@@ -18125,7 +18129,7 @@
         <v>11</v>
       </c>
       <c r="D466" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E466" t="s">
         <v>15</v>
@@ -18168,6 +18172,6 @@
     <hyperlink ref="D2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
+++ b/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12300"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Kênh YouTube" state="visible" r:id="rId4"/>
+    <sheet name="Kênh YouTube" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5111" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5099" uniqueCount="484">
   <si>
     <t>EMAIL</t>
   </si>
@@ -67,7 +67,7 @@
     <t>https://www.youtube.com/watch?v=hX45BtIdlIA</t>
   </si>
   <si>
-    <t xml:space="preserve">『修羅子のドロドロ人生朗読』では
+    <t>『修羅子のドロドロ人生朗読』では
 日常で起こる様々なスカッとする話や修羅場な体験談を
 投稿しております。
 是非チャンネル登録をお願いいたします！
@@ -1527,28 +1527,36 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <color theme="10"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <color theme="1"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1574,18 +1582,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1644,7 +1655,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1679,7 +1690,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1853,13 +1864,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K466"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1872,7 +1889,7 @@
     <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1907,7 +1924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1931,7 +1948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1960,7 +1977,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1992,7 +2009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2021,7 +2038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2053,7 +2070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2088,7 +2105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2098,12 +2115,9 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
@@ -2119,11 +2133,11 @@
       <c r="J8" t="s">
         <v>11</v>
       </c>
-      <c r="K8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2133,12 +2147,9 @@
       <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
       <c r="F9" t="s">
         <v>11</v>
       </c>
@@ -2154,11 +2165,11 @@
       <c r="J9" t="s">
         <v>11</v>
       </c>
-      <c r="K9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2168,12 +2179,9 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
@@ -2189,11 +2197,11 @@
       <c r="J10" t="s">
         <v>11</v>
       </c>
-      <c r="K10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2203,12 +2211,9 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
       <c r="F11" t="s">
         <v>11</v>
       </c>
@@ -2224,11 +2229,11 @@
       <c r="J11" t="s">
         <v>11</v>
       </c>
-      <c r="K11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2238,12 +2243,9 @@
       <c r="C12" t="s">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
       <c r="F12" t="s">
         <v>11</v>
       </c>
@@ -2259,11 +2261,11 @@
       <c r="J12" t="s">
         <v>11</v>
       </c>
-      <c r="K12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2273,12 +2275,9 @@
       <c r="C13" t="s">
         <v>11</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
       <c r="F13" t="s">
         <v>11</v>
       </c>
@@ -2294,11 +2293,11 @@
       <c r="J13" t="s">
         <v>11</v>
       </c>
-      <c r="K13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2333,7 +2332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2368,7 +2367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2403,7 +2402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2473,7 +2472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2508,7 +2507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2543,7 +2542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -2578,7 +2577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -2613,7 +2612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2683,7 +2682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -2718,7 +2717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -2753,7 +2752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -2788,7 +2787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -2823,7 +2822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -2858,7 +2857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -2893,7 +2892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -2928,7 +2927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -2963,7 +2962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -2998,7 +2997,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3033,7 +3032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -3103,7 +3102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -3138,7 +3137,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -3173,7 +3172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -3208,7 +3207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -3243,7 +3242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -3278,7 +3277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -3348,7 +3347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -3383,7 +3382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -3418,7 +3417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -3453,7 +3452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -3488,7 +3487,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -3523,7 +3522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -3558,7 +3557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -3593,7 +3592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -3628,7 +3627,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -3663,7 +3662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -3698,7 +3697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -3733,7 +3732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -3768,7 +3767,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -3803,7 +3802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -3838,7 +3837,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -3873,7 +3872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -3908,7 +3907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -3943,7 +3942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -3978,7 +3977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -4013,7 +4012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -4048,7 +4047,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -4083,7 +4082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -4118,7 +4117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -4188,7 +4187,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -4223,7 +4222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -4258,7 +4257,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -4293,7 +4292,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -4328,7 +4327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -4363,7 +4362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -4398,7 +4397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -4433,7 +4432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -4503,7 +4502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -4538,7 +4537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -4573,7 +4572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -4608,7 +4607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -4643,7 +4642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -4678,7 +4677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -4713,7 +4712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -4748,7 +4747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -4783,7 +4782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -4818,7 +4817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -4853,7 +4852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -4888,7 +4887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -4923,7 +4922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -4958,7 +4957,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -4993,7 +4992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -5028,7 +5027,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -5063,7 +5062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -5098,7 +5097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -5133,7 +5132,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -5168,7 +5167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -5203,7 +5202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -5238,7 +5237,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -5273,7 +5272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -5308,7 +5307,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -5343,7 +5342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -5378,7 +5377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -5413,7 +5412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -5448,7 +5447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -5483,7 +5482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -5518,7 +5517,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -5553,7 +5552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -5588,7 +5587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -5623,7 +5622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -5658,7 +5657,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11">
       <c r="A110" t="s">
         <v>11</v>
       </c>
@@ -5693,7 +5692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11">
       <c r="A111" t="s">
         <v>11</v>
       </c>
@@ -5728,7 +5727,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -5763,7 +5762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -5798,7 +5797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -5833,7 +5832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -5868,7 +5867,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -5903,7 +5902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -5938,7 +5937,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -5973,7 +5972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -6008,7 +6007,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -6043,7 +6042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -6078,7 +6077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -6113,7 +6112,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -6148,7 +6147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -6183,7 +6182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -6218,7 +6217,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -6253,7 +6252,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -6288,7 +6287,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -6323,7 +6322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -6358,7 +6357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -6393,7 +6392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11">
       <c r="A131" t="s">
         <v>11</v>
       </c>
@@ -6428,7 +6427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11">
       <c r="A132" t="s">
         <v>11</v>
       </c>
@@ -6463,7 +6462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11">
       <c r="A133" t="s">
         <v>11</v>
       </c>
@@ -6498,7 +6497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11">
       <c r="A134" t="s">
         <v>11</v>
       </c>
@@ -6533,7 +6532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11">
       <c r="A135" t="s">
         <v>11</v>
       </c>
@@ -6568,7 +6567,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11">
       <c r="A136" t="s">
         <v>11</v>
       </c>
@@ -6603,7 +6602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11">
       <c r="A137" t="s">
         <v>11</v>
       </c>
@@ -6638,7 +6637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11">
       <c r="A138" t="s">
         <v>11</v>
       </c>
@@ -6673,7 +6672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11">
       <c r="A139" t="s">
         <v>11</v>
       </c>
@@ -6708,7 +6707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11">
       <c r="A140" t="s">
         <v>11</v>
       </c>
@@ -6743,7 +6742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11">
       <c r="A141" t="s">
         <v>11</v>
       </c>
@@ -6778,7 +6777,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -6813,7 +6812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11">
       <c r="A143" t="s">
         <v>11</v>
       </c>
@@ -6848,7 +6847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11">
       <c r="A144" t="s">
         <v>11</v>
       </c>
@@ -6883,7 +6882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11">
       <c r="A145" t="s">
         <v>11</v>
       </c>
@@ -6918,7 +6917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11">
       <c r="A146" t="s">
         <v>11</v>
       </c>
@@ -6953,7 +6952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11">
       <c r="A147" t="s">
         <v>11</v>
       </c>
@@ -6988,7 +6987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11">
       <c r="A148" t="s">
         <v>11</v>
       </c>
@@ -7023,7 +7022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11">
       <c r="A149" t="s">
         <v>11</v>
       </c>
@@ -7058,7 +7057,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11">
       <c r="A150" t="s">
         <v>11</v>
       </c>
@@ -7093,7 +7092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11">
       <c r="A151" t="s">
         <v>11</v>
       </c>
@@ -7128,7 +7127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -7163,7 +7162,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11">
       <c r="A153" t="s">
         <v>11</v>
       </c>
@@ -7198,7 +7197,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11">
       <c r="A154" t="s">
         <v>11</v>
       </c>
@@ -7233,7 +7232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11">
       <c r="A155" t="s">
         <v>11</v>
       </c>
@@ -7268,7 +7267,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11">
       <c r="A156" t="s">
         <v>11</v>
       </c>
@@ -7303,7 +7302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11">
       <c r="A157" t="s">
         <v>11</v>
       </c>
@@ -7338,7 +7337,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11">
       <c r="A158" t="s">
         <v>11</v>
       </c>
@@ -7373,7 +7372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -7408,7 +7407,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -7443,7 +7442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11">
       <c r="A161" t="s">
         <v>11</v>
       </c>
@@ -7478,7 +7477,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -7513,7 +7512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11">
       <c r="A163" t="s">
         <v>11</v>
       </c>
@@ -7548,7 +7547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11">
       <c r="A164" t="s">
         <v>11</v>
       </c>
@@ -7583,7 +7582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11">
       <c r="A165" t="s">
         <v>11</v>
       </c>
@@ -7618,7 +7617,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -7653,7 +7652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -7688,7 +7687,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11">
       <c r="A168" t="s">
         <v>11</v>
       </c>
@@ -7723,7 +7722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -7758,7 +7757,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11">
       <c r="A170" t="s">
         <v>11</v>
       </c>
@@ -7793,7 +7792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11">
       <c r="A171" t="s">
         <v>11</v>
       </c>
@@ -7828,7 +7827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11">
       <c r="A172" t="s">
         <v>11</v>
       </c>
@@ -7863,7 +7862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11">
       <c r="A173" t="s">
         <v>11</v>
       </c>
@@ -7898,7 +7897,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11">
       <c r="A174" t="s">
         <v>11</v>
       </c>
@@ -7933,7 +7932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11">
       <c r="A175" t="s">
         <v>11</v>
       </c>
@@ -7968,7 +7967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11">
       <c r="A176" t="s">
         <v>11</v>
       </c>
@@ -8003,7 +8002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11">
       <c r="A177" t="s">
         <v>11</v>
       </c>
@@ -8038,7 +8037,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11">
       <c r="A178" t="s">
         <v>11</v>
       </c>
@@ -8073,7 +8072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11">
       <c r="A179" t="s">
         <v>11</v>
       </c>
@@ -8108,7 +8107,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11">
       <c r="A180" t="s">
         <v>11</v>
       </c>
@@ -8143,7 +8142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11">
       <c r="A181" t="s">
         <v>11</v>
       </c>
@@ -8178,7 +8177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11">
       <c r="A182" t="s">
         <v>11</v>
       </c>
@@ -8213,7 +8212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11">
       <c r="A183" t="s">
         <v>11</v>
       </c>
@@ -8248,7 +8247,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11">
       <c r="A184" t="s">
         <v>11</v>
       </c>
@@ -8283,7 +8282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11">
       <c r="A185" t="s">
         <v>11</v>
       </c>
@@ -8318,7 +8317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11">
       <c r="A186" t="s">
         <v>11</v>
       </c>
@@ -8353,7 +8352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11">
       <c r="A187" t="s">
         <v>11</v>
       </c>
@@ -8388,7 +8387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11">
       <c r="A188" t="s">
         <v>11</v>
       </c>
@@ -8423,7 +8422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11">
       <c r="A189" t="s">
         <v>11</v>
       </c>
@@ -8458,7 +8457,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11">
       <c r="A190" t="s">
         <v>11</v>
       </c>
@@ -8493,7 +8492,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11">
       <c r="A191" t="s">
         <v>11</v>
       </c>
@@ -8528,7 +8527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11">
       <c r="A192" t="s">
         <v>11</v>
       </c>
@@ -8563,7 +8562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11">
       <c r="A193" t="s">
         <v>11</v>
       </c>
@@ -8598,7 +8597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11">
       <c r="A194" t="s">
         <v>11</v>
       </c>
@@ -8633,7 +8632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11">
       <c r="A195" t="s">
         <v>11</v>
       </c>
@@ -8668,7 +8667,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11">
       <c r="A196" t="s">
         <v>11</v>
       </c>
@@ -8703,7 +8702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11">
       <c r="A197" t="s">
         <v>11</v>
       </c>
@@ -8738,7 +8737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11">
       <c r="A198" t="s">
         <v>11</v>
       </c>
@@ -8773,7 +8772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11">
       <c r="A199" t="s">
         <v>11</v>
       </c>
@@ -8808,7 +8807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11">
       <c r="A200" t="s">
         <v>11</v>
       </c>
@@ -8843,7 +8842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11">
       <c r="A201" t="s">
         <v>11</v>
       </c>
@@ -8878,7 +8877,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11">
       <c r="A202" t="s">
         <v>11</v>
       </c>
@@ -8913,7 +8912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11">
       <c r="A203" t="s">
         <v>11</v>
       </c>
@@ -8948,7 +8947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11">
       <c r="A204" t="s">
         <v>11</v>
       </c>
@@ -8983,7 +8982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11">
       <c r="A205" t="s">
         <v>11</v>
       </c>
@@ -9018,7 +9017,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11">
       <c r="A206" t="s">
         <v>11</v>
       </c>
@@ -9053,7 +9052,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11">
       <c r="A207" t="s">
         <v>11</v>
       </c>
@@ -9088,7 +9087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11">
       <c r="A208" t="s">
         <v>11</v>
       </c>
@@ -9123,7 +9122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11">
       <c r="A209" t="s">
         <v>11</v>
       </c>
@@ -9158,7 +9157,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11">
       <c r="A210" t="s">
         <v>11</v>
       </c>
@@ -9193,7 +9192,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11">
       <c r="A211" t="s">
         <v>11</v>
       </c>
@@ -9228,7 +9227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11">
       <c r="A212" t="s">
         <v>11</v>
       </c>
@@ -9263,7 +9262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11">
       <c r="A213" t="s">
         <v>11</v>
       </c>
@@ -9298,7 +9297,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11">
       <c r="A214" t="s">
         <v>11</v>
       </c>
@@ -9333,7 +9332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11">
       <c r="A215" t="s">
         <v>11</v>
       </c>
@@ -9368,7 +9367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11">
       <c r="A216" t="s">
         <v>11</v>
       </c>
@@ -9403,7 +9402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11">
       <c r="A217" t="s">
         <v>11</v>
       </c>
@@ -9438,7 +9437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11">
       <c r="A218" t="s">
         <v>11</v>
       </c>
@@ -9473,7 +9472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11">
       <c r="A219" t="s">
         <v>11</v>
       </c>
@@ -9508,7 +9507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11">
       <c r="A220" t="s">
         <v>11</v>
       </c>
@@ -9543,7 +9542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11">
       <c r="A221" t="s">
         <v>11</v>
       </c>
@@ -9578,7 +9577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11">
       <c r="A222" t="s">
         <v>11</v>
       </c>
@@ -9613,7 +9612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11">
       <c r="A223" t="s">
         <v>11</v>
       </c>
@@ -9648,7 +9647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11">
       <c r="A224" t="s">
         <v>11</v>
       </c>
@@ -9683,7 +9682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11">
       <c r="A225" t="s">
         <v>11</v>
       </c>
@@ -9718,7 +9717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11">
       <c r="A226" t="s">
         <v>11</v>
       </c>
@@ -9753,7 +9752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11">
       <c r="A227" t="s">
         <v>11</v>
       </c>
@@ -9788,7 +9787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11">
       <c r="A228" t="s">
         <v>11</v>
       </c>
@@ -9823,7 +9822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11">
       <c r="A229" t="s">
         <v>11</v>
       </c>
@@ -9858,7 +9857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11">
       <c r="A230" t="s">
         <v>11</v>
       </c>
@@ -9893,7 +9892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11">
       <c r="A231" t="s">
         <v>11</v>
       </c>
@@ -9928,7 +9927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11">
       <c r="A232" t="s">
         <v>11</v>
       </c>
@@ -9963,7 +9962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11">
       <c r="A233" t="s">
         <v>11</v>
       </c>
@@ -9998,7 +9997,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11">
       <c r="A234" t="s">
         <v>11</v>
       </c>
@@ -10033,7 +10032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11">
       <c r="A235" t="s">
         <v>11</v>
       </c>
@@ -10068,7 +10067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11">
       <c r="A236" t="s">
         <v>11</v>
       </c>
@@ -10103,7 +10102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11">
       <c r="A237" t="s">
         <v>11</v>
       </c>
@@ -10138,7 +10137,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11">
       <c r="A238" t="s">
         <v>11</v>
       </c>
@@ -10173,7 +10172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11">
       <c r="A239" t="s">
         <v>11</v>
       </c>
@@ -10208,7 +10207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11">
       <c r="A240" t="s">
         <v>11</v>
       </c>
@@ -10243,7 +10242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11">
       <c r="A241" t="s">
         <v>11</v>
       </c>
@@ -10278,7 +10277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11">
       <c r="A242" t="s">
         <v>11</v>
       </c>
@@ -10313,7 +10312,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11">
       <c r="A243" t="s">
         <v>11</v>
       </c>
@@ -10348,7 +10347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11">
       <c r="A244" t="s">
         <v>11</v>
       </c>
@@ -10383,7 +10382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11">
       <c r="A245" t="s">
         <v>11</v>
       </c>
@@ -10418,7 +10417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11">
       <c r="A246" t="s">
         <v>11</v>
       </c>
@@ -10453,7 +10452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11">
       <c r="A247" t="s">
         <v>11</v>
       </c>
@@ -10488,7 +10487,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11">
       <c r="A248" t="s">
         <v>11</v>
       </c>
@@ -10523,7 +10522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11">
       <c r="A249" t="s">
         <v>11</v>
       </c>
@@ -10558,7 +10557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11">
       <c r="A250" t="s">
         <v>11</v>
       </c>
@@ -10593,7 +10592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11">
       <c r="A251" t="s">
         <v>11</v>
       </c>
@@ -10628,7 +10627,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11">
       <c r="A252" t="s">
         <v>11</v>
       </c>
@@ -10663,7 +10662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11">
       <c r="A253" t="s">
         <v>11</v>
       </c>
@@ -10698,7 +10697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11">
       <c r="A254" t="s">
         <v>11</v>
       </c>
@@ -10733,7 +10732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11">
       <c r="A255" t="s">
         <v>11</v>
       </c>
@@ -10768,7 +10767,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11">
       <c r="A256" t="s">
         <v>11</v>
       </c>
@@ -10803,7 +10802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11">
       <c r="A257" t="s">
         <v>11</v>
       </c>
@@ -10838,7 +10837,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11">
       <c r="A258" t="s">
         <v>11</v>
       </c>
@@ -10873,7 +10872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11">
       <c r="A259" t="s">
         <v>11</v>
       </c>
@@ -10908,7 +10907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11">
       <c r="A260" t="s">
         <v>11</v>
       </c>
@@ -10943,7 +10942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11">
       <c r="A261" t="s">
         <v>11</v>
       </c>
@@ -10978,7 +10977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -11013,7 +11012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11">
       <c r="A263" t="s">
         <v>11</v>
       </c>
@@ -11048,7 +11047,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11">
       <c r="A264" t="s">
         <v>11</v>
       </c>
@@ -11083,7 +11082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11">
       <c r="A265" t="s">
         <v>11</v>
       </c>
@@ -11118,7 +11117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11">
       <c r="A266" t="s">
         <v>11</v>
       </c>
@@ -11153,7 +11152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11">
       <c r="A267" t="s">
         <v>11</v>
       </c>
@@ -11188,7 +11187,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11">
       <c r="A268" t="s">
         <v>11</v>
       </c>
@@ -11223,7 +11222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11">
       <c r="A269" t="s">
         <v>11</v>
       </c>
@@ -11258,7 +11257,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11">
       <c r="A270" t="s">
         <v>11</v>
       </c>
@@ -11293,7 +11292,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11">
       <c r="A271" t="s">
         <v>11</v>
       </c>
@@ -11328,7 +11327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11">
       <c r="A272" t="s">
         <v>11</v>
       </c>
@@ -11363,7 +11362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11">
       <c r="A273" t="s">
         <v>11</v>
       </c>
@@ -11398,7 +11397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11">
       <c r="A274" t="s">
         <v>11</v>
       </c>
@@ -11433,7 +11432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11">
       <c r="A275" t="s">
         <v>11</v>
       </c>
@@ -11468,7 +11467,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11">
       <c r="A276" t="s">
         <v>11</v>
       </c>
@@ -11503,7 +11502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11">
       <c r="A277" t="s">
         <v>11</v>
       </c>
@@ -11538,7 +11537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11">
       <c r="A278" t="s">
         <v>11</v>
       </c>
@@ -11573,7 +11572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11">
       <c r="A279" t="s">
         <v>11</v>
       </c>
@@ -11608,7 +11607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11">
       <c r="A280" t="s">
         <v>11</v>
       </c>
@@ -11643,7 +11642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11">
       <c r="A281" t="s">
         <v>11</v>
       </c>
@@ -11678,7 +11677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11">
       <c r="A282" t="s">
         <v>11</v>
       </c>
@@ -11713,7 +11712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11">
       <c r="A283" t="s">
         <v>11</v>
       </c>
@@ -11748,7 +11747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11">
       <c r="A284" t="s">
         <v>11</v>
       </c>
@@ -11783,7 +11782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11">
       <c r="A285" t="s">
         <v>11</v>
       </c>
@@ -11818,7 +11817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11">
       <c r="A286" t="s">
         <v>11</v>
       </c>
@@ -11853,7 +11852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11">
       <c r="A287" t="s">
         <v>11</v>
       </c>
@@ -11888,7 +11887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11">
       <c r="A288" t="s">
         <v>11</v>
       </c>
@@ -11923,7 +11922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11">
       <c r="A289" t="s">
         <v>11</v>
       </c>
@@ -11958,7 +11957,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11">
       <c r="A290" t="s">
         <v>11</v>
       </c>
@@ -11993,7 +11992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11">
       <c r="A291" t="s">
         <v>11</v>
       </c>
@@ -12028,7 +12027,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11">
       <c r="A292" t="s">
         <v>11</v>
       </c>
@@ -12063,7 +12062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11">
       <c r="A293" t="s">
         <v>11</v>
       </c>
@@ -12098,7 +12097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11">
       <c r="A294" t="s">
         <v>11</v>
       </c>
@@ -12133,7 +12132,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11">
       <c r="A295" t="s">
         <v>11</v>
       </c>
@@ -12168,7 +12167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11">
       <c r="A296" t="s">
         <v>11</v>
       </c>
@@ -12203,7 +12202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11">
       <c r="A297" t="s">
         <v>11</v>
       </c>
@@ -12238,7 +12237,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11">
       <c r="A298" t="s">
         <v>11</v>
       </c>
@@ -12273,7 +12272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11">
       <c r="A299" t="s">
         <v>11</v>
       </c>
@@ -12308,7 +12307,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11">
       <c r="A300" t="s">
         <v>11</v>
       </c>
@@ -12343,7 +12342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11">
       <c r="A301" t="s">
         <v>11</v>
       </c>
@@ -12378,7 +12377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11">
       <c r="A302" t="s">
         <v>11</v>
       </c>
@@ -12413,7 +12412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11">
       <c r="A303" t="s">
         <v>11</v>
       </c>
@@ -12448,7 +12447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11">
       <c r="A304" t="s">
         <v>11</v>
       </c>
@@ -12483,7 +12482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11">
       <c r="A305" t="s">
         <v>11</v>
       </c>
@@ -12518,7 +12517,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11">
       <c r="A306" t="s">
         <v>11</v>
       </c>
@@ -12553,7 +12552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11">
       <c r="A307" t="s">
         <v>11</v>
       </c>
@@ -12588,7 +12587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11">
       <c r="A308" t="s">
         <v>11</v>
       </c>
@@ -12623,7 +12622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11">
       <c r="A309" t="s">
         <v>11</v>
       </c>
@@ -12658,7 +12657,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11">
       <c r="A310" t="s">
         <v>11</v>
       </c>
@@ -12693,7 +12692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11">
       <c r="A311" t="s">
         <v>11</v>
       </c>
@@ -12728,7 +12727,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11">
       <c r="A312" t="s">
         <v>11</v>
       </c>
@@ -12763,7 +12762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11">
       <c r="A313" t="s">
         <v>11</v>
       </c>
@@ -12798,7 +12797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11">
       <c r="A314" t="s">
         <v>11</v>
       </c>
@@ -12833,7 +12832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11">
       <c r="A315" t="s">
         <v>11</v>
       </c>
@@ -12868,7 +12867,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11">
       <c r="A316" t="s">
         <v>11</v>
       </c>
@@ -12903,7 +12902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11">
       <c r="A317" t="s">
         <v>11</v>
       </c>
@@ -12938,7 +12937,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11">
       <c r="A318" t="s">
         <v>11</v>
       </c>
@@ -12973,7 +12972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11">
       <c r="A319" t="s">
         <v>11</v>
       </c>
@@ -13008,7 +13007,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11">
       <c r="A320" t="s">
         <v>11</v>
       </c>
@@ -13043,7 +13042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11">
       <c r="A321" t="s">
         <v>11</v>
       </c>
@@ -13078,7 +13077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11">
       <c r="A322" t="s">
         <v>11</v>
       </c>
@@ -13113,7 +13112,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11">
       <c r="A323" t="s">
         <v>11</v>
       </c>
@@ -13148,7 +13147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11">
       <c r="A324" t="s">
         <v>11</v>
       </c>
@@ -13183,7 +13182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11">
       <c r="A325" t="s">
         <v>11</v>
       </c>
@@ -13218,7 +13217,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11">
       <c r="A326" t="s">
         <v>11</v>
       </c>
@@ -13253,7 +13252,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11">
       <c r="A327" t="s">
         <v>11</v>
       </c>
@@ -13288,7 +13287,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11">
       <c r="A328" t="s">
         <v>11</v>
       </c>
@@ -13323,7 +13322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11">
       <c r="A329" t="s">
         <v>11</v>
       </c>
@@ -13358,7 +13357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11">
       <c r="A330" t="s">
         <v>11</v>
       </c>
@@ -13393,7 +13392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11">
       <c r="A331" t="s">
         <v>11</v>
       </c>
@@ -13428,7 +13427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11">
       <c r="A332" t="s">
         <v>11</v>
       </c>
@@ -13463,7 +13462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11">
       <c r="A333" t="s">
         <v>11</v>
       </c>
@@ -13498,7 +13497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11">
       <c r="A334" t="s">
         <v>11</v>
       </c>
@@ -13533,7 +13532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11">
       <c r="A335" t="s">
         <v>11</v>
       </c>
@@ -13568,7 +13567,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11">
       <c r="A336" t="s">
         <v>11</v>
       </c>
@@ -13603,7 +13602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11">
       <c r="A337" t="s">
         <v>11</v>
       </c>
@@ -13638,7 +13637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11">
       <c r="A338" t="s">
         <v>11</v>
       </c>
@@ -13673,7 +13672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11">
       <c r="A339" t="s">
         <v>11</v>
       </c>
@@ -13708,7 +13707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11">
       <c r="A340" t="s">
         <v>11</v>
       </c>
@@ -13743,7 +13742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11">
       <c r="A341" t="s">
         <v>11</v>
       </c>
@@ -13778,7 +13777,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11">
       <c r="A342" t="s">
         <v>11</v>
       </c>
@@ -13813,7 +13812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11">
       <c r="A343" t="s">
         <v>11</v>
       </c>
@@ -13848,7 +13847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11">
       <c r="A344" t="s">
         <v>11</v>
       </c>
@@ -13883,7 +13882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11">
       <c r="A345" t="s">
         <v>11</v>
       </c>
@@ -13918,7 +13917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11">
       <c r="A346" t="s">
         <v>11</v>
       </c>
@@ -13953,7 +13952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11">
       <c r="A347" t="s">
         <v>11</v>
       </c>
@@ -13988,7 +13987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11">
       <c r="A348" t="s">
         <v>11</v>
       </c>
@@ -14023,7 +14022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11">
       <c r="A349" t="s">
         <v>11</v>
       </c>
@@ -14058,7 +14057,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11">
       <c r="A350" t="s">
         <v>11</v>
       </c>
@@ -14093,7 +14092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11">
       <c r="A351" t="s">
         <v>11</v>
       </c>
@@ -14128,7 +14127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11">
       <c r="A352" t="s">
         <v>11</v>
       </c>
@@ -14163,7 +14162,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11">
       <c r="A353" t="s">
         <v>11</v>
       </c>
@@ -14198,7 +14197,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11">
       <c r="A354" t="s">
         <v>11</v>
       </c>
@@ -14233,7 +14232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11">
       <c r="A355" t="s">
         <v>11</v>
       </c>
@@ -14268,7 +14267,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11">
       <c r="A356" t="s">
         <v>11</v>
       </c>
@@ -14303,7 +14302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11">
       <c r="A357" t="s">
         <v>11</v>
       </c>
@@ -14338,7 +14337,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11">
       <c r="A358" t="s">
         <v>11</v>
       </c>
@@ -14373,7 +14372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11">
       <c r="A359" t="s">
         <v>11</v>
       </c>
@@ -14408,7 +14407,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11">
       <c r="A360" t="s">
         <v>11</v>
       </c>
@@ -14443,7 +14442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11">
       <c r="A361" t="s">
         <v>11</v>
       </c>
@@ -14478,7 +14477,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11">
       <c r="A362" t="s">
         <v>11</v>
       </c>
@@ -14513,7 +14512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11">
       <c r="A363" t="s">
         <v>11</v>
       </c>
@@ -14548,7 +14547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11">
       <c r="A364" t="s">
         <v>11</v>
       </c>
@@ -14583,7 +14582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11">
       <c r="A365" t="s">
         <v>11</v>
       </c>
@@ -14618,7 +14617,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11">
       <c r="A366" t="s">
         <v>11</v>
       </c>
@@ -14653,7 +14652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11">
       <c r="A367" t="s">
         <v>11</v>
       </c>
@@ -14688,7 +14687,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11">
       <c r="A368" t="s">
         <v>11</v>
       </c>
@@ -14723,7 +14722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11">
       <c r="A369" t="s">
         <v>11</v>
       </c>
@@ -14758,7 +14757,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11">
       <c r="A370" t="s">
         <v>11</v>
       </c>
@@ -14793,7 +14792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11">
       <c r="A371" t="s">
         <v>11</v>
       </c>
@@ -14828,7 +14827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11">
       <c r="A372" t="s">
         <v>11</v>
       </c>
@@ -14863,7 +14862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11">
       <c r="A373" t="s">
         <v>11</v>
       </c>
@@ -14898,7 +14897,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11">
       <c r="A374" t="s">
         <v>11</v>
       </c>
@@ -14933,7 +14932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11">
       <c r="A375" t="s">
         <v>11</v>
       </c>
@@ -14968,7 +14967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11">
       <c r="A376" t="s">
         <v>11</v>
       </c>
@@ -15003,7 +15002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11">
       <c r="A377" t="s">
         <v>11</v>
       </c>
@@ -15038,7 +15037,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11">
       <c r="A378" t="s">
         <v>11</v>
       </c>
@@ -15073,7 +15072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11">
       <c r="A379" t="s">
         <v>11</v>
       </c>
@@ -15108,7 +15107,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11">
       <c r="A380" t="s">
         <v>11</v>
       </c>
@@ -15143,7 +15142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11">
       <c r="A381" t="s">
         <v>11</v>
       </c>
@@ -15178,7 +15177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11">
       <c r="A382" t="s">
         <v>11</v>
       </c>
@@ -15213,7 +15212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11">
       <c r="A383" t="s">
         <v>11</v>
       </c>
@@ -15248,7 +15247,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11">
       <c r="A384" t="s">
         <v>11</v>
       </c>
@@ -15283,7 +15282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11">
       <c r="A385" t="s">
         <v>11</v>
       </c>
@@ -15318,7 +15317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11">
       <c r="A386" t="s">
         <v>11</v>
       </c>
@@ -15353,7 +15352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11">
       <c r="A387" t="s">
         <v>11</v>
       </c>
@@ -15388,7 +15387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11">
       <c r="A388" t="s">
         <v>11</v>
       </c>
@@ -15423,7 +15422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11">
       <c r="A389" t="s">
         <v>11</v>
       </c>
@@ -15458,7 +15457,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11">
       <c r="A390" t="s">
         <v>11</v>
       </c>
@@ -15493,7 +15492,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11">
       <c r="A391" t="s">
         <v>11</v>
       </c>
@@ -15528,7 +15527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11">
       <c r="A392" t="s">
         <v>11</v>
       </c>
@@ -15563,7 +15562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11">
       <c r="A393" t="s">
         <v>11</v>
       </c>
@@ -15598,7 +15597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11">
       <c r="A394" t="s">
         <v>11</v>
       </c>
@@ -15633,7 +15632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11">
       <c r="A395" t="s">
         <v>11</v>
       </c>
@@ -15668,7 +15667,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11">
       <c r="A396" t="s">
         <v>11</v>
       </c>
@@ -15703,7 +15702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11">
       <c r="A397" t="s">
         <v>11</v>
       </c>
@@ -15738,7 +15737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11">
       <c r="A398" t="s">
         <v>11</v>
       </c>
@@ -15773,7 +15772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11">
       <c r="A399" t="s">
         <v>11</v>
       </c>
@@ -15808,7 +15807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11">
       <c r="A400" t="s">
         <v>11</v>
       </c>
@@ -15843,7 +15842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11">
       <c r="A401" t="s">
         <v>11</v>
       </c>
@@ -15878,7 +15877,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11">
       <c r="A402" t="s">
         <v>11</v>
       </c>
@@ -15913,7 +15912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11">
       <c r="A403" t="s">
         <v>11</v>
       </c>
@@ -15948,7 +15947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11">
       <c r="A404" t="s">
         <v>11</v>
       </c>
@@ -15983,7 +15982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:11">
       <c r="A405" t="s">
         <v>11</v>
       </c>
@@ -16018,7 +16017,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11">
       <c r="A406" t="s">
         <v>11</v>
       </c>
@@ -16053,7 +16052,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11">
       <c r="A407" t="s">
         <v>11</v>
       </c>
@@ -16088,7 +16087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11">
       <c r="A408" t="s">
         <v>11</v>
       </c>
@@ -16123,7 +16122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11">
       <c r="A409" t="s">
         <v>11</v>
       </c>
@@ -16158,7 +16157,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11">
       <c r="A410" t="s">
         <v>11</v>
       </c>
@@ -16193,7 +16192,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11">
       <c r="A411" t="s">
         <v>11</v>
       </c>
@@ -16228,7 +16227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11">
       <c r="A412" t="s">
         <v>11</v>
       </c>
@@ -16263,7 +16262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11">
       <c r="A413" t="s">
         <v>11</v>
       </c>
@@ -16298,7 +16297,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11">
       <c r="A414" t="s">
         <v>11</v>
       </c>
@@ -16333,7 +16332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11">
       <c r="A415" t="s">
         <v>11</v>
       </c>
@@ -16368,7 +16367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11">
       <c r="A416" t="s">
         <v>11</v>
       </c>
@@ -16403,7 +16402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11">
       <c r="A417" t="s">
         <v>11</v>
       </c>
@@ -16438,7 +16437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11">
       <c r="A418" t="s">
         <v>11</v>
       </c>
@@ -16473,7 +16472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11">
       <c r="A419" t="s">
         <v>11</v>
       </c>
@@ -16508,7 +16507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11">
       <c r="A420" t="s">
         <v>11</v>
       </c>
@@ -16543,7 +16542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11">
       <c r="A421" t="s">
         <v>11</v>
       </c>
@@ -16578,7 +16577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:11">
       <c r="A422" t="s">
         <v>11</v>
       </c>
@@ -16613,7 +16612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:11">
       <c r="A423" t="s">
         <v>11</v>
       </c>
@@ -16648,7 +16647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:11">
       <c r="A424" t="s">
         <v>11</v>
       </c>
@@ -16683,7 +16682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:11">
       <c r="A425" t="s">
         <v>11</v>
       </c>
@@ -16718,7 +16717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:11">
       <c r="A426" t="s">
         <v>11</v>
       </c>
@@ -16753,7 +16752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:11">
       <c r="A427" t="s">
         <v>11</v>
       </c>
@@ -16788,7 +16787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:11">
       <c r="A428" t="s">
         <v>11</v>
       </c>
@@ -16823,7 +16822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:11">
       <c r="A429" t="s">
         <v>11</v>
       </c>
@@ -16858,7 +16857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:11">
       <c r="A430" t="s">
         <v>11</v>
       </c>
@@ -16893,7 +16892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:11">
       <c r="A431" t="s">
         <v>11</v>
       </c>
@@ -16928,7 +16927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:11">
       <c r="A432" t="s">
         <v>11</v>
       </c>
@@ -16963,7 +16962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11">
       <c r="A433" t="s">
         <v>11</v>
       </c>
@@ -16998,7 +16997,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:11">
       <c r="A434" t="s">
         <v>11</v>
       </c>
@@ -17033,7 +17032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11">
       <c r="A435" t="s">
         <v>11</v>
       </c>
@@ -17068,7 +17067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11">
       <c r="A436" t="s">
         <v>11</v>
       </c>
@@ -17103,7 +17102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11">
       <c r="A437" t="s">
         <v>11</v>
       </c>
@@ -17138,7 +17137,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11">
       <c r="A438" t="s">
         <v>11</v>
       </c>
@@ -17173,7 +17172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11">
       <c r="A439" t="s">
         <v>11</v>
       </c>
@@ -17208,7 +17207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11">
       <c r="A440" t="s">
         <v>11</v>
       </c>
@@ -17243,7 +17242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11">
       <c r="A441" t="s">
         <v>11</v>
       </c>
@@ -17278,7 +17277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11">
       <c r="A442" t="s">
         <v>11</v>
       </c>
@@ -17313,7 +17312,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11">
       <c r="A443" t="s">
         <v>11</v>
       </c>
@@ -17348,7 +17347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11">
       <c r="A444" t="s">
         <v>11</v>
       </c>
@@ -17383,7 +17382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:11">
       <c r="A445" t="s">
         <v>11</v>
       </c>
@@ -17418,7 +17417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11">
       <c r="A446" t="s">
         <v>11</v>
       </c>
@@ -17453,7 +17452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11">
       <c r="A447" t="s">
         <v>11</v>
       </c>
@@ -17488,7 +17487,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11">
       <c r="A448" t="s">
         <v>11</v>
       </c>
@@ -17523,7 +17522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11">
       <c r="A449" t="s">
         <v>11</v>
       </c>
@@ -17558,7 +17557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11">
       <c r="A450" t="s">
         <v>11</v>
       </c>
@@ -17593,7 +17592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11">
       <c r="A451" t="s">
         <v>11</v>
       </c>
@@ -17628,7 +17627,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11">
       <c r="A452" t="s">
         <v>11</v>
       </c>
@@ -17663,7 +17662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11">
       <c r="A453" t="s">
         <v>11</v>
       </c>
@@ -17698,7 +17697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11">
       <c r="A454" t="s">
         <v>11</v>
       </c>
@@ -17733,7 +17732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11">
       <c r="A455" t="s">
         <v>11</v>
       </c>
@@ -17768,7 +17767,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11">
       <c r="A456" t="s">
         <v>11</v>
       </c>
@@ -17803,7 +17802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11">
       <c r="A457" t="s">
         <v>11</v>
       </c>
@@ -17838,7 +17837,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11">
       <c r="A458" t="s">
         <v>11</v>
       </c>
@@ -17873,7 +17872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11">
       <c r="A459" t="s">
         <v>11</v>
       </c>
@@ -17908,7 +17907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11">
       <c r="A460" t="s">
         <v>11</v>
       </c>
@@ -17943,7 +17942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11">
       <c r="A461" t="s">
         <v>11</v>
       </c>
@@ -17978,7 +17977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11">
       <c r="A462" t="s">
         <v>11</v>
       </c>
@@ -18013,7 +18012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11">
       <c r="A463" t="s">
         <v>11</v>
       </c>
@@ -18048,7 +18047,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11">
       <c r="A464" t="s">
         <v>11</v>
       </c>
@@ -18083,7 +18082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11">
       <c r="A465" t="s">
         <v>11</v>
       </c>
@@ -18118,7 +18117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11">
       <c r="A466" t="s">
         <v>11</v>
       </c>
@@ -18170,8 +18169,14 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="D8" r:id="rId2"/>
+    <hyperlink ref="D9" r:id="rId3"/>
+    <hyperlink ref="D10" r:id="rId4"/>
+    <hyperlink ref="D11" r:id="rId5"/>
+    <hyperlink ref="D12" r:id="rId6"/>
+    <hyperlink ref="D13" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
+++ b/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12300"/>
   </bookViews>
   <sheets>
-    <sheet name="Kênh YouTube" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Kênh YouTube" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5099" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5105" uniqueCount="490">
   <si>
     <t>EMAIL</t>
   </si>
@@ -67,7 +67,7 @@
     <t>https://www.youtube.com/watch?v=hX45BtIdlIA</t>
   </si>
   <si>
-    <t>『修羅子のドロドロ人生朗読』では
+    <t xml:space="preserve">『修羅子のドロドロ人生朗読』では
 日常で起こる様々なスカッとする話や修羅場な体験談を
 投稿しております。
 是非チャンネル登録をお願いいたします！
@@ -149,19 +149,37 @@
     <t>https://www.youtube.com/watch?v=0mMZPZmigGU</t>
   </si>
   <si>
+    <t>【修羅場な話】嫁が不倫をしていたが一度だけチャンスを与えるため夫婦水入らずの旅行に誘いました。嫁「分かった、会社に休めるか聞いてみる」すると旅行に行く3日前に嫁はこう言ってきたんです…【朗読】</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=KBXHQHWkls4</t>
   </si>
   <si>
+    <t>【修羅場な話】嫁の不倫で離婚し、しばらくして間男が訪ねて来た！俺「何の用だ？うちには嫁はもう居ないぞ！」間男はこう言って来たんです…【朗読】</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=cgb3zEvU6ak</t>
   </si>
   <si>
+    <t>【修羅場な話】義兄夫婦が離婚することに。義嫁「引っ越すからもう会う機会もないと思うので、これ渡しておきます。」封筒の中身を確認すると…【朗読】</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=ZtAPTciroF8</t>
   </si>
   <si>
+    <t>【修羅場な話】うちの両親は仮面夫婦です私「お父さん、離婚していいよ」父「お父さんはお母さんに復讐をしているんだよ」私「え？」【朗読】</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=DKWm1RuMqoU</t>
   </si>
   <si>
+    <t>【修羅場な話】車の中に大量のDVDがあり中身を確認すると…嫁「黙っててゴメン。でも、言ったら絶対怒ってたでしょ？」そして離婚を決断しました【朗読】</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=bsmxfFubyAo</t>
+  </si>
+  <si>
+    <t>【修羅場な話】目を覚ますと精神病院の隔離病棟だった。俺「姉貴…これ今どういう状況…？」姉貴「あんた、何も憶えてないの？この5日間のこと…」姉貴は残酷な事実を話し始めました…【朗読】</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=BEIP_UBAXbY</t>
@@ -1527,36 +1545,36 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <charset val="134"/>
+      <color theme="10"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="134"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1582,9 +1600,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1593,10 +1610,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1876,7 +1892,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K466"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1889,7 +1905,7 @@
     <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1924,7 +1940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1948,7 +1964,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1977,7 +1993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2009,7 +2025,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2038,7 +2054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2070,7 +2086,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2105,7 +2121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2118,14 +2134,17 @@
       <c r="D8" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>11</v>
@@ -2137,7 +2156,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2148,16 +2167,19 @@
         <v>11</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>11</v>
@@ -2169,7 +2191,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2180,16 +2202,19 @@
         <v>11</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
@@ -2201,7 +2226,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2212,16 +2237,19 @@
         <v>11</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>11</v>
@@ -2233,7 +2261,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2244,16 +2272,19 @@
         <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
         <v>11</v>
@@ -2265,7 +2296,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2276,16 +2307,19 @@
         <v>11</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
         <v>11</v>
@@ -2297,7 +2331,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2308,7 +2342,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2332,7 +2366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2343,7 +2377,7 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -2367,7 +2401,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2378,7 +2412,7 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -2402,7 +2436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2413,7 +2447,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -2437,7 +2471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2448,7 +2482,7 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -2472,7 +2506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2483,7 +2517,7 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -2507,7 +2541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2518,7 +2552,7 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -2542,7 +2576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -2553,7 +2587,7 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -2577,7 +2611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -2588,7 +2622,7 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -2612,7 +2646,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -2623,7 +2657,7 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -2647,7 +2681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2658,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -2682,7 +2716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -2693,7 +2727,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -2717,7 +2751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -2728,7 +2762,7 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -2752,7 +2786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -2763,7 +2797,7 @@
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -2787,7 +2821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -2798,7 +2832,7 @@
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -2822,7 +2856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -2833,7 +2867,7 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -2857,7 +2891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -2868,7 +2902,7 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -2892,7 +2926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -2903,7 +2937,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -2927,7 +2961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -2938,7 +2972,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -2962,7 +2996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -2973,7 +3007,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -2997,7 +3031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3008,7 +3042,7 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3032,7 +3066,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -3043,7 +3077,7 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3067,7 +3101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -3078,7 +3112,7 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -3102,7 +3136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -3113,7 +3147,7 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3137,7 +3171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -3148,7 +3182,7 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -3172,7 +3206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -3183,7 +3217,7 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -3207,7 +3241,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -3218,7 +3252,7 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -3242,7 +3276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -3253,7 +3287,7 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -3277,7 +3311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -3288,7 +3322,7 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -3312,7 +3346,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -3323,7 +3357,7 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -3347,7 +3381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -3358,7 +3392,7 @@
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -3382,7 +3416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -3393,7 +3427,7 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -3417,7 +3451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -3428,7 +3462,7 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -3452,7 +3486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -3463,7 +3497,7 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -3487,7 +3521,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -3498,7 +3532,7 @@
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -3522,7 +3556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -3533,7 +3567,7 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -3557,7 +3591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -3568,7 +3602,7 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -3592,7 +3626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -3603,7 +3637,7 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -3627,7 +3661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -3638,7 +3672,7 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -3662,7 +3696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -3673,7 +3707,7 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -3697,7 +3731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -3708,7 +3742,7 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -3732,7 +3766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -3743,7 +3777,7 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -3767,7 +3801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -3778,7 +3812,7 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -3802,7 +3836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -3813,7 +3847,7 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -3837,7 +3871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -3848,7 +3882,7 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -3872,7 +3906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -3883,7 +3917,7 @@
         <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -3907,7 +3941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -3918,7 +3952,7 @@
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -3942,7 +3976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -3953,7 +3987,7 @@
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -3977,7 +4011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -3988,7 +4022,7 @@
         <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -4012,7 +4046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -4023,7 +4057,7 @@
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -4047,7 +4081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -4058,7 +4092,7 @@
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -4082,7 +4116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -4093,7 +4127,7 @@
         <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -4117,7 +4151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -4128,7 +4162,7 @@
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -4152,7 +4186,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -4163,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -4187,7 +4221,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -4198,7 +4232,7 @@
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -4222,7 +4256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -4233,7 +4267,7 @@
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -4257,7 +4291,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -4268,7 +4302,7 @@
         <v>11</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -4292,7 +4326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -4303,7 +4337,7 @@
         <v>11</v>
       </c>
       <c r="D71" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -4327,7 +4361,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -4338,7 +4372,7 @@
         <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -4362,7 +4396,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -4373,7 +4407,7 @@
         <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -4397,7 +4431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -4408,7 +4442,7 @@
         <v>11</v>
       </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -4432,7 +4466,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -4443,7 +4477,7 @@
         <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -4467,7 +4501,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -4478,7 +4512,7 @@
         <v>11</v>
       </c>
       <c r="D76" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -4502,7 +4536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -4513,7 +4547,7 @@
         <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -4537,7 +4571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -4548,7 +4582,7 @@
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -4572,7 +4606,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -4583,7 +4617,7 @@
         <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -4607,7 +4641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -4618,7 +4652,7 @@
         <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -4642,7 +4676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -4653,7 +4687,7 @@
         <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E81" t="s">
         <v>15</v>
@@ -4677,7 +4711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -4688,7 +4722,7 @@
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
@@ -4712,7 +4746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -4723,7 +4757,7 @@
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E83" t="s">
         <v>15</v>
@@ -4747,7 +4781,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -4758,7 +4792,7 @@
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -4782,7 +4816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -4793,7 +4827,7 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -4817,7 +4851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -4828,7 +4862,7 @@
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
@@ -4852,7 +4886,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -4863,7 +4897,7 @@
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -4887,7 +4921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -4898,7 +4932,7 @@
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -4922,7 +4956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -4933,7 +4967,7 @@
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -4957,7 +4991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -4968,7 +5002,7 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -4992,7 +5026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -5003,7 +5037,7 @@
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -5027,7 +5061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -5038,7 +5072,7 @@
         <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -5062,7 +5096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -5073,7 +5107,7 @@
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -5097,7 +5131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -5108,7 +5142,7 @@
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -5132,7 +5166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -5143,7 +5177,7 @@
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -5167,7 +5201,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -5178,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E96" t="s">
         <v>15</v>
@@ -5202,7 +5236,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -5213,7 +5247,7 @@
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E97" t="s">
         <v>15</v>
@@ -5237,7 +5271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -5248,7 +5282,7 @@
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E98" t="s">
         <v>15</v>
@@ -5272,7 +5306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -5283,7 +5317,7 @@
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E99" t="s">
         <v>15</v>
@@ -5307,7 +5341,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -5318,7 +5352,7 @@
         <v>11</v>
       </c>
       <c r="D100" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E100" t="s">
         <v>15</v>
@@ -5342,7 +5376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -5353,7 +5387,7 @@
         <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E101" t="s">
         <v>15</v>
@@ -5377,7 +5411,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -5388,7 +5422,7 @@
         <v>11</v>
       </c>
       <c r="D102" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E102" t="s">
         <v>15</v>
@@ -5412,7 +5446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -5423,7 +5457,7 @@
         <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E103" t="s">
         <v>15</v>
@@ -5447,7 +5481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -5458,7 +5492,7 @@
         <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E104" t="s">
         <v>15</v>
@@ -5482,7 +5516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -5493,7 +5527,7 @@
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E105" t="s">
         <v>15</v>
@@ -5517,7 +5551,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -5528,7 +5562,7 @@
         <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E106" t="s">
         <v>15</v>
@@ -5552,7 +5586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -5563,7 +5597,7 @@
         <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E107" t="s">
         <v>15</v>
@@ -5587,7 +5621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -5598,7 +5632,7 @@
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E108" t="s">
         <v>15</v>
@@ -5622,7 +5656,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -5633,7 +5667,7 @@
         <v>11</v>
       </c>
       <c r="D109" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E109" t="s">
         <v>15</v>
@@ -5657,7 +5691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>11</v>
       </c>
@@ -5668,7 +5702,7 @@
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E110" t="s">
         <v>15</v>
@@ -5692,7 +5726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>11</v>
       </c>
@@ -5703,7 +5737,7 @@
         <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E111" t="s">
         <v>15</v>
@@ -5727,7 +5761,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -5738,7 +5772,7 @@
         <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E112" t="s">
         <v>15</v>
@@ -5762,7 +5796,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -5773,7 +5807,7 @@
         <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E113" t="s">
         <v>15</v>
@@ -5797,7 +5831,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -5808,7 +5842,7 @@
         <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E114" t="s">
         <v>15</v>
@@ -5832,7 +5866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -5843,7 +5877,7 @@
         <v>11</v>
       </c>
       <c r="D115" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E115" t="s">
         <v>15</v>
@@ -5867,7 +5901,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -5878,7 +5912,7 @@
         <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E116" t="s">
         <v>15</v>
@@ -5902,7 +5936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -5913,7 +5947,7 @@
         <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E117" t="s">
         <v>15</v>
@@ -5937,7 +5971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -5948,7 +5982,7 @@
         <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E118" t="s">
         <v>15</v>
@@ -5972,7 +6006,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -5983,7 +6017,7 @@
         <v>11</v>
       </c>
       <c r="D119" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E119" t="s">
         <v>15</v>
@@ -6007,7 +6041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -6018,7 +6052,7 @@
         <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E120" t="s">
         <v>15</v>
@@ -6042,7 +6076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -6053,7 +6087,7 @@
         <v>11</v>
       </c>
       <c r="D121" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E121" t="s">
         <v>15</v>
@@ -6077,7 +6111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -6088,7 +6122,7 @@
         <v>11</v>
       </c>
       <c r="D122" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>15</v>
@@ -6112,7 +6146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -6123,7 +6157,7 @@
         <v>11</v>
       </c>
       <c r="D123" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
         <v>15</v>
@@ -6147,7 +6181,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -6158,7 +6192,7 @@
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E124" t="s">
         <v>15</v>
@@ -6182,7 +6216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -6193,7 +6227,7 @@
         <v>11</v>
       </c>
       <c r="D125" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E125" t="s">
         <v>15</v>
@@ -6217,7 +6251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -6228,7 +6262,7 @@
         <v>11</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
@@ -6252,7 +6286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -6263,7 +6297,7 @@
         <v>11</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E127" t="s">
         <v>15</v>
@@ -6287,7 +6321,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -6298,7 +6332,7 @@
         <v>11</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E128" t="s">
         <v>15</v>
@@ -6322,7 +6356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -6333,7 +6367,7 @@
         <v>11</v>
       </c>
       <c r="D129" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E129" t="s">
         <v>15</v>
@@ -6357,7 +6391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -6368,7 +6402,7 @@
         <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E130" t="s">
         <v>15</v>
@@ -6392,7 +6426,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>11</v>
       </c>
@@ -6403,7 +6437,7 @@
         <v>11</v>
       </c>
       <c r="D131" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E131" t="s">
         <v>15</v>
@@ -6427,7 +6461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>11</v>
       </c>
@@ -6438,7 +6472,7 @@
         <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E132" t="s">
         <v>15</v>
@@ -6462,7 +6496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>11</v>
       </c>
@@ -6473,7 +6507,7 @@
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E133" t="s">
         <v>15</v>
@@ -6497,7 +6531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>11</v>
       </c>
@@ -6508,7 +6542,7 @@
         <v>11</v>
       </c>
       <c r="D134" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E134" t="s">
         <v>15</v>
@@ -6532,7 +6566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>11</v>
       </c>
@@ -6543,7 +6577,7 @@
         <v>11</v>
       </c>
       <c r="D135" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E135" t="s">
         <v>15</v>
@@ -6567,7 +6601,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>11</v>
       </c>
@@ -6578,7 +6612,7 @@
         <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E136" t="s">
         <v>15</v>
@@ -6602,7 +6636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>11</v>
       </c>
@@ -6613,7 +6647,7 @@
         <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E137" t="s">
         <v>15</v>
@@ -6637,7 +6671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>11</v>
       </c>
@@ -6648,7 +6682,7 @@
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E138" t="s">
         <v>15</v>
@@ -6672,7 +6706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>11</v>
       </c>
@@ -6683,7 +6717,7 @@
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E139" t="s">
         <v>15</v>
@@ -6707,7 +6741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>11</v>
       </c>
@@ -6718,7 +6752,7 @@
         <v>11</v>
       </c>
       <c r="D140" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E140" t="s">
         <v>15</v>
@@ -6742,7 +6776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>11</v>
       </c>
@@ -6753,7 +6787,7 @@
         <v>11</v>
       </c>
       <c r="D141" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E141" t="s">
         <v>15</v>
@@ -6777,7 +6811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -6788,7 +6822,7 @@
         <v>11</v>
       </c>
       <c r="D142" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E142" t="s">
         <v>15</v>
@@ -6812,7 +6846,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>11</v>
       </c>
@@ -6823,7 +6857,7 @@
         <v>11</v>
       </c>
       <c r="D143" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E143" t="s">
         <v>15</v>
@@ -6847,7 +6881,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>11</v>
       </c>
@@ -6858,7 +6892,7 @@
         <v>11</v>
       </c>
       <c r="D144" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E144" t="s">
         <v>15</v>
@@ -6882,7 +6916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>11</v>
       </c>
@@ -6893,7 +6927,7 @@
         <v>11</v>
       </c>
       <c r="D145" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E145" t="s">
         <v>15</v>
@@ -6917,7 +6951,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>11</v>
       </c>
@@ -6928,7 +6962,7 @@
         <v>11</v>
       </c>
       <c r="D146" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E146" t="s">
         <v>15</v>
@@ -6952,7 +6986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>11</v>
       </c>
@@ -6963,7 +6997,7 @@
         <v>11</v>
       </c>
       <c r="D147" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E147" t="s">
         <v>15</v>
@@ -6987,7 +7021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>11</v>
       </c>
@@ -6998,7 +7032,7 @@
         <v>11</v>
       </c>
       <c r="D148" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E148" t="s">
         <v>15</v>
@@ -7022,7 +7056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>11</v>
       </c>
@@ -7033,7 +7067,7 @@
         <v>11</v>
       </c>
       <c r="D149" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E149" t="s">
         <v>15</v>
@@ -7057,7 +7091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>11</v>
       </c>
@@ -7068,7 +7102,7 @@
         <v>11</v>
       </c>
       <c r="D150" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E150" t="s">
         <v>15</v>
@@ -7092,7 +7126,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>11</v>
       </c>
@@ -7103,7 +7137,7 @@
         <v>11</v>
       </c>
       <c r="D151" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E151" t="s">
         <v>15</v>
@@ -7127,7 +7161,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -7138,7 +7172,7 @@
         <v>11</v>
       </c>
       <c r="D152" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E152" t="s">
         <v>15</v>
@@ -7162,7 +7196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>11</v>
       </c>
@@ -7173,7 +7207,7 @@
         <v>11</v>
       </c>
       <c r="D153" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E153" t="s">
         <v>15</v>
@@ -7197,7 +7231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>11</v>
       </c>
@@ -7208,7 +7242,7 @@
         <v>11</v>
       </c>
       <c r="D154" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E154" t="s">
         <v>15</v>
@@ -7232,7 +7266,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>11</v>
       </c>
@@ -7243,7 +7277,7 @@
         <v>11</v>
       </c>
       <c r="D155" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E155" t="s">
         <v>15</v>
@@ -7267,7 +7301,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>11</v>
       </c>
@@ -7278,7 +7312,7 @@
         <v>11</v>
       </c>
       <c r="D156" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E156" t="s">
         <v>15</v>
@@ -7302,7 +7336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>11</v>
       </c>
@@ -7313,7 +7347,7 @@
         <v>11</v>
       </c>
       <c r="D157" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E157" t="s">
         <v>15</v>
@@ -7337,7 +7371,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>11</v>
       </c>
@@ -7348,7 +7382,7 @@
         <v>11</v>
       </c>
       <c r="D158" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E158" t="s">
         <v>15</v>
@@ -7372,7 +7406,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -7383,7 +7417,7 @@
         <v>11</v>
       </c>
       <c r="D159" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E159" t="s">
         <v>15</v>
@@ -7407,7 +7441,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -7418,7 +7452,7 @@
         <v>11</v>
       </c>
       <c r="D160" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E160" t="s">
         <v>15</v>
@@ -7442,7 +7476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>11</v>
       </c>
@@ -7453,7 +7487,7 @@
         <v>11</v>
       </c>
       <c r="D161" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E161" t="s">
         <v>15</v>
@@ -7477,7 +7511,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -7488,7 +7522,7 @@
         <v>11</v>
       </c>
       <c r="D162" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E162" t="s">
         <v>15</v>
@@ -7512,7 +7546,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>11</v>
       </c>
@@ -7523,7 +7557,7 @@
         <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E163" t="s">
         <v>15</v>
@@ -7547,7 +7581,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>11</v>
       </c>
@@ -7558,7 +7592,7 @@
         <v>11</v>
       </c>
       <c r="D164" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E164" t="s">
         <v>15</v>
@@ -7582,7 +7616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>11</v>
       </c>
@@ -7593,7 +7627,7 @@
         <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E165" t="s">
         <v>15</v>
@@ -7617,7 +7651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -7628,7 +7662,7 @@
         <v>11</v>
       </c>
       <c r="D166" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E166" t="s">
         <v>15</v>
@@ -7652,7 +7686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -7663,7 +7697,7 @@
         <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E167" t="s">
         <v>15</v>
@@ -7687,7 +7721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>11</v>
       </c>
@@ -7698,7 +7732,7 @@
         <v>11</v>
       </c>
       <c r="D168" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E168" t="s">
         <v>15</v>
@@ -7722,7 +7756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -7733,7 +7767,7 @@
         <v>11</v>
       </c>
       <c r="D169" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E169" t="s">
         <v>15</v>
@@ -7757,7 +7791,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>11</v>
       </c>
@@ -7768,7 +7802,7 @@
         <v>11</v>
       </c>
       <c r="D170" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E170" t="s">
         <v>15</v>
@@ -7792,7 +7826,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>11</v>
       </c>
@@ -7803,7 +7837,7 @@
         <v>11</v>
       </c>
       <c r="D171" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E171" t="s">
         <v>15</v>
@@ -7827,7 +7861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>11</v>
       </c>
@@ -7838,7 +7872,7 @@
         <v>11</v>
       </c>
       <c r="D172" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E172" t="s">
         <v>15</v>
@@ -7862,7 +7896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>11</v>
       </c>
@@ -7873,7 +7907,7 @@
         <v>11</v>
       </c>
       <c r="D173" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E173" t="s">
         <v>15</v>
@@ -7897,7 +7931,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>11</v>
       </c>
@@ -7908,7 +7942,7 @@
         <v>11</v>
       </c>
       <c r="D174" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E174" t="s">
         <v>15</v>
@@ -7932,7 +7966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>11</v>
       </c>
@@ -7943,7 +7977,7 @@
         <v>11</v>
       </c>
       <c r="D175" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E175" t="s">
         <v>15</v>
@@ -7967,7 +8001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>11</v>
       </c>
@@ -7978,7 +8012,7 @@
         <v>11</v>
       </c>
       <c r="D176" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E176" t="s">
         <v>15</v>
@@ -8002,7 +8036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>11</v>
       </c>
@@ -8013,7 +8047,7 @@
         <v>11</v>
       </c>
       <c r="D177" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E177" t="s">
         <v>15</v>
@@ -8037,7 +8071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>11</v>
       </c>
@@ -8048,7 +8082,7 @@
         <v>11</v>
       </c>
       <c r="D178" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E178" t="s">
         <v>15</v>
@@ -8072,7 +8106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>11</v>
       </c>
@@ -8083,7 +8117,7 @@
         <v>11</v>
       </c>
       <c r="D179" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E179" t="s">
         <v>15</v>
@@ -8107,7 +8141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>11</v>
       </c>
@@ -8118,7 +8152,7 @@
         <v>11</v>
       </c>
       <c r="D180" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E180" t="s">
         <v>15</v>
@@ -8142,7 +8176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>11</v>
       </c>
@@ -8153,7 +8187,7 @@
         <v>11</v>
       </c>
       <c r="D181" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E181" t="s">
         <v>15</v>
@@ -8177,7 +8211,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>11</v>
       </c>
@@ -8188,7 +8222,7 @@
         <v>11</v>
       </c>
       <c r="D182" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E182" t="s">
         <v>15</v>
@@ -8212,7 +8246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>11</v>
       </c>
@@ -8223,7 +8257,7 @@
         <v>11</v>
       </c>
       <c r="D183" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E183" t="s">
         <v>15</v>
@@ -8247,7 +8281,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>11</v>
       </c>
@@ -8258,7 +8292,7 @@
         <v>11</v>
       </c>
       <c r="D184" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E184" t="s">
         <v>15</v>
@@ -8282,7 +8316,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>11</v>
       </c>
@@ -8293,7 +8327,7 @@
         <v>11</v>
       </c>
       <c r="D185" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E185" t="s">
         <v>15</v>
@@ -8317,7 +8351,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>11</v>
       </c>
@@ -8328,7 +8362,7 @@
         <v>11</v>
       </c>
       <c r="D186" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E186" t="s">
         <v>15</v>
@@ -8352,7 +8386,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>11</v>
       </c>
@@ -8363,7 +8397,7 @@
         <v>11</v>
       </c>
       <c r="D187" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E187" t="s">
         <v>15</v>
@@ -8387,7 +8421,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>11</v>
       </c>
@@ -8398,7 +8432,7 @@
         <v>11</v>
       </c>
       <c r="D188" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E188" t="s">
         <v>15</v>
@@ -8422,7 +8456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>11</v>
       </c>
@@ -8433,7 +8467,7 @@
         <v>11</v>
       </c>
       <c r="D189" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E189" t="s">
         <v>15</v>
@@ -8457,7 +8491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>11</v>
       </c>
@@ -8468,7 +8502,7 @@
         <v>11</v>
       </c>
       <c r="D190" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E190" t="s">
         <v>15</v>
@@ -8492,7 +8526,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>11</v>
       </c>
@@ -8503,7 +8537,7 @@
         <v>11</v>
       </c>
       <c r="D191" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E191" t="s">
         <v>15</v>
@@ -8527,7 +8561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>11</v>
       </c>
@@ -8538,7 +8572,7 @@
         <v>11</v>
       </c>
       <c r="D192" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E192" t="s">
         <v>15</v>
@@ -8562,7 +8596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>11</v>
       </c>
@@ -8573,7 +8607,7 @@
         <v>11</v>
       </c>
       <c r="D193" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E193" t="s">
         <v>15</v>
@@ -8597,7 +8631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>11</v>
       </c>
@@ -8608,7 +8642,7 @@
         <v>11</v>
       </c>
       <c r="D194" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E194" t="s">
         <v>15</v>
@@ -8632,7 +8666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>11</v>
       </c>
@@ -8643,7 +8677,7 @@
         <v>11</v>
       </c>
       <c r="D195" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E195" t="s">
         <v>15</v>
@@ -8667,7 +8701,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>11</v>
       </c>
@@ -8678,7 +8712,7 @@
         <v>11</v>
       </c>
       <c r="D196" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E196" t="s">
         <v>15</v>
@@ -8702,7 +8736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>11</v>
       </c>
@@ -8713,7 +8747,7 @@
         <v>11</v>
       </c>
       <c r="D197" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E197" t="s">
         <v>15</v>
@@ -8737,7 +8771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>11</v>
       </c>
@@ -8748,7 +8782,7 @@
         <v>11</v>
       </c>
       <c r="D198" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E198" t="s">
         <v>15</v>
@@ -8772,7 +8806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>11</v>
       </c>
@@ -8783,7 +8817,7 @@
         <v>11</v>
       </c>
       <c r="D199" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E199" t="s">
         <v>15</v>
@@ -8807,7 +8841,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>11</v>
       </c>
@@ -8818,7 +8852,7 @@
         <v>11</v>
       </c>
       <c r="D200" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E200" t="s">
         <v>15</v>
@@ -8842,7 +8876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>11</v>
       </c>
@@ -8853,7 +8887,7 @@
         <v>11</v>
       </c>
       <c r="D201" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E201" t="s">
         <v>15</v>
@@ -8877,7 +8911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>11</v>
       </c>
@@ -8888,7 +8922,7 @@
         <v>11</v>
       </c>
       <c r="D202" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E202" t="s">
         <v>15</v>
@@ -8912,7 +8946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>11</v>
       </c>
@@ -8923,7 +8957,7 @@
         <v>11</v>
       </c>
       <c r="D203" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E203" t="s">
         <v>15</v>
@@ -8947,7 +8981,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>11</v>
       </c>
@@ -8958,7 +8992,7 @@
         <v>11</v>
       </c>
       <c r="D204" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E204" t="s">
         <v>15</v>
@@ -8982,7 +9016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>11</v>
       </c>
@@ -8993,7 +9027,7 @@
         <v>11</v>
       </c>
       <c r="D205" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E205" t="s">
         <v>15</v>
@@ -9017,7 +9051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>11</v>
       </c>
@@ -9028,7 +9062,7 @@
         <v>11</v>
       </c>
       <c r="D206" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E206" t="s">
         <v>15</v>
@@ -9052,7 +9086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>11</v>
       </c>
@@ -9063,7 +9097,7 @@
         <v>11</v>
       </c>
       <c r="D207" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E207" t="s">
         <v>15</v>
@@ -9087,7 +9121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>11</v>
       </c>
@@ -9098,7 +9132,7 @@
         <v>11</v>
       </c>
       <c r="D208" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E208" t="s">
         <v>15</v>
@@ -9122,7 +9156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>11</v>
       </c>
@@ -9133,7 +9167,7 @@
         <v>11</v>
       </c>
       <c r="D209" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E209" t="s">
         <v>15</v>
@@ -9157,7 +9191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>11</v>
       </c>
@@ -9168,7 +9202,7 @@
         <v>11</v>
       </c>
       <c r="D210" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E210" t="s">
         <v>15</v>
@@ -9192,7 +9226,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>11</v>
       </c>
@@ -9203,7 +9237,7 @@
         <v>11</v>
       </c>
       <c r="D211" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E211" t="s">
         <v>15</v>
@@ -9227,7 +9261,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>11</v>
       </c>
@@ -9238,7 +9272,7 @@
         <v>11</v>
       </c>
       <c r="D212" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E212" t="s">
         <v>15</v>
@@ -9262,7 +9296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>11</v>
       </c>
@@ -9273,7 +9307,7 @@
         <v>11</v>
       </c>
       <c r="D213" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E213" t="s">
         <v>15</v>
@@ -9297,7 +9331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>11</v>
       </c>
@@ -9308,7 +9342,7 @@
         <v>11</v>
       </c>
       <c r="D214" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E214" t="s">
         <v>15</v>
@@ -9332,7 +9366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>11</v>
       </c>
@@ -9343,7 +9377,7 @@
         <v>11</v>
       </c>
       <c r="D215" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E215" t="s">
         <v>15</v>
@@ -9367,7 +9401,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>11</v>
       </c>
@@ -9378,7 +9412,7 @@
         <v>11</v>
       </c>
       <c r="D216" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E216" t="s">
         <v>15</v>
@@ -9402,7 +9436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>11</v>
       </c>
@@ -9413,7 +9447,7 @@
         <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E217" t="s">
         <v>15</v>
@@ -9437,7 +9471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>11</v>
       </c>
@@ -9448,7 +9482,7 @@
         <v>11</v>
       </c>
       <c r="D218" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E218" t="s">
         <v>15</v>
@@ -9472,7 +9506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>11</v>
       </c>
@@ -9483,7 +9517,7 @@
         <v>11</v>
       </c>
       <c r="D219" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E219" t="s">
         <v>15</v>
@@ -9507,7 +9541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>11</v>
       </c>
@@ -9518,7 +9552,7 @@
         <v>11</v>
       </c>
       <c r="D220" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E220" t="s">
         <v>15</v>
@@ -9542,7 +9576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>11</v>
       </c>
@@ -9553,7 +9587,7 @@
         <v>11</v>
       </c>
       <c r="D221" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E221" t="s">
         <v>15</v>
@@ -9577,7 +9611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>11</v>
       </c>
@@ -9588,7 +9622,7 @@
         <v>11</v>
       </c>
       <c r="D222" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E222" t="s">
         <v>15</v>
@@ -9612,7 +9646,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>11</v>
       </c>
@@ -9623,7 +9657,7 @@
         <v>11</v>
       </c>
       <c r="D223" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E223" t="s">
         <v>15</v>
@@ -9647,7 +9681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>11</v>
       </c>
@@ -9658,7 +9692,7 @@
         <v>11</v>
       </c>
       <c r="D224" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E224" t="s">
         <v>15</v>
@@ -9682,7 +9716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>11</v>
       </c>
@@ -9693,7 +9727,7 @@
         <v>11</v>
       </c>
       <c r="D225" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E225" t="s">
         <v>15</v>
@@ -9717,7 +9751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>11</v>
       </c>
@@ -9728,7 +9762,7 @@
         <v>11</v>
       </c>
       <c r="D226" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E226" t="s">
         <v>15</v>
@@ -9752,7 +9786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>11</v>
       </c>
@@ -9763,7 +9797,7 @@
         <v>11</v>
       </c>
       <c r="D227" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E227" t="s">
         <v>15</v>
@@ -9787,7 +9821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>11</v>
       </c>
@@ -9798,7 +9832,7 @@
         <v>11</v>
       </c>
       <c r="D228" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E228" t="s">
         <v>15</v>
@@ -9822,7 +9856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>11</v>
       </c>
@@ -9833,7 +9867,7 @@
         <v>11</v>
       </c>
       <c r="D229" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E229" t="s">
         <v>15</v>
@@ -9857,7 +9891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>11</v>
       </c>
@@ -9868,7 +9902,7 @@
         <v>11</v>
       </c>
       <c r="D230" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E230" t="s">
         <v>15</v>
@@ -9892,7 +9926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>11</v>
       </c>
@@ -9903,7 +9937,7 @@
         <v>11</v>
       </c>
       <c r="D231" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E231" t="s">
         <v>15</v>
@@ -9927,7 +9961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>11</v>
       </c>
@@ -9938,7 +9972,7 @@
         <v>11</v>
       </c>
       <c r="D232" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E232" t="s">
         <v>15</v>
@@ -9962,7 +9996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>11</v>
       </c>
@@ -9973,7 +10007,7 @@
         <v>11</v>
       </c>
       <c r="D233" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E233" t="s">
         <v>15</v>
@@ -9997,7 +10031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>11</v>
       </c>
@@ -10008,7 +10042,7 @@
         <v>11</v>
       </c>
       <c r="D234" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E234" t="s">
         <v>15</v>
@@ -10032,7 +10066,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>11</v>
       </c>
@@ -10043,7 +10077,7 @@
         <v>11</v>
       </c>
       <c r="D235" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E235" t="s">
         <v>15</v>
@@ -10067,7 +10101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>11</v>
       </c>
@@ -10078,7 +10112,7 @@
         <v>11</v>
       </c>
       <c r="D236" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E236" t="s">
         <v>15</v>
@@ -10102,7 +10136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>11</v>
       </c>
@@ -10113,7 +10147,7 @@
         <v>11</v>
       </c>
       <c r="D237" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E237" t="s">
         <v>15</v>
@@ -10137,7 +10171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>11</v>
       </c>
@@ -10148,7 +10182,7 @@
         <v>11</v>
       </c>
       <c r="D238" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E238" t="s">
         <v>15</v>
@@ -10172,7 +10206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>11</v>
       </c>
@@ -10183,7 +10217,7 @@
         <v>11</v>
       </c>
       <c r="D239" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E239" t="s">
         <v>15</v>
@@ -10207,7 +10241,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>11</v>
       </c>
@@ -10218,7 +10252,7 @@
         <v>11</v>
       </c>
       <c r="D240" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E240" t="s">
         <v>15</v>
@@ -10242,7 +10276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>11</v>
       </c>
@@ -10253,7 +10287,7 @@
         <v>11</v>
       </c>
       <c r="D241" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E241" t="s">
         <v>15</v>
@@ -10277,7 +10311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>11</v>
       </c>
@@ -10288,7 +10322,7 @@
         <v>11</v>
       </c>
       <c r="D242" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E242" t="s">
         <v>15</v>
@@ -10312,7 +10346,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>11</v>
       </c>
@@ -10323,7 +10357,7 @@
         <v>11</v>
       </c>
       <c r="D243" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E243" t="s">
         <v>15</v>
@@ -10347,7 +10381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>11</v>
       </c>
@@ -10358,7 +10392,7 @@
         <v>11</v>
       </c>
       <c r="D244" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E244" t="s">
         <v>15</v>
@@ -10382,7 +10416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>11</v>
       </c>
@@ -10393,7 +10427,7 @@
         <v>11</v>
       </c>
       <c r="D245" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E245" t="s">
         <v>15</v>
@@ -10417,7 +10451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>11</v>
       </c>
@@ -10428,7 +10462,7 @@
         <v>11</v>
       </c>
       <c r="D246" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E246" t="s">
         <v>15</v>
@@ -10452,7 +10486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>11</v>
       </c>
@@ -10463,7 +10497,7 @@
         <v>11</v>
       </c>
       <c r="D247" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E247" t="s">
         <v>15</v>
@@ -10487,7 +10521,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>11</v>
       </c>
@@ -10498,7 +10532,7 @@
         <v>11</v>
       </c>
       <c r="D248" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E248" t="s">
         <v>15</v>
@@ -10522,7 +10556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>11</v>
       </c>
@@ -10533,7 +10567,7 @@
         <v>11</v>
       </c>
       <c r="D249" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E249" t="s">
         <v>15</v>
@@ -10557,7 +10591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>11</v>
       </c>
@@ -10568,7 +10602,7 @@
         <v>11</v>
       </c>
       <c r="D250" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E250" t="s">
         <v>15</v>
@@ -10592,7 +10626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>11</v>
       </c>
@@ -10603,7 +10637,7 @@
         <v>11</v>
       </c>
       <c r="D251" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E251" t="s">
         <v>15</v>
@@ -10627,7 +10661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>11</v>
       </c>
@@ -10638,7 +10672,7 @@
         <v>11</v>
       </c>
       <c r="D252" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E252" t="s">
         <v>15</v>
@@ -10662,7 +10696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>11</v>
       </c>
@@ -10673,7 +10707,7 @@
         <v>11</v>
       </c>
       <c r="D253" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E253" t="s">
         <v>15</v>
@@ -10697,7 +10731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>11</v>
       </c>
@@ -10708,7 +10742,7 @@
         <v>11</v>
       </c>
       <c r="D254" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E254" t="s">
         <v>15</v>
@@ -10732,7 +10766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>11</v>
       </c>
@@ -10743,7 +10777,7 @@
         <v>11</v>
       </c>
       <c r="D255" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E255" t="s">
         <v>15</v>
@@ -10767,7 +10801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>11</v>
       </c>
@@ -10778,7 +10812,7 @@
         <v>11</v>
       </c>
       <c r="D256" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E256" t="s">
         <v>15</v>
@@ -10802,7 +10836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>11</v>
       </c>
@@ -10813,7 +10847,7 @@
         <v>11</v>
       </c>
       <c r="D257" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E257" t="s">
         <v>15</v>
@@ -10837,7 +10871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>11</v>
       </c>
@@ -10848,7 +10882,7 @@
         <v>11</v>
       </c>
       <c r="D258" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E258" t="s">
         <v>15</v>
@@ -10872,7 +10906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>11</v>
       </c>
@@ -10883,7 +10917,7 @@
         <v>11</v>
       </c>
       <c r="D259" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E259" t="s">
         <v>15</v>
@@ -10907,7 +10941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>11</v>
       </c>
@@ -10918,7 +10952,7 @@
         <v>11</v>
       </c>
       <c r="D260" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E260" t="s">
         <v>15</v>
@@ -10942,7 +10976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>11</v>
       </c>
@@ -10953,7 +10987,7 @@
         <v>11</v>
       </c>
       <c r="D261" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E261" t="s">
         <v>15</v>
@@ -10977,7 +11011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -10988,7 +11022,7 @@
         <v>11</v>
       </c>
       <c r="D262" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E262" t="s">
         <v>15</v>
@@ -11012,7 +11046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>11</v>
       </c>
@@ -11023,7 +11057,7 @@
         <v>11</v>
       </c>
       <c r="D263" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E263" t="s">
         <v>15</v>
@@ -11047,7 +11081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>11</v>
       </c>
@@ -11058,7 +11092,7 @@
         <v>11</v>
       </c>
       <c r="D264" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E264" t="s">
         <v>15</v>
@@ -11082,7 +11116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>11</v>
       </c>
@@ -11093,7 +11127,7 @@
         <v>11</v>
       </c>
       <c r="D265" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E265" t="s">
         <v>15</v>
@@ -11117,7 +11151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>11</v>
       </c>
@@ -11128,7 +11162,7 @@
         <v>11</v>
       </c>
       <c r="D266" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E266" t="s">
         <v>15</v>
@@ -11152,7 +11186,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>11</v>
       </c>
@@ -11163,7 +11197,7 @@
         <v>11</v>
       </c>
       <c r="D267" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E267" t="s">
         <v>15</v>
@@ -11187,7 +11221,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>11</v>
       </c>
@@ -11198,7 +11232,7 @@
         <v>11</v>
       </c>
       <c r="D268" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E268" t="s">
         <v>15</v>
@@ -11222,7 +11256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>11</v>
       </c>
@@ -11233,7 +11267,7 @@
         <v>11</v>
       </c>
       <c r="D269" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E269" t="s">
         <v>15</v>
@@ -11257,7 +11291,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>11</v>
       </c>
@@ -11268,7 +11302,7 @@
         <v>11</v>
       </c>
       <c r="D270" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E270" t="s">
         <v>15</v>
@@ -11292,7 +11326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>11</v>
       </c>
@@ -11303,7 +11337,7 @@
         <v>11</v>
       </c>
       <c r="D271" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E271" t="s">
         <v>15</v>
@@ -11327,7 +11361,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>11</v>
       </c>
@@ -11338,7 +11372,7 @@
         <v>11</v>
       </c>
       <c r="D272" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E272" t="s">
         <v>15</v>
@@ -11362,7 +11396,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>11</v>
       </c>
@@ -11373,7 +11407,7 @@
         <v>11</v>
       </c>
       <c r="D273" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E273" t="s">
         <v>15</v>
@@ -11397,7 +11431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>11</v>
       </c>
@@ -11408,7 +11442,7 @@
         <v>11</v>
       </c>
       <c r="D274" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E274" t="s">
         <v>15</v>
@@ -11432,7 +11466,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>11</v>
       </c>
@@ -11443,7 +11477,7 @@
         <v>11</v>
       </c>
       <c r="D275" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E275" t="s">
         <v>15</v>
@@ -11467,7 +11501,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>11</v>
       </c>
@@ -11478,7 +11512,7 @@
         <v>11</v>
       </c>
       <c r="D276" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E276" t="s">
         <v>15</v>
@@ -11502,7 +11536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>11</v>
       </c>
@@ -11513,7 +11547,7 @@
         <v>11</v>
       </c>
       <c r="D277" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E277" t="s">
         <v>15</v>
@@ -11537,7 +11571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>11</v>
       </c>
@@ -11548,7 +11582,7 @@
         <v>11</v>
       </c>
       <c r="D278" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E278" t="s">
         <v>15</v>
@@ -11572,7 +11606,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>11</v>
       </c>
@@ -11583,7 +11617,7 @@
         <v>11</v>
       </c>
       <c r="D279" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E279" t="s">
         <v>15</v>
@@ -11607,7 +11641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>11</v>
       </c>
@@ -11618,7 +11652,7 @@
         <v>11</v>
       </c>
       <c r="D280" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E280" t="s">
         <v>15</v>
@@ -11642,7 +11676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>11</v>
       </c>
@@ -11653,7 +11687,7 @@
         <v>11</v>
       </c>
       <c r="D281" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E281" t="s">
         <v>15</v>
@@ -11677,7 +11711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>11</v>
       </c>
@@ -11688,7 +11722,7 @@
         <v>11</v>
       </c>
       <c r="D282" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E282" t="s">
         <v>15</v>
@@ -11712,7 +11746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>11</v>
       </c>
@@ -11723,7 +11757,7 @@
         <v>11</v>
       </c>
       <c r="D283" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E283" t="s">
         <v>15</v>
@@ -11747,7 +11781,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>11</v>
       </c>
@@ -11758,7 +11792,7 @@
         <v>11</v>
       </c>
       <c r="D284" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E284" t="s">
         <v>15</v>
@@ -11782,7 +11816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>11</v>
       </c>
@@ -11793,7 +11827,7 @@
         <v>11</v>
       </c>
       <c r="D285" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E285" t="s">
         <v>15</v>
@@ -11817,7 +11851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>11</v>
       </c>
@@ -11828,7 +11862,7 @@
         <v>11</v>
       </c>
       <c r="D286" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E286" t="s">
         <v>15</v>
@@ -11852,7 +11886,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>11</v>
       </c>
@@ -11863,7 +11897,7 @@
         <v>11</v>
       </c>
       <c r="D287" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E287" t="s">
         <v>15</v>
@@ -11887,7 +11921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>11</v>
       </c>
@@ -11898,7 +11932,7 @@
         <v>11</v>
       </c>
       <c r="D288" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E288" t="s">
         <v>15</v>
@@ -11922,7 +11956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>11</v>
       </c>
@@ -11933,7 +11967,7 @@
         <v>11</v>
       </c>
       <c r="D289" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E289" t="s">
         <v>15</v>
@@ -11957,7 +11991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>11</v>
       </c>
@@ -11968,7 +12002,7 @@
         <v>11</v>
       </c>
       <c r="D290" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E290" t="s">
         <v>15</v>
@@ -11992,7 +12026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>11</v>
       </c>
@@ -12003,7 +12037,7 @@
         <v>11</v>
       </c>
       <c r="D291" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E291" t="s">
         <v>15</v>
@@ -12027,7 +12061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>11</v>
       </c>
@@ -12038,7 +12072,7 @@
         <v>11</v>
       </c>
       <c r="D292" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E292" t="s">
         <v>15</v>
@@ -12062,7 +12096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>11</v>
       </c>
@@ -12073,7 +12107,7 @@
         <v>11</v>
       </c>
       <c r="D293" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E293" t="s">
         <v>15</v>
@@ -12097,7 +12131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>11</v>
       </c>
@@ -12108,7 +12142,7 @@
         <v>11</v>
       </c>
       <c r="D294" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E294" t="s">
         <v>15</v>
@@ -12132,7 +12166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>11</v>
       </c>
@@ -12143,7 +12177,7 @@
         <v>11</v>
       </c>
       <c r="D295" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E295" t="s">
         <v>15</v>
@@ -12167,7 +12201,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>11</v>
       </c>
@@ -12178,7 +12212,7 @@
         <v>11</v>
       </c>
       <c r="D296" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E296" t="s">
         <v>15</v>
@@ -12202,7 +12236,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>11</v>
       </c>
@@ -12213,7 +12247,7 @@
         <v>11</v>
       </c>
       <c r="D297" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E297" t="s">
         <v>15</v>
@@ -12237,7 +12271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>11</v>
       </c>
@@ -12248,7 +12282,7 @@
         <v>11</v>
       </c>
       <c r="D298" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E298" t="s">
         <v>15</v>
@@ -12272,7 +12306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>11</v>
       </c>
@@ -12283,7 +12317,7 @@
         <v>11</v>
       </c>
       <c r="D299" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E299" t="s">
         <v>15</v>
@@ -12307,7 +12341,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>11</v>
       </c>
@@ -12318,7 +12352,7 @@
         <v>11</v>
       </c>
       <c r="D300" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E300" t="s">
         <v>15</v>
@@ -12342,7 +12376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>11</v>
       </c>
@@ -12353,7 +12387,7 @@
         <v>11</v>
       </c>
       <c r="D301" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E301" t="s">
         <v>15</v>
@@ -12377,7 +12411,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>11</v>
       </c>
@@ -12388,7 +12422,7 @@
         <v>11</v>
       </c>
       <c r="D302" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E302" t="s">
         <v>15</v>
@@ -12412,7 +12446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>11</v>
       </c>
@@ -12423,7 +12457,7 @@
         <v>11</v>
       </c>
       <c r="D303" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E303" t="s">
         <v>15</v>
@@ -12447,7 +12481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>11</v>
       </c>
@@ -12458,7 +12492,7 @@
         <v>11</v>
       </c>
       <c r="D304" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E304" t="s">
         <v>15</v>
@@ -12482,7 +12516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>11</v>
       </c>
@@ -12493,7 +12527,7 @@
         <v>11</v>
       </c>
       <c r="D305" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E305" t="s">
         <v>15</v>
@@ -12517,7 +12551,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>11</v>
       </c>
@@ -12528,7 +12562,7 @@
         <v>11</v>
       </c>
       <c r="D306" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="E306" t="s">
         <v>15</v>
@@ -12552,7 +12586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>11</v>
       </c>
@@ -12563,7 +12597,7 @@
         <v>11</v>
       </c>
       <c r="D307" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E307" t="s">
         <v>15</v>
@@ -12587,7 +12621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>11</v>
       </c>
@@ -12598,7 +12632,7 @@
         <v>11</v>
       </c>
       <c r="D308" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E308" t="s">
         <v>15</v>
@@ -12622,7 +12656,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>11</v>
       </c>
@@ -12633,7 +12667,7 @@
         <v>11</v>
       </c>
       <c r="D309" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E309" t="s">
         <v>15</v>
@@ -12657,7 +12691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>11</v>
       </c>
@@ -12668,7 +12702,7 @@
         <v>11</v>
       </c>
       <c r="D310" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E310" t="s">
         <v>15</v>
@@ -12692,7 +12726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>11</v>
       </c>
@@ -12703,7 +12737,7 @@
         <v>11</v>
       </c>
       <c r="D311" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E311" t="s">
         <v>15</v>
@@ -12727,7 +12761,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>11</v>
       </c>
@@ -12738,7 +12772,7 @@
         <v>11</v>
       </c>
       <c r="D312" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E312" t="s">
         <v>15</v>
@@ -12762,7 +12796,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>11</v>
       </c>
@@ -12773,7 +12807,7 @@
         <v>11</v>
       </c>
       <c r="D313" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E313" t="s">
         <v>15</v>
@@ -12797,7 +12831,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>11</v>
       </c>
@@ -12808,7 +12842,7 @@
         <v>11</v>
       </c>
       <c r="D314" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E314" t="s">
         <v>15</v>
@@ -12832,7 +12866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>11</v>
       </c>
@@ -12843,7 +12877,7 @@
         <v>11</v>
       </c>
       <c r="D315" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E315" t="s">
         <v>15</v>
@@ -12867,7 +12901,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>11</v>
       </c>
@@ -12878,7 +12912,7 @@
         <v>11</v>
       </c>
       <c r="D316" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E316" t="s">
         <v>15</v>
@@ -12902,7 +12936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>11</v>
       </c>
@@ -12913,7 +12947,7 @@
         <v>11</v>
       </c>
       <c r="D317" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E317" t="s">
         <v>15</v>
@@ -12937,7 +12971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>11</v>
       </c>
@@ -12948,7 +12982,7 @@
         <v>11</v>
       </c>
       <c r="D318" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E318" t="s">
         <v>15</v>
@@ -12972,7 +13006,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>11</v>
       </c>
@@ -12983,7 +13017,7 @@
         <v>11</v>
       </c>
       <c r="D319" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E319" t="s">
         <v>15</v>
@@ -13007,7 +13041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>11</v>
       </c>
@@ -13018,7 +13052,7 @@
         <v>11</v>
       </c>
       <c r="D320" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E320" t="s">
         <v>15</v>
@@ -13042,7 +13076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>11</v>
       </c>
@@ -13053,7 +13087,7 @@
         <v>11</v>
       </c>
       <c r="D321" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E321" t="s">
         <v>15</v>
@@ -13077,7 +13111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>11</v>
       </c>
@@ -13088,7 +13122,7 @@
         <v>11</v>
       </c>
       <c r="D322" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E322" t="s">
         <v>15</v>
@@ -13112,7 +13146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>11</v>
       </c>
@@ -13123,7 +13157,7 @@
         <v>11</v>
       </c>
       <c r="D323" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E323" t="s">
         <v>15</v>
@@ -13147,7 +13181,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>11</v>
       </c>
@@ -13158,7 +13192,7 @@
         <v>11</v>
       </c>
       <c r="D324" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E324" t="s">
         <v>15</v>
@@ -13182,7 +13216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>11</v>
       </c>
@@ -13193,7 +13227,7 @@
         <v>11</v>
       </c>
       <c r="D325" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E325" t="s">
         <v>15</v>
@@ -13217,7 +13251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>11</v>
       </c>
@@ -13228,7 +13262,7 @@
         <v>11</v>
       </c>
       <c r="D326" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E326" t="s">
         <v>15</v>
@@ -13252,7 +13286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>11</v>
       </c>
@@ -13263,7 +13297,7 @@
         <v>11</v>
       </c>
       <c r="D327" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E327" t="s">
         <v>15</v>
@@ -13287,7 +13321,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>11</v>
       </c>
@@ -13298,7 +13332,7 @@
         <v>11</v>
       </c>
       <c r="D328" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E328" t="s">
         <v>15</v>
@@ -13322,7 +13356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>11</v>
       </c>
@@ -13333,7 +13367,7 @@
         <v>11</v>
       </c>
       <c r="D329" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E329" t="s">
         <v>15</v>
@@ -13357,7 +13391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>11</v>
       </c>
@@ -13368,7 +13402,7 @@
         <v>11</v>
       </c>
       <c r="D330" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E330" t="s">
         <v>15</v>
@@ -13392,7 +13426,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>11</v>
       </c>
@@ -13403,7 +13437,7 @@
         <v>11</v>
       </c>
       <c r="D331" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E331" t="s">
         <v>15</v>
@@ -13427,7 +13461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>11</v>
       </c>
@@ -13438,7 +13472,7 @@
         <v>11</v>
       </c>
       <c r="D332" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E332" t="s">
         <v>15</v>
@@ -13462,7 +13496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>11</v>
       </c>
@@ -13473,7 +13507,7 @@
         <v>11</v>
       </c>
       <c r="D333" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E333" t="s">
         <v>15</v>
@@ -13497,7 +13531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>11</v>
       </c>
@@ -13508,7 +13542,7 @@
         <v>11</v>
       </c>
       <c r="D334" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E334" t="s">
         <v>15</v>
@@ -13532,7 +13566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>11</v>
       </c>
@@ -13543,7 +13577,7 @@
         <v>11</v>
       </c>
       <c r="D335" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E335" t="s">
         <v>15</v>
@@ -13567,7 +13601,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>11</v>
       </c>
@@ -13578,7 +13612,7 @@
         <v>11</v>
       </c>
       <c r="D336" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E336" t="s">
         <v>15</v>
@@ -13602,7 +13636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>11</v>
       </c>
@@ -13613,7 +13647,7 @@
         <v>11</v>
       </c>
       <c r="D337" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E337" t="s">
         <v>15</v>
@@ -13637,7 +13671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>11</v>
       </c>
@@ -13648,7 +13682,7 @@
         <v>11</v>
       </c>
       <c r="D338" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E338" t="s">
         <v>15</v>
@@ -13672,7 +13706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>11</v>
       </c>
@@ -13683,7 +13717,7 @@
         <v>11</v>
       </c>
       <c r="D339" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E339" t="s">
         <v>15</v>
@@ -13707,7 +13741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>11</v>
       </c>
@@ -13718,7 +13752,7 @@
         <v>11</v>
       </c>
       <c r="D340" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E340" t="s">
         <v>15</v>
@@ -13742,7 +13776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>11</v>
       </c>
@@ -13753,7 +13787,7 @@
         <v>11</v>
       </c>
       <c r="D341" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E341" t="s">
         <v>15</v>
@@ -13777,7 +13811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>11</v>
       </c>
@@ -13788,7 +13822,7 @@
         <v>11</v>
       </c>
       <c r="D342" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E342" t="s">
         <v>15</v>
@@ -13812,7 +13846,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>11</v>
       </c>
@@ -13823,7 +13857,7 @@
         <v>11</v>
       </c>
       <c r="D343" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E343" t="s">
         <v>15</v>
@@ -13847,7 +13881,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>11</v>
       </c>
@@ -13858,7 +13892,7 @@
         <v>11</v>
       </c>
       <c r="D344" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E344" t="s">
         <v>15</v>
@@ -13882,7 +13916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>11</v>
       </c>
@@ -13893,7 +13927,7 @@
         <v>11</v>
       </c>
       <c r="D345" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E345" t="s">
         <v>15</v>
@@ -13917,7 +13951,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>11</v>
       </c>
@@ -13928,7 +13962,7 @@
         <v>11</v>
       </c>
       <c r="D346" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E346" t="s">
         <v>15</v>
@@ -13952,7 +13986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>11</v>
       </c>
@@ -13963,7 +13997,7 @@
         <v>11</v>
       </c>
       <c r="D347" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E347" t="s">
         <v>15</v>
@@ -13987,7 +14021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>11</v>
       </c>
@@ -13998,7 +14032,7 @@
         <v>11</v>
       </c>
       <c r="D348" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E348" t="s">
         <v>15</v>
@@ -14022,7 +14056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>11</v>
       </c>
@@ -14033,7 +14067,7 @@
         <v>11</v>
       </c>
       <c r="D349" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E349" t="s">
         <v>15</v>
@@ -14057,7 +14091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>11</v>
       </c>
@@ -14068,7 +14102,7 @@
         <v>11</v>
       </c>
       <c r="D350" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E350" t="s">
         <v>15</v>
@@ -14092,7 +14126,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>11</v>
       </c>
@@ -14103,7 +14137,7 @@
         <v>11</v>
       </c>
       <c r="D351" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E351" t="s">
         <v>15</v>
@@ -14127,7 +14161,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>11</v>
       </c>
@@ -14138,7 +14172,7 @@
         <v>11</v>
       </c>
       <c r="D352" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E352" t="s">
         <v>15</v>
@@ -14162,7 +14196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>11</v>
       </c>
@@ -14173,7 +14207,7 @@
         <v>11</v>
       </c>
       <c r="D353" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E353" t="s">
         <v>15</v>
@@ -14197,7 +14231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>11</v>
       </c>
@@ -14208,7 +14242,7 @@
         <v>11</v>
       </c>
       <c r="D354" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E354" t="s">
         <v>15</v>
@@ -14232,7 +14266,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>11</v>
       </c>
@@ -14243,7 +14277,7 @@
         <v>11</v>
       </c>
       <c r="D355" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E355" t="s">
         <v>15</v>
@@ -14267,7 +14301,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>11</v>
       </c>
@@ -14278,7 +14312,7 @@
         <v>11</v>
       </c>
       <c r="D356" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E356" t="s">
         <v>15</v>
@@ -14302,7 +14336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>11</v>
       </c>
@@ -14313,7 +14347,7 @@
         <v>11</v>
       </c>
       <c r="D357" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E357" t="s">
         <v>15</v>
@@ -14337,7 +14371,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>11</v>
       </c>
@@ -14348,7 +14382,7 @@
         <v>11</v>
       </c>
       <c r="D358" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E358" t="s">
         <v>15</v>
@@ -14372,7 +14406,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>11</v>
       </c>
@@ -14383,7 +14417,7 @@
         <v>11</v>
       </c>
       <c r="D359" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E359" t="s">
         <v>15</v>
@@ -14407,7 +14441,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>11</v>
       </c>
@@ -14418,7 +14452,7 @@
         <v>11</v>
       </c>
       <c r="D360" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E360" t="s">
         <v>15</v>
@@ -14442,7 +14476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>11</v>
       </c>
@@ -14453,7 +14487,7 @@
         <v>11</v>
       </c>
       <c r="D361" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E361" t="s">
         <v>15</v>
@@ -14477,7 +14511,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>11</v>
       </c>
@@ -14488,7 +14522,7 @@
         <v>11</v>
       </c>
       <c r="D362" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E362" t="s">
         <v>15</v>
@@ -14512,7 +14546,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>11</v>
       </c>
@@ -14523,7 +14557,7 @@
         <v>11</v>
       </c>
       <c r="D363" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E363" t="s">
         <v>15</v>
@@ -14547,7 +14581,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>11</v>
       </c>
@@ -14558,7 +14592,7 @@
         <v>11</v>
       </c>
       <c r="D364" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E364" t="s">
         <v>15</v>
@@ -14582,7 +14616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>11</v>
       </c>
@@ -14593,7 +14627,7 @@
         <v>11</v>
       </c>
       <c r="D365" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E365" t="s">
         <v>15</v>
@@ -14617,7 +14651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>11</v>
       </c>
@@ -14628,7 +14662,7 @@
         <v>11</v>
       </c>
       <c r="D366" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="E366" t="s">
         <v>15</v>
@@ -14652,7 +14686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>11</v>
       </c>
@@ -14663,7 +14697,7 @@
         <v>11</v>
       </c>
       <c r="D367" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E367" t="s">
         <v>15</v>
@@ -14687,7 +14721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>11</v>
       </c>
@@ -14698,7 +14732,7 @@
         <v>11</v>
       </c>
       <c r="D368" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E368" t="s">
         <v>15</v>
@@ -14722,7 +14756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>11</v>
       </c>
@@ -14733,7 +14767,7 @@
         <v>11</v>
       </c>
       <c r="D369" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E369" t="s">
         <v>15</v>
@@ -14757,7 +14791,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>11</v>
       </c>
@@ -14768,7 +14802,7 @@
         <v>11</v>
       </c>
       <c r="D370" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E370" t="s">
         <v>15</v>
@@ -14792,7 +14826,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>11</v>
       </c>
@@ -14803,7 +14837,7 @@
         <v>11</v>
       </c>
       <c r="D371" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E371" t="s">
         <v>15</v>
@@ -14827,7 +14861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>11</v>
       </c>
@@ -14838,7 +14872,7 @@
         <v>11</v>
       </c>
       <c r="D372" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E372" t="s">
         <v>15</v>
@@ -14862,7 +14896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>11</v>
       </c>
@@ -14873,7 +14907,7 @@
         <v>11</v>
       </c>
       <c r="D373" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E373" t="s">
         <v>15</v>
@@ -14897,7 +14931,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>11</v>
       </c>
@@ -14908,7 +14942,7 @@
         <v>11</v>
       </c>
       <c r="D374" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E374" t="s">
         <v>15</v>
@@ -14932,7 +14966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>11</v>
       </c>
@@ -14943,7 +14977,7 @@
         <v>11</v>
       </c>
       <c r="D375" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E375" t="s">
         <v>15</v>
@@ -14967,7 +15001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>11</v>
       </c>
@@ -14978,7 +15012,7 @@
         <v>11</v>
       </c>
       <c r="D376" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E376" t="s">
         <v>15</v>
@@ -15002,7 +15036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>11</v>
       </c>
@@ -15013,7 +15047,7 @@
         <v>11</v>
       </c>
       <c r="D377" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E377" t="s">
         <v>15</v>
@@ -15037,7 +15071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>11</v>
       </c>
@@ -15048,7 +15082,7 @@
         <v>11</v>
       </c>
       <c r="D378" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="E378" t="s">
         <v>15</v>
@@ -15072,7 +15106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>11</v>
       </c>
@@ -15083,7 +15117,7 @@
         <v>11</v>
       </c>
       <c r="D379" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E379" t="s">
         <v>15</v>
@@ -15107,7 +15141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>11</v>
       </c>
@@ -15118,7 +15152,7 @@
         <v>11</v>
       </c>
       <c r="D380" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E380" t="s">
         <v>15</v>
@@ -15142,7 +15176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>11</v>
       </c>
@@ -15153,7 +15187,7 @@
         <v>11</v>
       </c>
       <c r="D381" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E381" t="s">
         <v>15</v>
@@ -15177,7 +15211,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>11</v>
       </c>
@@ -15188,7 +15222,7 @@
         <v>11</v>
       </c>
       <c r="D382" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E382" t="s">
         <v>15</v>
@@ -15212,7 +15246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>11</v>
       </c>
@@ -15223,7 +15257,7 @@
         <v>11</v>
       </c>
       <c r="D383" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E383" t="s">
         <v>15</v>
@@ -15247,7 +15281,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>11</v>
       </c>
@@ -15258,7 +15292,7 @@
         <v>11</v>
       </c>
       <c r="D384" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E384" t="s">
         <v>15</v>
@@ -15282,7 +15316,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>11</v>
       </c>
@@ -15293,7 +15327,7 @@
         <v>11</v>
       </c>
       <c r="D385" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E385" t="s">
         <v>15</v>
@@ -15317,7 +15351,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>11</v>
       </c>
@@ -15328,7 +15362,7 @@
         <v>11</v>
       </c>
       <c r="D386" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="E386" t="s">
         <v>15</v>
@@ -15352,7 +15386,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>11</v>
       </c>
@@ -15363,7 +15397,7 @@
         <v>11</v>
       </c>
       <c r="D387" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E387" t="s">
         <v>15</v>
@@ -15387,7 +15421,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>11</v>
       </c>
@@ -15398,7 +15432,7 @@
         <v>11</v>
       </c>
       <c r="D388" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="E388" t="s">
         <v>15</v>
@@ -15422,7 +15456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>11</v>
       </c>
@@ -15433,7 +15467,7 @@
         <v>11</v>
       </c>
       <c r="D389" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E389" t="s">
         <v>15</v>
@@ -15457,7 +15491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>11</v>
       </c>
@@ -15468,7 +15502,7 @@
         <v>11</v>
       </c>
       <c r="D390" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="E390" t="s">
         <v>15</v>
@@ -15492,7 +15526,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>11</v>
       </c>
@@ -15503,7 +15537,7 @@
         <v>11</v>
       </c>
       <c r="D391" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E391" t="s">
         <v>15</v>
@@ -15527,7 +15561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>11</v>
       </c>
@@ -15538,7 +15572,7 @@
         <v>11</v>
       </c>
       <c r="D392" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E392" t="s">
         <v>15</v>
@@ -15562,7 +15596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>11</v>
       </c>
@@ -15573,7 +15607,7 @@
         <v>11</v>
       </c>
       <c r="D393" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E393" t="s">
         <v>15</v>
@@ -15597,7 +15631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>11</v>
       </c>
@@ -15608,7 +15642,7 @@
         <v>11</v>
       </c>
       <c r="D394" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="E394" t="s">
         <v>15</v>
@@ -15632,7 +15666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>11</v>
       </c>
@@ -15643,7 +15677,7 @@
         <v>11</v>
       </c>
       <c r="D395" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E395" t="s">
         <v>15</v>
@@ -15667,7 +15701,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>11</v>
       </c>
@@ -15678,7 +15712,7 @@
         <v>11</v>
       </c>
       <c r="D396" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="E396" t="s">
         <v>15</v>
@@ -15702,7 +15736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>11</v>
       </c>
@@ -15713,7 +15747,7 @@
         <v>11</v>
       </c>
       <c r="D397" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E397" t="s">
         <v>15</v>
@@ -15737,7 +15771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>11</v>
       </c>
@@ -15748,7 +15782,7 @@
         <v>11</v>
       </c>
       <c r="D398" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E398" t="s">
         <v>15</v>
@@ -15772,7 +15806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>11</v>
       </c>
@@ -15783,7 +15817,7 @@
         <v>11</v>
       </c>
       <c r="D399" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E399" t="s">
         <v>15</v>
@@ -15807,7 +15841,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>11</v>
       </c>
@@ -15818,7 +15852,7 @@
         <v>11</v>
       </c>
       <c r="D400" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E400" t="s">
         <v>15</v>
@@ -15842,7 +15876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>11</v>
       </c>
@@ -15853,7 +15887,7 @@
         <v>11</v>
       </c>
       <c r="D401" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E401" t="s">
         <v>15</v>
@@ -15877,7 +15911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>11</v>
       </c>
@@ -15888,7 +15922,7 @@
         <v>11</v>
       </c>
       <c r="D402" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E402" t="s">
         <v>15</v>
@@ -15912,7 +15946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>11</v>
       </c>
@@ -15923,7 +15957,7 @@
         <v>11</v>
       </c>
       <c r="D403" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E403" t="s">
         <v>15</v>
@@ -15947,7 +15981,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>11</v>
       </c>
@@ -15958,7 +15992,7 @@
         <v>11</v>
       </c>
       <c r="D404" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E404" t="s">
         <v>15</v>
@@ -15982,7 +16016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>11</v>
       </c>
@@ -15993,7 +16027,7 @@
         <v>11</v>
       </c>
       <c r="D405" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E405" t="s">
         <v>15</v>
@@ -16017,7 +16051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>11</v>
       </c>
@@ -16028,7 +16062,7 @@
         <v>11</v>
       </c>
       <c r="D406" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="E406" t="s">
         <v>15</v>
@@ -16052,7 +16086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>11</v>
       </c>
@@ -16063,7 +16097,7 @@
         <v>11</v>
       </c>
       <c r="D407" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E407" t="s">
         <v>15</v>
@@ -16087,7 +16121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>11</v>
       </c>
@@ -16098,7 +16132,7 @@
         <v>11</v>
       </c>
       <c r="D408" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E408" t="s">
         <v>15</v>
@@ -16122,7 +16156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>11</v>
       </c>
@@ -16133,7 +16167,7 @@
         <v>11</v>
       </c>
       <c r="D409" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E409" t="s">
         <v>15</v>
@@ -16157,7 +16191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>11</v>
       </c>
@@ -16168,7 +16202,7 @@
         <v>11</v>
       </c>
       <c r="D410" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E410" t="s">
         <v>15</v>
@@ -16192,7 +16226,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>11</v>
       </c>
@@ -16203,7 +16237,7 @@
         <v>11</v>
       </c>
       <c r="D411" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E411" t="s">
         <v>15</v>
@@ -16227,7 +16261,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>11</v>
       </c>
@@ -16238,7 +16272,7 @@
         <v>11</v>
       </c>
       <c r="D412" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E412" t="s">
         <v>15</v>
@@ -16262,7 +16296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>11</v>
       </c>
@@ -16273,7 +16307,7 @@
         <v>11</v>
       </c>
       <c r="D413" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E413" t="s">
         <v>15</v>
@@ -16297,7 +16331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>11</v>
       </c>
@@ -16308,7 +16342,7 @@
         <v>11</v>
       </c>
       <c r="D414" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E414" t="s">
         <v>15</v>
@@ -16332,7 +16366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>11</v>
       </c>
@@ -16343,7 +16377,7 @@
         <v>11</v>
       </c>
       <c r="D415" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E415" t="s">
         <v>15</v>
@@ -16367,7 +16401,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>11</v>
       </c>
@@ -16378,7 +16412,7 @@
         <v>11</v>
       </c>
       <c r="D416" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E416" t="s">
         <v>15</v>
@@ -16402,7 +16436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>11</v>
       </c>
@@ -16413,7 +16447,7 @@
         <v>11</v>
       </c>
       <c r="D417" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E417" t="s">
         <v>15</v>
@@ -16437,7 +16471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>11</v>
       </c>
@@ -16448,7 +16482,7 @@
         <v>11</v>
       </c>
       <c r="D418" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E418" t="s">
         <v>15</v>
@@ -16472,7 +16506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>11</v>
       </c>
@@ -16483,7 +16517,7 @@
         <v>11</v>
       </c>
       <c r="D419" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E419" t="s">
         <v>15</v>
@@ -16507,7 +16541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>11</v>
       </c>
@@ -16518,7 +16552,7 @@
         <v>11</v>
       </c>
       <c r="D420" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E420" t="s">
         <v>15</v>
@@ -16542,7 +16576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>11</v>
       </c>
@@ -16553,7 +16587,7 @@
         <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E421" t="s">
         <v>15</v>
@@ -16577,7 +16611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>11</v>
       </c>
@@ -16588,7 +16622,7 @@
         <v>11</v>
       </c>
       <c r="D422" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E422" t="s">
         <v>15</v>
@@ -16612,7 +16646,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>11</v>
       </c>
@@ -16623,7 +16657,7 @@
         <v>11</v>
       </c>
       <c r="D423" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E423" t="s">
         <v>15</v>
@@ -16647,7 +16681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>11</v>
       </c>
@@ -16658,7 +16692,7 @@
         <v>11</v>
       </c>
       <c r="D424" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E424" t="s">
         <v>15</v>
@@ -16682,7 +16716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>11</v>
       </c>
@@ -16693,7 +16727,7 @@
         <v>11</v>
       </c>
       <c r="D425" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E425" t="s">
         <v>15</v>
@@ -16717,7 +16751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>11</v>
       </c>
@@ -16728,7 +16762,7 @@
         <v>11</v>
       </c>
       <c r="D426" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E426" t="s">
         <v>15</v>
@@ -16752,7 +16786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>11</v>
       </c>
@@ -16763,7 +16797,7 @@
         <v>11</v>
       </c>
       <c r="D427" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E427" t="s">
         <v>15</v>
@@ -16787,7 +16821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>11</v>
       </c>
@@ -16798,7 +16832,7 @@
         <v>11</v>
       </c>
       <c r="D428" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E428" t="s">
         <v>15</v>
@@ -16822,7 +16856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>11</v>
       </c>
@@ -16833,7 +16867,7 @@
         <v>11</v>
       </c>
       <c r="D429" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E429" t="s">
         <v>15</v>
@@ -16857,7 +16891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>11</v>
       </c>
@@ -16868,7 +16902,7 @@
         <v>11</v>
       </c>
       <c r="D430" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E430" t="s">
         <v>15</v>
@@ -16892,7 +16926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>11</v>
       </c>
@@ -16903,7 +16937,7 @@
         <v>11</v>
       </c>
       <c r="D431" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E431" t="s">
         <v>15</v>
@@ -16927,7 +16961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>11</v>
       </c>
@@ -16938,7 +16972,7 @@
         <v>11</v>
       </c>
       <c r="D432" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E432" t="s">
         <v>15</v>
@@ -16962,7 +16996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>11</v>
       </c>
@@ -16973,7 +17007,7 @@
         <v>11</v>
       </c>
       <c r="D433" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E433" t="s">
         <v>15</v>
@@ -16997,7 +17031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>11</v>
       </c>
@@ -17008,7 +17042,7 @@
         <v>11</v>
       </c>
       <c r="D434" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E434" t="s">
         <v>15</v>
@@ -17032,7 +17066,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>11</v>
       </c>
@@ -17043,7 +17077,7 @@
         <v>11</v>
       </c>
       <c r="D435" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="E435" t="s">
         <v>15</v>
@@ -17067,7 +17101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>11</v>
       </c>
@@ -17078,7 +17112,7 @@
         <v>11</v>
       </c>
       <c r="D436" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E436" t="s">
         <v>15</v>
@@ -17102,7 +17136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>11</v>
       </c>
@@ -17113,7 +17147,7 @@
         <v>11</v>
       </c>
       <c r="D437" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E437" t="s">
         <v>15</v>
@@ -17137,7 +17171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>11</v>
       </c>
@@ -17148,7 +17182,7 @@
         <v>11</v>
       </c>
       <c r="D438" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E438" t="s">
         <v>15</v>
@@ -17172,7 +17206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>11</v>
       </c>
@@ -17183,7 +17217,7 @@
         <v>11</v>
       </c>
       <c r="D439" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E439" t="s">
         <v>15</v>
@@ -17207,7 +17241,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>11</v>
       </c>
@@ -17218,7 +17252,7 @@
         <v>11</v>
       </c>
       <c r="D440" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E440" t="s">
         <v>15</v>
@@ -17242,7 +17276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>11</v>
       </c>
@@ -17253,7 +17287,7 @@
         <v>11</v>
       </c>
       <c r="D441" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="E441" t="s">
         <v>15</v>
@@ -17277,7 +17311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>11</v>
       </c>
@@ -17288,7 +17322,7 @@
         <v>11</v>
       </c>
       <c r="D442" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E442" t="s">
         <v>15</v>
@@ -17312,7 +17346,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>11</v>
       </c>
@@ -17323,7 +17357,7 @@
         <v>11</v>
       </c>
       <c r="D443" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E443" t="s">
         <v>15</v>
@@ -17347,7 +17381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>11</v>
       </c>
@@ -17358,7 +17392,7 @@
         <v>11</v>
       </c>
       <c r="D444" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E444" t="s">
         <v>15</v>
@@ -17382,7 +17416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>11</v>
       </c>
@@ -17393,7 +17427,7 @@
         <v>11</v>
       </c>
       <c r="D445" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E445" t="s">
         <v>15</v>
@@ -17417,7 +17451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>11</v>
       </c>
@@ -17428,7 +17462,7 @@
         <v>11</v>
       </c>
       <c r="D446" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="E446" t="s">
         <v>15</v>
@@ -17452,7 +17486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>11</v>
       </c>
@@ -17463,7 +17497,7 @@
         <v>11</v>
       </c>
       <c r="D447" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E447" t="s">
         <v>15</v>
@@ -17487,7 +17521,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>11</v>
       </c>
@@ -17498,7 +17532,7 @@
         <v>11</v>
       </c>
       <c r="D448" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E448" t="s">
         <v>15</v>
@@ -17522,7 +17556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>11</v>
       </c>
@@ -17533,7 +17567,7 @@
         <v>11</v>
       </c>
       <c r="D449" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E449" t="s">
         <v>15</v>
@@ -17557,7 +17591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>11</v>
       </c>
@@ -17568,7 +17602,7 @@
         <v>11</v>
       </c>
       <c r="D450" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E450" t="s">
         <v>15</v>
@@ -17592,7 +17626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>11</v>
       </c>
@@ -17603,7 +17637,7 @@
         <v>11</v>
       </c>
       <c r="D451" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E451" t="s">
         <v>15</v>
@@ -17627,7 +17661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>11</v>
       </c>
@@ -17638,7 +17672,7 @@
         <v>11</v>
       </c>
       <c r="D452" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E452" t="s">
         <v>15</v>
@@ -17662,7 +17696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>11</v>
       </c>
@@ -17673,7 +17707,7 @@
         <v>11</v>
       </c>
       <c r="D453" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E453" t="s">
         <v>15</v>
@@ -17697,7 +17731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>11</v>
       </c>
@@ -17708,7 +17742,7 @@
         <v>11</v>
       </c>
       <c r="D454" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E454" t="s">
         <v>15</v>
@@ -17732,7 +17766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>11</v>
       </c>
@@ -17743,7 +17777,7 @@
         <v>11</v>
       </c>
       <c r="D455" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E455" t="s">
         <v>15</v>
@@ -17767,7 +17801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>11</v>
       </c>
@@ -17778,7 +17812,7 @@
         <v>11</v>
       </c>
       <c r="D456" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E456" t="s">
         <v>15</v>
@@ -17802,7 +17836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>11</v>
       </c>
@@ -17813,7 +17847,7 @@
         <v>11</v>
       </c>
       <c r="D457" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E457" t="s">
         <v>15</v>
@@ -17837,7 +17871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>11</v>
       </c>
@@ -17848,7 +17882,7 @@
         <v>11</v>
       </c>
       <c r="D458" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E458" t="s">
         <v>15</v>
@@ -17872,7 +17906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>11</v>
       </c>
@@ -17883,7 +17917,7 @@
         <v>11</v>
       </c>
       <c r="D459" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E459" t="s">
         <v>15</v>
@@ -17907,7 +17941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>11</v>
       </c>
@@ -17918,7 +17952,7 @@
         <v>11</v>
       </c>
       <c r="D460" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="E460" t="s">
         <v>15</v>
@@ -17942,7 +17976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>11</v>
       </c>
@@ -17953,7 +17987,7 @@
         <v>11</v>
       </c>
       <c r="D461" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E461" t="s">
         <v>15</v>
@@ -17977,7 +18011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>11</v>
       </c>
@@ -17988,7 +18022,7 @@
         <v>11</v>
       </c>
       <c r="D462" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E462" t="s">
         <v>15</v>
@@ -18012,7 +18046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>11</v>
       </c>
@@ -18023,7 +18057,7 @@
         <v>11</v>
       </c>
       <c r="D463" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E463" t="s">
         <v>15</v>
@@ -18047,7 +18081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>11</v>
       </c>
@@ -18058,7 +18092,7 @@
         <v>11</v>
       </c>
       <c r="D464" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E464" t="s">
         <v>15</v>
@@ -18082,7 +18116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>11</v>
       </c>
@@ -18093,7 +18127,7 @@
         <v>11</v>
       </c>
       <c r="D465" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E465" t="s">
         <v>15</v>
@@ -18117,7 +18151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>11</v>
       </c>
@@ -18128,7 +18162,7 @@
         <v>11</v>
       </c>
       <c r="D466" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E466" t="s">
         <v>15</v>
@@ -18177,6 +18211,6 @@
     <hyperlink ref="D13" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
+++ b/channels/スカッと汚嫁ニャンバ/oyome-nyanba.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="11700"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Kênh YouTube" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5105" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5084" uniqueCount="485">
   <si>
     <t>EMAIL</t>
   </si>
@@ -137,49 +137,49 @@
     <t>https://www.youtube.com/watch?v=4Tj_V3MT800</t>
   </si>
   <si>
-    <t>【修羅場な話】嫁が家で間男と行為してた…間男「旦那と離婚しなよ！愛人としてお前を幸せにしてやる！」嫁「本当！？嬉しい！」→嫁「助けて！」俺「警察！」【朗読】</t>
+    <t>【修羅場】「寂しくて浮気した」と家を出た嫁が半年後にSOS…？変わり果てた姿で泣きつく元嫁に、俺が放った”残酷すぎる一言”とは…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#修羅場 #浮気 #スカッとする話 #離婚 #復讐
+「寂しかったから浮気した」
+身勝手な言い訳を残して家を出た嫁が、半年後にボロボロの姿で現れた。
+変わり果てた元嫁が泣きながら放ったSOS。
+そんな彼女に俺が言い放った、残酷すぎる一言とは……。
+【今回のあらすじ】
+仕事の決算で忙しかった3月末、たった2週間のすれ違いを理由に浮気に走った妻。
+相手はあろうことか、嫁友の旦那である「間男」だった。
+鉄の意志を持つ嫁友と共に、不倫の証拠を叩きつけ、慰謝料をきっちり回収して離婚。
+すべてが終わったはずだったが、半年後、俺の家のインターホンが鳴る。
+そこに立っていたのは、間男とのバラ色の生活を送っているはずの元嫁だった。
+悲惨な現実から逃げ出してきた彼女への、俺なりの「最後通牒」をお聞きください。
+修羅子のドロドロ人生朗読では、日常で起こるスカッとする話や衝撃の体験談を投稿しています。
+もし気に入っていただけたら、チャンネル登録と高評価で応援していただけると励みになります！
+皆さんの感想もコメント欄でお待ちしています。
+#不倫の末路 #因果応報 #泥沼 #スカッと #サレ夫 #2ch #朗読 #実話 #スカッとする話 #人間関係</t>
+  </si>
+  <si>
+    <t>修羅場,スカッとする話,修羅場な話,朗読,その後,因果応報,スカッと,復讐,浮気,不倫,離婚,後悔,DQN返し,スッキリ,汚嫁,慰謝料,旦那,撃退,間男,浮気男,サレ夫,逆襲,不倫の末路,浮気の代償,5ch,2ch,泥沼,修羅場実録,自業自得,捨てられた元嫁,浮気した嫁が半年後に泣きついてきた話,寂しいという理由で不倫した妻の末路,間男と駆け落ちした元嫁の悲惨な現状,不倫相手に捨てられた元妻がSOS,離婚後に元嫁がボロボロになって戻ってきた,浮気した妻に放った残酷な一言,浮気されて離婚した夫のその後の生活,間男との生活が地獄だった元嫁の話,自分勝手な言い訳で不倫した嫁への復讐,浮気嫁を警察に突き出した結果スカッとした</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=5SkR8ViDXpg</t>
   </si>
   <si>
-    <t>【修羅場な話】嫁が不倫した。間嫁「大事な話がある。お宅の嫁と私の夫が不倫してる」俺「えっ！？」急いでファミレスに向かうと... 間嫁「制裁の条件は...慰謝料は山分けしましょう」俺「おｋ」→結果【朗読</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=0mMZPZmigGU</t>
   </si>
   <si>
-    <t>【修羅場な話】嫁が不倫をしていたが一度だけチャンスを与えるため夫婦水入らずの旅行に誘いました。嫁「分かった、会社に休めるか聞いてみる」すると旅行に行く3日前に嫁はこう言ってきたんです…【朗読】</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=KBXHQHWkls4</t>
   </si>
   <si>
-    <t>【修羅場な話】嫁の不倫で離婚し、しばらくして間男が訪ねて来た！俺「何の用だ？うちには嫁はもう居ないぞ！」間男はこう言って来たんです…【朗読】</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=cgb3zEvU6ak</t>
   </si>
   <si>
-    <t>【修羅場な話】義兄夫婦が離婚することに。義嫁「引っ越すからもう会う機会もないと思うので、これ渡しておきます。」封筒の中身を確認すると…【朗読】</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=ZtAPTciroF8</t>
   </si>
   <si>
-    <t>【修羅場な話】うちの両親は仮面夫婦です私「お父さん、離婚していいよ」父「お父さんはお母さんに復讐をしているんだよ」私「え？」【朗読】</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=DKWm1RuMqoU</t>
   </si>
   <si>
-    <t>【修羅場な話】車の中に大量のDVDがあり中身を確認すると…嫁「黙っててゴメン。でも、言ったら絶対怒ってたでしょ？」そして離婚を決断しました【朗読】</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=bsmxfFubyAo</t>
-  </si>
-  <si>
-    <t>【修羅場な話】目を覚ますと精神病院の隔離病棟だった。俺「姉貴…これ今どういう状況…？」姉貴「あんた、何も憶えてないの？この5日間のこと…」姉貴は残酷な事実を話し始めました…【朗読】</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=BEIP_UBAXbY</t>
@@ -1545,7 +1545,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1564,14 +1564,6 @@
     <font>
       <charset val="134"/>
       <color theme="1"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <color theme="10"/>
-      <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1610,7 +1602,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1671,7 +1663,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1706,7 +1698,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1880,12 +1872,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -2074,10 +2060,10 @@
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
         <v>11</v>
@@ -2097,19 +2083,10 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>11</v>
@@ -2132,19 +2109,10 @@
         <v>11</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>11</v>
@@ -2172,15 +2140,6 @@
       <c r="E9" t="s">
         <v>15</v>
       </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
       <c r="I9" t="s">
         <v>11</v>
       </c>
@@ -2202,19 +2161,10 @@
         <v>11</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
@@ -2237,19 +2187,10 @@
         <v>11</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>11</v>
@@ -2272,19 +2213,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" t="s">
-        <v>18</v>
       </c>
       <c r="I12" t="s">
         <v>11</v>
@@ -2307,19 +2239,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
       </c>
       <c r="I13" t="s">
         <v>11</v>
@@ -2342,7 +2265,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2377,7 +2300,7 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -2412,7 +2335,7 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -2447,7 +2370,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -2482,7 +2405,7 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -2517,7 +2440,7 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -2552,7 +2475,7 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -2587,7 +2510,7 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -2622,7 +2545,7 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -2657,7 +2580,7 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -2692,7 +2615,7 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -2727,7 +2650,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -2762,7 +2685,7 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -2797,7 +2720,7 @@
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -2832,7 +2755,7 @@
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -2867,7 +2790,7 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -2902,7 +2825,7 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -2937,7 +2860,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -2972,7 +2895,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3007,7 +2930,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3042,7 +2965,7 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3077,7 +3000,7 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3112,7 +3035,7 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -3147,7 +3070,7 @@
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3182,7 +3105,7 @@
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -3217,7 +3140,7 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -3252,7 +3175,7 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -3287,7 +3210,7 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -3322,7 +3245,7 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -3357,7 +3280,7 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -3392,7 +3315,7 @@
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -3427,7 +3350,7 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -3462,7 +3385,7 @@
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -3497,7 +3420,7 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -3532,7 +3455,7 @@
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -3567,7 +3490,7 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -3602,7 +3525,7 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -3637,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -3672,7 +3595,7 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -3707,7 +3630,7 @@
         <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -3742,7 +3665,7 @@
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -3777,7 +3700,7 @@
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -3812,7 +3735,7 @@
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -3847,7 +3770,7 @@
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -3882,7 +3805,7 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -3917,7 +3840,7 @@
         <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -3952,7 +3875,7 @@
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -3987,7 +3910,7 @@
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -4022,7 +3945,7 @@
         <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -4057,7 +3980,7 @@
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -4092,7 +4015,7 @@
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -4127,7 +4050,7 @@
         <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -4162,7 +4085,7 @@
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -4197,7 +4120,7 @@
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -4232,7 +4155,7 @@
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -4267,7 +4190,7 @@
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -4302,7 +4225,7 @@
         <v>11</v>
       </c>
       <c r="D70" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -4337,7 +4260,7 @@
         <v>11</v>
       </c>
       <c r="D71" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -4372,7 +4295,7 @@
         <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -4407,7 +4330,7 @@
         <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -4442,7 +4365,7 @@
         <v>11</v>
       </c>
       <c r="D74" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -4477,7 +4400,7 @@
         <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -4512,7 +4435,7 @@
         <v>11</v>
       </c>
       <c r="D76" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -4547,7 +4470,7 @@
         <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -4582,7 +4505,7 @@
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -4617,7 +4540,7 @@
         <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -4652,7 +4575,7 @@
         <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -4687,7 +4610,7 @@
         <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E81" t="s">
         <v>15</v>
@@ -4722,7 +4645,7 @@
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
@@ -4757,7 +4680,7 @@
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E83" t="s">
         <v>15</v>
@@ -4792,7 +4715,7 @@
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -4827,7 +4750,7 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -4862,7 +4785,7 @@
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
@@ -4897,7 +4820,7 @@
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -4932,7 +4855,7 @@
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -4967,7 +4890,7 @@
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -5002,7 +4925,7 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -5037,7 +4960,7 @@
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -5072,7 +4995,7 @@
         <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -5107,7 +5030,7 @@
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -5142,7 +5065,7 @@
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -5177,7 +5100,7 @@
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -5212,7 +5135,7 @@
         <v>11</v>
       </c>
       <c r="D96" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E96" t="s">
         <v>15</v>
@@ -5247,7 +5170,7 @@
         <v>11</v>
       </c>
       <c r="D97" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E97" t="s">
         <v>15</v>
@@ -5282,7 +5205,7 @@
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E98" t="s">
         <v>15</v>
@@ -5317,7 +5240,7 @@
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E99" t="s">
         <v>15</v>
@@ -5352,7 +5275,7 @@
         <v>11</v>
       </c>
       <c r="D100" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E100" t="s">
         <v>15</v>
@@ -5387,7 +5310,7 @@
         <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E101" t="s">
         <v>15</v>
@@ -5422,7 +5345,7 @@
         <v>11</v>
       </c>
       <c r="D102" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E102" t="s">
         <v>15</v>
@@ -5457,7 +5380,7 @@
         <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E103" t="s">
         <v>15</v>
@@ -5492,7 +5415,7 @@
         <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E104" t="s">
         <v>15</v>
@@ -5527,7 +5450,7 @@
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E105" t="s">
         <v>15</v>
@@ -5562,7 +5485,7 @@
         <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E106" t="s">
         <v>15</v>
@@ -5597,7 +5520,7 @@
         <v>11</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E107" t="s">
         <v>15</v>
@@ -5632,7 +5555,7 @@
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E108" t="s">
         <v>15</v>
@@ -5667,7 +5590,7 @@
         <v>11</v>
       </c>
       <c r="D109" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E109" t="s">
         <v>15</v>
@@ -5702,7 +5625,7 @@
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E110" t="s">
         <v>15</v>
@@ -5737,7 +5660,7 @@
         <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E111" t="s">
         <v>15</v>
@@ -5772,7 +5695,7 @@
         <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E112" t="s">
         <v>15</v>
@@ -5807,7 +5730,7 @@
         <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E113" t="s">
         <v>15</v>
@@ -5842,7 +5765,7 @@
         <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E114" t="s">
         <v>15</v>
@@ -5877,7 +5800,7 @@
         <v>11</v>
       </c>
       <c r="D115" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E115" t="s">
         <v>15</v>
@@ -5912,7 +5835,7 @@
         <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E116" t="s">
         <v>15</v>
@@ -5947,7 +5870,7 @@
         <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E117" t="s">
         <v>15</v>
@@ -5982,7 +5905,7 @@
         <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E118" t="s">
         <v>15</v>
@@ -6017,7 +5940,7 @@
         <v>11</v>
       </c>
       <c r="D119" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E119" t="s">
         <v>15</v>
@@ -6052,7 +5975,7 @@
         <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E120" t="s">
         <v>15</v>
@@ -6087,7 +6010,7 @@
         <v>11</v>
       </c>
       <c r="D121" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E121" t="s">
         <v>15</v>
@@ -6122,7 +6045,7 @@
         <v>11</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E122" t="s">
         <v>15</v>
@@ -6157,7 +6080,7 @@
         <v>11</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E123" t="s">
         <v>15</v>
@@ -6192,7 +6115,7 @@
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E124" t="s">
         <v>15</v>
@@ -6227,7 +6150,7 @@
         <v>11</v>
       </c>
       <c r="D125" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E125" t="s">
         <v>15</v>
@@ -6262,7 +6185,7 @@
         <v>11</v>
       </c>
       <c r="D126" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
@@ -6297,7 +6220,7 @@
         <v>11</v>
       </c>
       <c r="D127" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E127" t="s">
         <v>15</v>
@@ -6332,7 +6255,7 @@
         <v>11</v>
       </c>
       <c r="D128" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E128" t="s">
         <v>15</v>
@@ -6367,7 +6290,7 @@
         <v>11</v>
       </c>
       <c r="D129" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E129" t="s">
         <v>15</v>
@@ -6402,7 +6325,7 @@
         <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E130" t="s">
         <v>15</v>
@@ -6437,7 +6360,7 @@
         <v>11</v>
       </c>
       <c r="D131" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E131" t="s">
         <v>15</v>
@@ -6472,7 +6395,7 @@
         <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E132" t="s">
         <v>15</v>
@@ -6507,7 +6430,7 @@
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E133" t="s">
         <v>15</v>
@@ -6542,7 +6465,7 @@
         <v>11</v>
       </c>
       <c r="D134" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E134" t="s">
         <v>15</v>
@@ -6577,7 +6500,7 @@
         <v>11</v>
       </c>
       <c r="D135" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E135" t="s">
         <v>15</v>
@@ -6612,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E136" t="s">
         <v>15</v>
@@ -6647,7 +6570,7 @@
         <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E137" t="s">
         <v>15</v>
@@ -6682,7 +6605,7 @@
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E138" t="s">
         <v>15</v>
@@ -6717,7 +6640,7 @@
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E139" t="s">
         <v>15</v>
@@ -6752,7 +6675,7 @@
         <v>11</v>
       </c>
       <c r="D140" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E140" t="s">
         <v>15</v>
@@ -6787,7 +6710,7 @@
         <v>11</v>
       </c>
       <c r="D141" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E141" t="s">
         <v>15</v>
@@ -6822,7 +6745,7 @@
         <v>11</v>
       </c>
       <c r="D142" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E142" t="s">
         <v>15</v>
@@ -6857,7 +6780,7 @@
         <v>11</v>
       </c>
       <c r="D143" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E143" t="s">
         <v>15</v>
@@ -6892,7 +6815,7 @@
         <v>11</v>
       </c>
       <c r="D144" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E144" t="s">
         <v>15</v>
@@ -6927,7 +6850,7 @@
         <v>11</v>
       </c>
       <c r="D145" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E145" t="s">
         <v>15</v>
@@ -6962,7 +6885,7 @@
         <v>11</v>
       </c>
       <c r="D146" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E146" t="s">
         <v>15</v>
@@ -6997,7 +6920,7 @@
         <v>11</v>
       </c>
       <c r="D147" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E147" t="s">
         <v>15</v>
@@ -7032,7 +6955,7 @@
         <v>11</v>
       </c>
       <c r="D148" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E148" t="s">
         <v>15</v>
@@ -7067,7 +6990,7 @@
         <v>11</v>
       </c>
       <c r="D149" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E149" t="s">
         <v>15</v>
@@ -7102,7 +7025,7 @@
         <v>11</v>
       </c>
       <c r="D150" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E150" t="s">
         <v>15</v>
@@ -7137,7 +7060,7 @@
         <v>11</v>
       </c>
       <c r="D151" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E151" t="s">
         <v>15</v>
@@ -7172,7 +7095,7 @@
         <v>11</v>
       </c>
       <c r="D152" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E152" t="s">
         <v>15</v>
@@ -7207,7 +7130,7 @@
         <v>11</v>
       </c>
       <c r="D153" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E153" t="s">
         <v>15</v>
@@ -7242,7 +7165,7 @@
         <v>11</v>
       </c>
       <c r="D154" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E154" t="s">
         <v>15</v>
@@ -7277,7 +7200,7 @@
         <v>11</v>
       </c>
       <c r="D155" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E155" t="s">
         <v>15</v>
@@ -7312,7 +7235,7 @@
         <v>11</v>
       </c>
       <c r="D156" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E156" t="s">
         <v>15</v>
@@ -7347,7 +7270,7 @@
         <v>11</v>
       </c>
       <c r="D157" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E157" t="s">
         <v>15</v>
@@ -7382,7 +7305,7 @@
         <v>11</v>
       </c>
       <c r="D158" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E158" t="s">
         <v>15</v>
@@ -7417,7 +7340,7 @@
         <v>11</v>
       </c>
       <c r="D159" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E159" t="s">
         <v>15</v>
@@ -7452,7 +7375,7 @@
         <v>11</v>
       </c>
       <c r="D160" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E160" t="s">
         <v>15</v>
@@ -7487,7 +7410,7 @@
         <v>11</v>
       </c>
       <c r="D161" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E161" t="s">
         <v>15</v>
@@ -7522,7 +7445,7 @@
         <v>11</v>
       </c>
       <c r="D162" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E162" t="s">
         <v>15</v>
@@ -7557,7 +7480,7 @@
         <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E163" t="s">
         <v>15</v>
@@ -7592,7 +7515,7 @@
         <v>11</v>
       </c>
       <c r="D164" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E164" t="s">
         <v>15</v>
@@ -7627,7 +7550,7 @@
         <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E165" t="s">
         <v>15</v>
@@ -7662,7 +7585,7 @@
         <v>11</v>
       </c>
       <c r="D166" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E166" t="s">
         <v>15</v>
@@ -7697,7 +7620,7 @@
         <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E167" t="s">
         <v>15</v>
@@ -7732,7 +7655,7 @@
         <v>11</v>
       </c>
       <c r="D168" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E168" t="s">
         <v>15</v>
@@ -7767,7 +7690,7 @@
         <v>11</v>
       </c>
       <c r="D169" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E169" t="s">
         <v>15</v>
@@ -7802,7 +7725,7 @@
         <v>11</v>
       </c>
       <c r="D170" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E170" t="s">
         <v>15</v>
@@ -7837,7 +7760,7 @@
         <v>11</v>
       </c>
       <c r="D171" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E171" t="s">
         <v>15</v>
@@ -7872,7 +7795,7 @@
         <v>11</v>
       </c>
       <c r="D172" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E172" t="s">
         <v>15</v>
@@ -7907,7 +7830,7 @@
         <v>11</v>
       </c>
       <c r="D173" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E173" t="s">
         <v>15</v>
@@ -7942,7 +7865,7 @@
         <v>11</v>
       </c>
       <c r="D174" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E174" t="s">
         <v>15</v>
@@ -7977,7 +7900,7 @@
         <v>11</v>
       </c>
       <c r="D175" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E175" t="s">
         <v>15</v>
@@ -8012,7 +7935,7 @@
         <v>11</v>
       </c>
       <c r="D176" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E176" t="s">
         <v>15</v>
@@ -8047,7 +7970,7 @@
         <v>11</v>
       </c>
       <c r="D177" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E177" t="s">
         <v>15</v>
@@ -8082,7 +8005,7 @@
         <v>11</v>
       </c>
       <c r="D178" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E178" t="s">
         <v>15</v>
@@ -8117,7 +8040,7 @@
         <v>11</v>
       </c>
       <c r="D179" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E179" t="s">
         <v>15</v>
@@ -8152,7 +8075,7 @@
         <v>11</v>
       </c>
       <c r="D180" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E180" t="s">
         <v>15</v>
@@ -8187,7 +8110,7 @@
         <v>11</v>
       </c>
       <c r="D181" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E181" t="s">
         <v>15</v>
@@ -8222,7 +8145,7 @@
         <v>11</v>
       </c>
       <c r="D182" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E182" t="s">
         <v>15</v>
@@ -8257,7 +8180,7 @@
         <v>11</v>
       </c>
       <c r="D183" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E183" t="s">
         <v>15</v>
@@ -8292,7 +8215,7 @@
         <v>11</v>
       </c>
       <c r="D184" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E184" t="s">
         <v>15</v>
@@ -8327,7 +8250,7 @@
         <v>11</v>
       </c>
       <c r="D185" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E185" t="s">
         <v>15</v>
@@ -8362,7 +8285,7 @@
         <v>11</v>
       </c>
       <c r="D186" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E186" t="s">
         <v>15</v>
@@ -8397,7 +8320,7 @@
         <v>11</v>
       </c>
       <c r="D187" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E187" t="s">
         <v>15</v>
@@ -8432,7 +8355,7 @@
         <v>11</v>
       </c>
       <c r="D188" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E188" t="s">
         <v>15</v>
@@ -8467,7 +8390,7 @@
         <v>11</v>
       </c>
       <c r="D189" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E189" t="s">
         <v>15</v>
@@ -8502,7 +8425,7 @@
         <v>11</v>
       </c>
       <c r="D190" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E190" t="s">
         <v>15</v>
@@ -8537,7 +8460,7 @@
         <v>11</v>
       </c>
       <c r="D191" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E191" t="s">
         <v>15</v>
@@ -8572,7 +8495,7 @@
         <v>11</v>
       </c>
       <c r="D192" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E192" t="s">
         <v>15</v>
@@ -8607,7 +8530,7 @@
         <v>11</v>
       </c>
       <c r="D193" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E193" t="s">
         <v>15</v>
@@ -8642,7 +8565,7 @@
         <v>11</v>
       </c>
       <c r="D194" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E194" t="s">
         <v>15</v>
@@ -8677,7 +8600,7 @@
         <v>11</v>
       </c>
       <c r="D195" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E195" t="s">
         <v>15</v>
@@ -8712,7 +8635,7 @@
         <v>11</v>
       </c>
       <c r="D196" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E196" t="s">
         <v>15</v>
@@ -8747,7 +8670,7 @@
         <v>11</v>
       </c>
       <c r="D197" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E197" t="s">
         <v>15</v>
@@ -8782,7 +8705,7 @@
         <v>11</v>
       </c>
       <c r="D198" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E198" t="s">
         <v>15</v>
@@ -8817,7 +8740,7 @@
         <v>11</v>
       </c>
       <c r="D199" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E199" t="s">
         <v>15</v>
@@ -8852,7 +8775,7 @@
         <v>11</v>
       </c>
       <c r="D200" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E200" t="s">
         <v>15</v>
@@ -8887,7 +8810,7 @@
         <v>11</v>
       </c>
       <c r="D201" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E201" t="s">
         <v>15</v>
@@ -8922,7 +8845,7 @@
         <v>11</v>
       </c>
       <c r="D202" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E202" t="s">
         <v>15</v>
@@ -8957,7 +8880,7 @@
         <v>11</v>
       </c>
       <c r="D203" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E203" t="s">
         <v>15</v>
@@ -8992,7 +8915,7 @@
         <v>11</v>
       </c>
       <c r="D204" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E204" t="s">
         <v>15</v>
@@ -9027,7 +8950,7 @@
         <v>11</v>
       </c>
       <c r="D205" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E205" t="s">
         <v>15</v>
@@ -9062,7 +8985,7 @@
         <v>11</v>
       </c>
       <c r="D206" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E206" t="s">
         <v>15</v>
@@ -9097,7 +9020,7 @@
         <v>11</v>
       </c>
       <c r="D207" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E207" t="s">
         <v>15</v>
@@ -9132,7 +9055,7 @@
         <v>11</v>
       </c>
       <c r="D208" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E208" t="s">
         <v>15</v>
@@ -9167,7 +9090,7 @@
         <v>11</v>
       </c>
       <c r="D209" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E209" t="s">
         <v>15</v>
@@ -9202,7 +9125,7 @@
         <v>11</v>
       </c>
       <c r="D210" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E210" t="s">
         <v>15</v>
@@ -9237,7 +9160,7 @@
         <v>11</v>
       </c>
       <c r="D211" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E211" t="s">
         <v>15</v>
@@ -9272,7 +9195,7 @@
         <v>11</v>
       </c>
       <c r="D212" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E212" t="s">
         <v>15</v>
@@ -9307,7 +9230,7 @@
         <v>11</v>
       </c>
       <c r="D213" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E213" t="s">
         <v>15</v>
@@ -9342,7 +9265,7 @@
         <v>11</v>
       </c>
       <c r="D214" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E214" t="s">
         <v>15</v>
@@ -9377,7 +9300,7 @@
         <v>11</v>
       </c>
       <c r="D215" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E215" t="s">
         <v>15</v>
@@ -9412,7 +9335,7 @@
         <v>11</v>
       </c>
       <c r="D216" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E216" t="s">
         <v>15</v>
@@ -9447,7 +9370,7 @@
         <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E217" t="s">
         <v>15</v>
@@ -9482,7 +9405,7 @@
         <v>11</v>
       </c>
       <c r="D218" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E218" t="s">
         <v>15</v>
@@ -9517,7 +9440,7 @@
         <v>11</v>
       </c>
       <c r="D219" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E219" t="s">
         <v>15</v>
@@ -9552,7 +9475,7 @@
         <v>11</v>
       </c>
       <c r="D220" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E220" t="s">
         <v>15</v>
@@ -9587,7 +9510,7 @@
         <v>11</v>
       </c>
       <c r="D221" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E221" t="s">
         <v>15</v>
@@ -9622,7 +9545,7 @@
         <v>11</v>
       </c>
       <c r="D222" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E222" t="s">
         <v>15</v>
@@ -9657,7 +9580,7 @@
         <v>11</v>
       </c>
       <c r="D223" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E223" t="s">
         <v>15</v>
@@ -9692,7 +9615,7 @@
         <v>11</v>
       </c>
       <c r="D224" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E224" t="s">
         <v>15</v>
@@ -9727,7 +9650,7 @@
         <v>11</v>
       </c>
       <c r="D225" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E225" t="s">
         <v>15</v>
@@ -9762,7 +9685,7 @@
         <v>11</v>
       </c>
       <c r="D226" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E226" t="s">
         <v>15</v>
@@ -9797,7 +9720,7 @@
         <v>11</v>
       </c>
       <c r="D227" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E227" t="s">
         <v>15</v>
@@ -9832,7 +9755,7 @@
         <v>11</v>
       </c>
       <c r="D228" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E228" t="s">
         <v>15</v>
@@ -9867,7 +9790,7 @@
         <v>11</v>
       </c>
       <c r="D229" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E229" t="s">
         <v>15</v>
@@ -9902,7 +9825,7 @@
         <v>11</v>
       </c>
       <c r="D230" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E230" t="s">
         <v>15</v>
@@ -9937,7 +9860,7 @@
         <v>11</v>
       </c>
       <c r="D231" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E231" t="s">
         <v>15</v>
@@ -9972,7 +9895,7 @@
         <v>11</v>
       </c>
       <c r="D232" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E232" t="s">
         <v>15</v>
@@ -10007,7 +9930,7 @@
         <v>11</v>
       </c>
       <c r="D233" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E233" t="s">
         <v>15</v>
@@ -10042,7 +9965,7 @@
         <v>11</v>
       </c>
       <c r="D234" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E234" t="s">
         <v>15</v>
@@ -10077,7 +10000,7 @@
         <v>11</v>
       </c>
       <c r="D235" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E235" t="s">
         <v>15</v>
@@ -10112,7 +10035,7 @@
         <v>11</v>
       </c>
       <c r="D236" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E236" t="s">
         <v>15</v>
@@ -10147,7 +10070,7 @@
         <v>11</v>
       </c>
       <c r="D237" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E237" t="s">
         <v>15</v>
@@ -10182,7 +10105,7 @@
         <v>11</v>
       </c>
       <c r="D238" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E238" t="s">
         <v>15</v>
@@ -10217,7 +10140,7 @@
         <v>11</v>
       </c>
       <c r="D239" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E239" t="s">
         <v>15</v>
@@ -10252,7 +10175,7 @@
         <v>11</v>
       </c>
       <c r="D240" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E240" t="s">
         <v>15</v>
@@ -10287,7 +10210,7 @@
         <v>11</v>
       </c>
       <c r="D241" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E241" t="s">
         <v>15</v>
@@ -10322,7 +10245,7 @@
         <v>11</v>
       </c>
       <c r="D242" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E242" t="s">
         <v>15</v>
@@ -10357,7 +10280,7 @@
         <v>11</v>
       </c>
       <c r="D243" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E243" t="s">
         <v>15</v>
@@ -10392,7 +10315,7 @@
         <v>11</v>
       </c>
       <c r="D244" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E244" t="s">
         <v>15</v>
@@ -10427,7 +10350,7 @@
         <v>11</v>
       </c>
       <c r="D245" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E245" t="s">
         <v>15</v>
@@ -10462,7 +10385,7 @@
         <v>11</v>
       </c>
       <c r="D246" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E246" t="s">
         <v>15</v>
@@ -10497,7 +10420,7 @@
         <v>11</v>
       </c>
       <c r="D247" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E247" t="s">
         <v>15</v>
@@ -10532,7 +10455,7 @@
         <v>11</v>
       </c>
       <c r="D248" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E248" t="s">
         <v>15</v>
@@ -10567,7 +10490,7 @@
         <v>11</v>
       </c>
       <c r="D249" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E249" t="s">
         <v>15</v>
@@ -10602,7 +10525,7 @@
         <v>11</v>
       </c>
       <c r="D250" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E250" t="s">
         <v>15</v>
@@ -10637,7 +10560,7 @@
         <v>11</v>
       </c>
       <c r="D251" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E251" t="s">
         <v>15</v>
@@ -10672,7 +10595,7 @@
         <v>11</v>
       </c>
       <c r="D252" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E252" t="s">
         <v>15</v>
@@ -10707,7 +10630,7 @@
         <v>11</v>
       </c>
       <c r="D253" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E253" t="s">
         <v>15</v>
@@ -10742,7 +10665,7 @@
         <v>11</v>
       </c>
       <c r="D254" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E254" t="s">
         <v>15</v>
@@ -10777,7 +10700,7 @@
         <v>11</v>
       </c>
       <c r="D255" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E255" t="s">
         <v>15</v>
@@ -10812,7 +10735,7 @@
         <v>11</v>
       </c>
       <c r="D256" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E256" t="s">
         <v>15</v>
@@ -10847,7 +10770,7 @@
         <v>11</v>
       </c>
       <c r="D257" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E257" t="s">
         <v>15</v>
@@ -10882,7 +10805,7 @@
         <v>11</v>
       </c>
       <c r="D258" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E258" t="s">
         <v>15</v>
@@ -10917,7 +10840,7 @@
         <v>11</v>
       </c>
       <c r="D259" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E259" t="s">
         <v>15</v>
@@ -10952,7 +10875,7 @@
         <v>11</v>
       </c>
       <c r="D260" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E260" t="s">
         <v>15</v>
@@ -10987,7 +10910,7 @@
         <v>11</v>
       </c>
       <c r="D261" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E261" t="s">
         <v>15</v>
@@ -11022,7 +10945,7 @@
         <v>11</v>
       </c>
       <c r="D262" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E262" t="s">
         <v>15</v>
@@ -11057,7 +10980,7 @@
         <v>11</v>
       </c>
       <c r="D263" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E263" t="s">
         <v>15</v>
@@ -11092,7 +11015,7 @@
         <v>11</v>
       </c>
       <c r="D264" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E264" t="s">
         <v>15</v>
@@ -11127,7 +11050,7 @@
         <v>11</v>
       </c>
       <c r="D265" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E265" t="s">
         <v>15</v>
@@ -11162,7 +11085,7 @@
         <v>11</v>
       </c>
       <c r="D266" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E266" t="s">
         <v>15</v>
@@ -11197,7 +11120,7 @@
         <v>11</v>
       </c>
       <c r="D267" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E267" t="s">
         <v>15</v>
@@ -11232,7 +11155,7 @@
         <v>11</v>
       </c>
       <c r="D268" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E268" t="s">
         <v>15</v>
@@ -11267,7 +11190,7 @@
         <v>11</v>
       </c>
       <c r="D269" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E269" t="s">
         <v>15</v>
@@ -11302,7 +11225,7 @@
         <v>11</v>
       </c>
       <c r="D270" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E270" t="s">
         <v>15</v>
@@ -11337,7 +11260,7 @@
         <v>11</v>
       </c>
       <c r="D271" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E271" t="s">
         <v>15</v>
@@ -11372,7 +11295,7 @@
         <v>11</v>
       </c>
       <c r="D272" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E272" t="s">
         <v>15</v>
@@ -11407,7 +11330,7 @@
         <v>11</v>
       </c>
       <c r="D273" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E273" t="s">
         <v>15</v>
@@ -11442,7 +11365,7 @@
         <v>11</v>
       </c>
       <c r="D274" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E274" t="s">
         <v>15</v>
@@ -11477,7 +11400,7 @@
         <v>11</v>
       </c>
       <c r="D275" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E275" t="s">
         <v>15</v>
@@ -11512,7 +11435,7 @@
         <v>11</v>
       </c>
       <c r="D276" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E276" t="s">
         <v>15</v>
@@ -11547,7 +11470,7 @@
         <v>11</v>
       </c>
       <c r="D277" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E277" t="s">
         <v>15</v>
@@ -11582,7 +11505,7 @@
         <v>11</v>
       </c>
       <c r="D278" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E278" t="s">
         <v>15</v>
@@ -11617,7 +11540,7 @@
         <v>11</v>
       </c>
       <c r="D279" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E279" t="s">
         <v>15</v>
@@ -11652,7 +11575,7 @@
         <v>11</v>
       </c>
       <c r="D280" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E280" t="s">
         <v>15</v>
@@ -11687,7 +11610,7 @@
         <v>11</v>
       </c>
       <c r="D281" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E281" t="s">
         <v>15</v>
@@ -11722,7 +11645,7 @@
         <v>11</v>
       </c>
       <c r="D282" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E282" t="s">
         <v>15</v>
@@ -11757,7 +11680,7 @@
         <v>11</v>
       </c>
       <c r="D283" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E283" t="s">
         <v>15</v>
@@ -11792,7 +11715,7 @@
         <v>11</v>
       </c>
       <c r="D284" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E284" t="s">
         <v>15</v>
@@ -11827,7 +11750,7 @@
         <v>11</v>
       </c>
       <c r="D285" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E285" t="s">
         <v>15</v>
@@ -11862,7 +11785,7 @@
         <v>11</v>
       </c>
       <c r="D286" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E286" t="s">
         <v>15</v>
@@ -11897,7 +11820,7 @@
         <v>11</v>
       </c>
       <c r="D287" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E287" t="s">
         <v>15</v>
@@ -11932,7 +11855,7 @@
         <v>11</v>
       </c>
       <c r="D288" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E288" t="s">
         <v>15</v>
@@ -11967,7 +11890,7 @@
         <v>11</v>
       </c>
       <c r="D289" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E289" t="s">
         <v>15</v>
@@ -12002,7 +11925,7 @@
         <v>11</v>
       </c>
       <c r="D290" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E290" t="s">
         <v>15</v>
@@ -12037,7 +11960,7 @@
         <v>11</v>
       </c>
       <c r="D291" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E291" t="s">
         <v>15</v>
@@ -12072,7 +11995,7 @@
         <v>11</v>
       </c>
       <c r="D292" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E292" t="s">
         <v>15</v>
@@ -12107,7 +12030,7 @@
         <v>11</v>
       </c>
       <c r="D293" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E293" t="s">
         <v>15</v>
@@ -12142,7 +12065,7 @@
         <v>11</v>
       </c>
       <c r="D294" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E294" t="s">
         <v>15</v>
@@ -12177,7 +12100,7 @@
         <v>11</v>
       </c>
       <c r="D295" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E295" t="s">
         <v>15</v>
@@ -12212,7 +12135,7 @@
         <v>11</v>
       </c>
       <c r="D296" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E296" t="s">
         <v>15</v>
@@ -12247,7 +12170,7 @@
         <v>11</v>
       </c>
       <c r="D297" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E297" t="s">
         <v>15</v>
@@ -12282,7 +12205,7 @@
         <v>11</v>
       </c>
       <c r="D298" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E298" t="s">
         <v>15</v>
@@ -12317,7 +12240,7 @@
         <v>11</v>
       </c>
       <c r="D299" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E299" t="s">
         <v>15</v>
@@ -12352,7 +12275,7 @@
         <v>11</v>
       </c>
       <c r="D300" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E300" t="s">
         <v>15</v>
@@ -12387,7 +12310,7 @@
         <v>11</v>
       </c>
       <c r="D301" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E301" t="s">
         <v>15</v>
@@ -12422,7 +12345,7 @@
         <v>11</v>
       </c>
       <c r="D302" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E302" t="s">
         <v>15</v>
@@ -12457,7 +12380,7 @@
         <v>11</v>
       </c>
       <c r="D303" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E303" t="s">
         <v>15</v>
@@ -12492,7 +12415,7 @@
         <v>11</v>
       </c>
       <c r="D304" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E304" t="s">
         <v>15</v>
@@ -12527,7 +12450,7 @@
         <v>11</v>
       </c>
       <c r="D305" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E305" t="s">
         <v>15</v>
@@ -12562,7 +12485,7 @@
         <v>11</v>
       </c>
       <c r="D306" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E306" t="s">
         <v>15</v>
@@ -12597,7 +12520,7 @@
         <v>11</v>
       </c>
       <c r="D307" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E307" t="s">
         <v>15</v>
@@ -12632,7 +12555,7 @@
         <v>11</v>
       </c>
       <c r="D308" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E308" t="s">
         <v>15</v>
@@ -12667,7 +12590,7 @@
         <v>11</v>
       </c>
       <c r="D309" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E309" t="s">
         <v>15</v>
@@ -12702,7 +12625,7 @@
         <v>11</v>
       </c>
       <c r="D310" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E310" t="s">
         <v>15</v>
@@ -12737,7 +12660,7 @@
         <v>11</v>
       </c>
       <c r="D311" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E311" t="s">
         <v>15</v>
@@ -12772,7 +12695,7 @@
         <v>11</v>
       </c>
       <c r="D312" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E312" t="s">
         <v>15</v>
@@ -12807,7 +12730,7 @@
         <v>11</v>
       </c>
       <c r="D313" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E313" t="s">
         <v>15</v>
@@ -12842,7 +12765,7 @@
         <v>11</v>
       </c>
       <c r="D314" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E314" t="s">
         <v>15</v>
@@ -12877,7 +12800,7 @@
         <v>11</v>
       </c>
       <c r="D315" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E315" t="s">
         <v>15</v>
@@ -12912,7 +12835,7 @@
         <v>11</v>
       </c>
       <c r="D316" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E316" t="s">
         <v>15</v>
@@ -12947,7 +12870,7 @@
         <v>11</v>
       </c>
       <c r="D317" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E317" t="s">
         <v>15</v>
@@ -12982,7 +12905,7 @@
         <v>11</v>
       </c>
       <c r="D318" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E318" t="s">
         <v>15</v>
@@ -13017,7 +12940,7 @@
         <v>11</v>
       </c>
       <c r="D319" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="E319" t="s">
         <v>15</v>
@@ -13052,7 +12975,7 @@
         <v>11</v>
       </c>
       <c r="D320" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E320" t="s">
         <v>15</v>
@@ -13087,7 +13010,7 @@
         <v>11</v>
       </c>
       <c r="D321" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E321" t="s">
         <v>15</v>
@@ -13122,7 +13045,7 @@
         <v>11</v>
       </c>
       <c r="D322" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E322" t="s">
         <v>15</v>
@@ -13157,7 +13080,7 @@
         <v>11</v>
       </c>
       <c r="D323" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E323" t="s">
         <v>15</v>
@@ -13192,7 +13115,7 @@
         <v>11</v>
       </c>
       <c r="D324" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E324" t="s">
         <v>15</v>
@@ -13227,7 +13150,7 @@
         <v>11</v>
       </c>
       <c r="D325" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E325" t="s">
         <v>15</v>
@@ -13262,7 +13185,7 @@
         <v>11</v>
       </c>
       <c r="D326" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E326" t="s">
         <v>15</v>
@@ -13297,7 +13220,7 @@
         <v>11</v>
       </c>
       <c r="D327" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E327" t="s">
         <v>15</v>
@@ -13332,7 +13255,7 @@
         <v>11</v>
       </c>
       <c r="D328" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E328" t="s">
         <v>15</v>
@@ -13367,7 +13290,7 @@
         <v>11</v>
       </c>
       <c r="D329" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E329" t="s">
         <v>15</v>
@@ -13402,7 +13325,7 @@
         <v>11</v>
       </c>
       <c r="D330" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E330" t="s">
         <v>15</v>
@@ -13437,7 +13360,7 @@
         <v>11</v>
       </c>
       <c r="D331" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E331" t="s">
         <v>15</v>
@@ -13472,7 +13395,7 @@
         <v>11</v>
       </c>
       <c r="D332" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E332" t="s">
         <v>15</v>
@@ -13507,7 +13430,7 @@
         <v>11</v>
       </c>
       <c r="D333" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E333" t="s">
         <v>15</v>
@@ -13542,7 +13465,7 @@
         <v>11</v>
       </c>
       <c r="D334" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E334" t="s">
         <v>15</v>
@@ -13577,7 +13500,7 @@
         <v>11</v>
       </c>
       <c r="D335" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E335" t="s">
         <v>15</v>
@@ -13612,7 +13535,7 @@
         <v>11</v>
       </c>
       <c r="D336" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E336" t="s">
         <v>15</v>
@@ -13647,7 +13570,7 @@
         <v>11</v>
       </c>
       <c r="D337" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E337" t="s">
         <v>15</v>
@@ -13682,7 +13605,7 @@
         <v>11</v>
       </c>
       <c r="D338" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E338" t="s">
         <v>15</v>
@@ -13717,7 +13640,7 @@
         <v>11</v>
       </c>
       <c r="D339" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E339" t="s">
         <v>15</v>
@@ -13752,7 +13675,7 @@
         <v>11</v>
       </c>
       <c r="D340" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E340" t="s">
         <v>15</v>
@@ -13787,7 +13710,7 @@
         <v>11</v>
       </c>
       <c r="D341" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E341" t="s">
         <v>15</v>
@@ -13822,7 +13745,7 @@
         <v>11</v>
       </c>
       <c r="D342" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E342" t="s">
         <v>15</v>
@@ -13857,7 +13780,7 @@
         <v>11</v>
       </c>
       <c r="D343" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E343" t="s">
         <v>15</v>
@@ -13892,7 +13815,7 @@
         <v>11</v>
       </c>
       <c r="D344" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E344" t="s">
         <v>15</v>
@@ -13927,7 +13850,7 @@
         <v>11</v>
       </c>
       <c r="D345" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E345" t="s">
         <v>15</v>
@@ -13962,7 +13885,7 @@
         <v>11</v>
       </c>
       <c r="D346" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E346" t="s">
         <v>15</v>
@@ -13997,7 +13920,7 @@
         <v>11</v>
       </c>
       <c r="D347" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E347" t="s">
         <v>15</v>
@@ -14032,7 +13955,7 @@
         <v>11</v>
       </c>
       <c r="D348" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E348" t="s">
         <v>15</v>
@@ -14067,7 +13990,7 @@
         <v>11</v>
       </c>
       <c r="D349" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E349" t="s">
         <v>15</v>
@@ -14102,7 +14025,7 @@
         <v>11</v>
       </c>
       <c r="D350" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E350" t="s">
         <v>15</v>
@@ -14137,7 +14060,7 @@
         <v>11</v>
       </c>
       <c r="D351" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E351" t="s">
         <v>15</v>
@@ -14172,7 +14095,7 @@
         <v>11</v>
       </c>
       <c r="D352" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E352" t="s">
         <v>15</v>
@@ -14207,7 +14130,7 @@
         <v>11</v>
       </c>
       <c r="D353" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E353" t="s">
         <v>15</v>
@@ -14242,7 +14165,7 @@
         <v>11</v>
       </c>
       <c r="D354" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E354" t="s">
         <v>15</v>
@@ -14277,7 +14200,7 @@
         <v>11</v>
       </c>
       <c r="D355" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E355" t="s">
         <v>15</v>
@@ -14312,7 +14235,7 @@
         <v>11</v>
       </c>
       <c r="D356" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E356" t="s">
         <v>15</v>
@@ -14347,7 +14270,7 @@
         <v>11</v>
       </c>
       <c r="D357" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E357" t="s">
         <v>15</v>
@@ -14382,7 +14305,7 @@
         <v>11</v>
       </c>
       <c r="D358" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E358" t="s">
         <v>15</v>
@@ -14417,7 +14340,7 @@
         <v>11</v>
       </c>
       <c r="D359" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E359" t="s">
         <v>15</v>
@@ -14452,7 +14375,7 @@
         <v>11</v>
       </c>
       <c r="D360" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E360" t="s">
         <v>15</v>
@@ -14487,7 +14410,7 @@
         <v>11</v>
       </c>
       <c r="D361" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E361" t="s">
         <v>15</v>
@@ -14522,7 +14445,7 @@
         <v>11</v>
       </c>
       <c r="D362" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E362" t="s">
         <v>15</v>
@@ -14557,7 +14480,7 @@
         <v>11</v>
       </c>
       <c r="D363" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E363" t="s">
         <v>15</v>
@@ -14592,7 +14515,7 @@
         <v>11</v>
       </c>
       <c r="D364" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E364" t="s">
         <v>15</v>
@@ -14627,7 +14550,7 @@
         <v>11</v>
       </c>
       <c r="D365" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E365" t="s">
         <v>15</v>
@@ -14662,7 +14585,7 @@
         <v>11</v>
       </c>
       <c r="D366" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E366" t="s">
         <v>15</v>
@@ -14697,7 +14620,7 @@
         <v>11</v>
       </c>
       <c r="D367" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E367" t="s">
         <v>15</v>
@@ -14732,7 +14655,7 @@
         <v>11</v>
       </c>
       <c r="D368" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E368" t="s">
         <v>15</v>
@@ -14767,7 +14690,7 @@
         <v>11</v>
       </c>
       <c r="D369" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E369" t="s">
         <v>15</v>
@@ -14802,7 +14725,7 @@
         <v>11</v>
       </c>
       <c r="D370" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E370" t="s">
         <v>15</v>
@@ -14837,7 +14760,7 @@
         <v>11</v>
       </c>
       <c r="D371" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E371" t="s">
         <v>15</v>
@@ -14872,7 +14795,7 @@
         <v>11</v>
       </c>
       <c r="D372" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E372" t="s">
         <v>15</v>
@@ -14907,7 +14830,7 @@
         <v>11</v>
       </c>
       <c r="D373" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E373" t="s">
         <v>15</v>
@@ -14942,7 +14865,7 @@
         <v>11</v>
       </c>
       <c r="D374" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E374" t="s">
         <v>15</v>
@@ -14977,7 +14900,7 @@
         <v>11</v>
       </c>
       <c r="D375" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E375" t="s">
         <v>15</v>
@@ -15012,7 +14935,7 @@
         <v>11</v>
       </c>
       <c r="D376" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E376" t="s">
         <v>15</v>
@@ -15047,7 +14970,7 @@
         <v>11</v>
       </c>
       <c r="D377" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E377" t="s">
         <v>15</v>
@@ -15082,7 +15005,7 @@
         <v>11</v>
       </c>
       <c r="D378" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E378" t="s">
         <v>15</v>
@@ -15117,7 +15040,7 @@
         <v>11</v>
       </c>
       <c r="D379" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E379" t="s">
         <v>15</v>
@@ -15152,7 +15075,7 @@
         <v>11</v>
       </c>
       <c r="D380" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E380" t="s">
         <v>15</v>
@@ -15187,7 +15110,7 @@
         <v>11</v>
       </c>
       <c r="D381" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E381" t="s">
         <v>15</v>
@@ -15222,7 +15145,7 @@
         <v>11</v>
       </c>
       <c r="D382" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E382" t="s">
         <v>15</v>
@@ -15257,7 +15180,7 @@
         <v>11</v>
       </c>
       <c r="D383" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E383" t="s">
         <v>15</v>
@@ -15292,7 +15215,7 @@
         <v>11</v>
       </c>
       <c r="D384" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E384" t="s">
         <v>15</v>
@@ -15327,7 +15250,7 @@
         <v>11</v>
       </c>
       <c r="D385" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E385" t="s">
         <v>15</v>
@@ -15362,7 +15285,7 @@
         <v>11</v>
       </c>
       <c r="D386" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="E386" t="s">
         <v>15</v>
@@ -15397,7 +15320,7 @@
         <v>11</v>
       </c>
       <c r="D387" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E387" t="s">
         <v>15</v>
@@ -15432,7 +15355,7 @@
         <v>11</v>
       </c>
       <c r="D388" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E388" t="s">
         <v>15</v>
@@ -15467,7 +15390,7 @@
         <v>11</v>
       </c>
       <c r="D389" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E389" t="s">
         <v>15</v>
@@ -15502,7 +15425,7 @@
         <v>11</v>
       </c>
       <c r="D390" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E390" t="s">
         <v>15</v>
@@ -15537,7 +15460,7 @@
         <v>11</v>
       </c>
       <c r="D391" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E391" t="s">
         <v>15</v>
@@ -15572,7 +15495,7 @@
         <v>11</v>
       </c>
       <c r="D392" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E392" t="s">
         <v>15</v>
@@ -15607,7 +15530,7 @@
         <v>11</v>
       </c>
       <c r="D393" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E393" t="s">
         <v>15</v>
@@ -15642,7 +15565,7 @@
         <v>11</v>
       </c>
       <c r="D394" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E394" t="s">
         <v>15</v>
@@ -15677,7 +15600,7 @@
         <v>11</v>
       </c>
       <c r="D395" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E395" t="s">
         <v>15</v>
@@ -15712,7 +15635,7 @@
         <v>11</v>
       </c>
       <c r="D396" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E396" t="s">
         <v>15</v>
@@ -15747,7 +15670,7 @@
         <v>11</v>
       </c>
       <c r="D397" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E397" t="s">
         <v>15</v>
@@ -15782,7 +15705,7 @@
         <v>11</v>
       </c>
       <c r="D398" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E398" t="s">
         <v>15</v>
@@ -15817,7 +15740,7 @@
         <v>11</v>
       </c>
       <c r="D399" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E399" t="s">
         <v>15</v>
@@ -15852,7 +15775,7 @@
         <v>11</v>
       </c>
       <c r="D400" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E400" t="s">
         <v>15</v>
@@ -15887,7 +15810,7 @@
         <v>11</v>
       </c>
       <c r="D401" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E401" t="s">
         <v>15</v>
@@ -15922,7 +15845,7 @@
         <v>11</v>
       </c>
       <c r="D402" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E402" t="s">
         <v>15</v>
@@ -15957,7 +15880,7 @@
         <v>11</v>
       </c>
       <c r="D403" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E403" t="s">
         <v>15</v>
@@ -15992,7 +15915,7 @@
         <v>11</v>
       </c>
       <c r="D404" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E404" t="s">
         <v>15</v>
@@ -16027,7 +15950,7 @@
         <v>11</v>
       </c>
       <c r="D405" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E405" t="s">
         <v>15</v>
@@ -16062,7 +15985,7 @@
         <v>11</v>
       </c>
       <c r="D406" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E406" t="s">
         <v>15</v>
@@ -16097,7 +16020,7 @@
         <v>11</v>
       </c>
       <c r="D407" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E407" t="s">
         <v>15</v>
@@ -16132,7 +16055,7 @@
         <v>11</v>
       </c>
       <c r="D408" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E408" t="s">
         <v>15</v>
@@ -16167,7 +16090,7 @@
         <v>11</v>
       </c>
       <c r="D409" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E409" t="s">
         <v>15</v>
@@ -16202,7 +16125,7 @@
         <v>11</v>
       </c>
       <c r="D410" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E410" t="s">
         <v>15</v>
@@ -16237,7 +16160,7 @@
         <v>11</v>
       </c>
       <c r="D411" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E411" t="s">
         <v>15</v>
@@ -16272,7 +16195,7 @@
         <v>11</v>
       </c>
       <c r="D412" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E412" t="s">
         <v>15</v>
@@ -16307,7 +16230,7 @@
         <v>11</v>
       </c>
       <c r="D413" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E413" t="s">
         <v>15</v>
@@ -16342,7 +16265,7 @@
         <v>11</v>
       </c>
       <c r="D414" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E414" t="s">
         <v>15</v>
@@ -16377,7 +16300,7 @@
         <v>11</v>
       </c>
       <c r="D415" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E415" t="s">
         <v>15</v>
@@ -16412,7 +16335,7 @@
         <v>11</v>
       </c>
       <c r="D416" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E416" t="s">
         <v>15</v>
@@ -16447,7 +16370,7 @@
         <v>11</v>
       </c>
       <c r="D417" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E417" t="s">
         <v>15</v>
@@ -16482,7 +16405,7 @@
         <v>11</v>
       </c>
       <c r="D418" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="E418" t="s">
         <v>15</v>
@@ -16517,7 +16440,7 @@
         <v>11</v>
       </c>
       <c r="D419" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E419" t="s">
         <v>15</v>
@@ -16552,7 +16475,7 @@
         <v>11</v>
       </c>
       <c r="D420" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="E420" t="s">
         <v>15</v>
@@ -16587,7 +16510,7 @@
         <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E421" t="s">
         <v>15</v>
@@ -16622,7 +16545,7 @@
         <v>11</v>
       </c>
       <c r="D422" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E422" t="s">
         <v>15</v>
@@ -16657,7 +16580,7 @@
         <v>11</v>
       </c>
       <c r="D423" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E423" t="s">
         <v>15</v>
@@ -16692,7 +16615,7 @@
         <v>11</v>
       </c>
       <c r="D424" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E424" t="s">
         <v>15</v>
@@ -16727,7 +16650,7 @@
         <v>11</v>
       </c>
       <c r="D425" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E425" t="s">
         <v>15</v>
@@ -16762,7 +16685,7 @@
         <v>11</v>
       </c>
       <c r="D426" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E426" t="s">
         <v>15</v>
@@ -16797,7 +16720,7 @@
         <v>11</v>
       </c>
       <c r="D427" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E427" t="s">
         <v>15</v>
@@ -16832,7 +16755,7 @@
         <v>11</v>
       </c>
       <c r="D428" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E428" t="s">
         <v>15</v>
@@ -16867,7 +16790,7 @@
         <v>11</v>
       </c>
       <c r="D429" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E429" t="s">
         <v>15</v>
@@ -16902,7 +16825,7 @@
         <v>11</v>
       </c>
       <c r="D430" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E430" t="s">
         <v>15</v>
@@ -16937,7 +16860,7 @@
         <v>11</v>
       </c>
       <c r="D431" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E431" t="s">
         <v>15</v>
@@ -16972,7 +16895,7 @@
         <v>11</v>
       </c>
       <c r="D432" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E432" t="s">
         <v>15</v>
@@ -17007,7 +16930,7 @@
         <v>11</v>
       </c>
       <c r="D433" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E433" t="s">
         <v>15</v>
@@ -17042,7 +16965,7 @@
         <v>11</v>
       </c>
       <c r="D434" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="E434" t="s">
         <v>15</v>
@@ -17077,7 +17000,7 @@
         <v>11</v>
       </c>
       <c r="D435" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E435" t="s">
         <v>15</v>
@@ -17112,7 +17035,7 @@
         <v>11</v>
       </c>
       <c r="D436" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E436" t="s">
         <v>15</v>
@@ -17147,7 +17070,7 @@
         <v>11</v>
       </c>
       <c r="D437" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E437" t="s">
         <v>15</v>
@@ -17182,7 +17105,7 @@
         <v>11</v>
       </c>
       <c r="D438" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E438" t="s">
         <v>15</v>
@@ -17217,7 +17140,7 @@
         <v>11</v>
       </c>
       <c r="D439" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E439" t="s">
         <v>15</v>
@@ -17252,7 +17175,7 @@
         <v>11</v>
       </c>
       <c r="D440" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E440" t="s">
         <v>15</v>
@@ -17287,7 +17210,7 @@
         <v>11</v>
       </c>
       <c r="D441" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E441" t="s">
         <v>15</v>
@@ -17322,7 +17245,7 @@
         <v>11</v>
       </c>
       <c r="D442" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E442" t="s">
         <v>15</v>
@@ -17357,7 +17280,7 @@
         <v>11</v>
       </c>
       <c r="D443" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E443" t="s">
         <v>15</v>
@@ -17392,7 +17315,7 @@
         <v>11</v>
       </c>
       <c r="D444" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E444" t="s">
         <v>15</v>
@@ -17427,7 +17350,7 @@
         <v>11</v>
       </c>
       <c r="D445" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="E445" t="s">
         <v>15</v>
@@ -17462,7 +17385,7 @@
         <v>11</v>
       </c>
       <c r="D446" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E446" t="s">
         <v>15</v>
@@ -17497,7 +17420,7 @@
         <v>11</v>
       </c>
       <c r="D447" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E447" t="s">
         <v>15</v>
@@ -17532,7 +17455,7 @@
         <v>11</v>
       </c>
       <c r="D448" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E448" t="s">
         <v>15</v>
@@ -17567,7 +17490,7 @@
         <v>11</v>
       </c>
       <c r="D449" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E449" t="s">
         <v>15</v>
@@ -17602,7 +17525,7 @@
         <v>11</v>
       </c>
       <c r="D450" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E450" t="s">
         <v>15</v>
@@ -17637,7 +17560,7 @@
         <v>11</v>
       </c>
       <c r="D451" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E451" t="s">
         <v>15</v>
@@ -17672,7 +17595,7 @@
         <v>11</v>
       </c>
       <c r="D452" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E452" t="s">
         <v>15</v>
@@ -17707,7 +17630,7 @@
         <v>11</v>
       </c>
       <c r="D453" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E453" t="s">
         <v>15</v>
@@ -17742,7 +17665,7 @@
         <v>11</v>
       </c>
       <c r="D454" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E454" t="s">
         <v>15</v>
@@ -17777,7 +17700,7 @@
         <v>11</v>
       </c>
       <c r="D455" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E455" t="s">
         <v>15</v>
@@ -17812,7 +17735,7 @@
         <v>11</v>
       </c>
       <c r="D456" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E456" t="s">
         <v>15</v>
@@ -17847,7 +17770,7 @@
         <v>11</v>
       </c>
       <c r="D457" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E457" t="s">
         <v>15</v>
@@ -17882,7 +17805,7 @@
         <v>11</v>
       </c>
       <c r="D458" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="E458" t="s">
         <v>15</v>
@@ -17917,7 +17840,7 @@
         <v>11</v>
       </c>
       <c r="D459" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E459" t="s">
         <v>15</v>
@@ -17952,7 +17875,7 @@
         <v>11</v>
       </c>
       <c r="D460" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E460" t="s">
         <v>15</v>
@@ -17987,7 +17910,7 @@
         <v>11</v>
       </c>
       <c r="D461" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E461" t="s">
         <v>15</v>
@@ -18022,7 +17945,7 @@
         <v>11</v>
       </c>
       <c r="D462" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="E462" t="s">
         <v>15</v>
@@ -18057,7 +17980,7 @@
         <v>11</v>
       </c>
       <c r="D463" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E463" t="s">
         <v>15</v>
@@ -18092,7 +18015,7 @@
         <v>11</v>
       </c>
       <c r="D464" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="E464" t="s">
         <v>15</v>
@@ -18127,7 +18050,7 @@
         <v>11</v>
       </c>
       <c r="D465" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="E465" t="s">
         <v>15</v>
@@ -18162,7 +18085,7 @@
         <v>11</v>
       </c>
       <c r="D466" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E466" t="s">
         <v>15</v>
@@ -18211,6 +18134,6 @@
     <hyperlink ref="D13" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>